--- a/SAT-SDMA-7 Perfiles.xlsx
+++ b/SAT-SDMA-7 Perfiles.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\raquell.martinez\Documents\AISolutions\analyzeCV\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2658ECC1-7A17-4441-A666-75F96C7D67DC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{48270E28-314C-46A5-AFAA-978C0A2F2BF4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="2" activeTab="2" xr2:uid="{D74C329F-941D-40F9-B295-21746B646AD6}"/>
+    <workbookView xWindow="0" yWindow="840" windowWidth="19360" windowHeight="10480" firstSheet="2" activeTab="2" xr2:uid="{D74C329F-941D-40F9-B295-21746B646AD6}"/>
   </bookViews>
   <sheets>
     <sheet name="Líneas de acción" sheetId="5" state="hidden" r:id="rId1"/>
@@ -1934,7 +1934,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="68">
+  <cellXfs count="69">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
@@ -2087,6 +2087,12 @@
     <xf numFmtId="0" fontId="1" fillId="11" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="12" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="13" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -2099,10 +2105,7 @@
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="12" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="13" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="10" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -3276,10 +3279,10 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:41" ht="39" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="C1" s="62" t="s">
+      <c r="C1" s="64" t="s">
         <v>368</v>
       </c>
-      <c r="D1" s="62"/>
+      <c r="D1" s="64"/>
       <c r="L1" s="16" t="s">
         <v>132</v>
       </c>
@@ -3435,7 +3438,7 @@
       </c>
     </row>
     <row r="3" spans="1:41" ht="90" x14ac:dyDescent="0.35">
-      <c r="B3" s="66" t="s">
+      <c r="B3" s="62" t="s">
         <v>66</v>
       </c>
       <c r="C3" s="21" t="s">
@@ -3795,7 +3798,7 @@
       </c>
     </row>
     <row r="6" spans="1:41" ht="150" x14ac:dyDescent="0.35">
-      <c r="B6" s="21" t="s">
+      <c r="B6" s="62" t="s">
         <v>18</v>
       </c>
       <c r="C6" s="21" t="s">
@@ -3915,7 +3918,7 @@
       </c>
     </row>
     <row r="7" spans="1:41" ht="150" x14ac:dyDescent="0.35">
-      <c r="B7" s="21" t="s">
+      <c r="B7" s="62" t="s">
         <v>18</v>
       </c>
       <c r="C7" s="21" t="s">
@@ -4035,7 +4038,7 @@
       </c>
     </row>
     <row r="8" spans="1:41" ht="140" x14ac:dyDescent="0.35">
-      <c r="B8" s="66" t="s">
+      <c r="B8" s="62" t="s">
         <v>55</v>
       </c>
       <c r="C8" s="21" t="s">
@@ -4155,7 +4158,7 @@
       </c>
     </row>
     <row r="9" spans="1:41" ht="140" x14ac:dyDescent="0.35">
-      <c r="B9" s="66" t="s">
+      <c r="B9" s="62" t="s">
         <v>57</v>
       </c>
       <c r="C9" s="21" t="s">
@@ -4275,7 +4278,7 @@
       </c>
     </row>
     <row r="10" spans="1:41" ht="70" x14ac:dyDescent="0.35">
-      <c r="B10" s="21" t="s">
+      <c r="B10" s="62" t="s">
         <v>5</v>
       </c>
       <c r="C10" s="21" t="s">
@@ -4747,7 +4750,7 @@
       </c>
     </row>
     <row r="14" spans="1:41" ht="140" x14ac:dyDescent="0.35">
-      <c r="B14" s="66" t="s">
+      <c r="B14" s="62" t="s">
         <v>60</v>
       </c>
       <c r="C14" s="21" t="s">
@@ -4867,7 +4870,7 @@
       </c>
     </row>
     <row r="15" spans="1:41" ht="140" x14ac:dyDescent="0.35">
-      <c r="B15" s="67" t="s">
+      <c r="B15" s="68" t="s">
         <v>59</v>
       </c>
       <c r="C15" s="21" t="s">
@@ -4988,7 +4991,7 @@
     </row>
     <row r="16" spans="1:41" ht="89" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A16" s="57"/>
-      <c r="B16" s="66" t="s">
+      <c r="B16" s="62" t="s">
         <v>64</v>
       </c>
       <c r="C16" s="21" t="s">
@@ -5109,7 +5112,7 @@
     </row>
     <row r="17" spans="1:41" ht="70" x14ac:dyDescent="0.35">
       <c r="A17" s="58"/>
-      <c r="B17" s="67" t="s">
+      <c r="B17" s="63" t="s">
         <v>62</v>
       </c>
       <c r="C17" s="21" t="s">
@@ -5472,7 +5475,7 @@
     </row>
     <row r="20" spans="1:41" ht="100" x14ac:dyDescent="0.35">
       <c r="A20" s="22"/>
-      <c r="B20" s="21" t="s">
+      <c r="B20" s="68" t="s">
         <v>65</v>
       </c>
       <c r="C20" s="21" t="s">
@@ -5593,7 +5596,7 @@
     </row>
     <row r="21" spans="1:41" ht="140" x14ac:dyDescent="0.35">
       <c r="A21" s="22"/>
-      <c r="B21" s="21" t="s">
+      <c r="B21" s="68" t="s">
         <v>42</v>
       </c>
       <c r="C21" s="21" t="s">
@@ -5834,7 +5837,7 @@
       </c>
     </row>
     <row r="23" spans="1:41" ht="70" x14ac:dyDescent="0.35">
-      <c r="B23" s="21" t="s">
+      <c r="B23" s="68" t="s">
         <v>33</v>
       </c>
       <c r="C23" s="21" t="s">
@@ -13275,13 +13278,13 @@
       <c r="D1" s="26" t="s">
         <v>16</v>
       </c>
-      <c r="F1" s="64" t="s">
+      <c r="F1" s="66" t="s">
         <v>242</v>
       </c>
-      <c r="G1" s="64"/>
-      <c r="H1" s="64"/>
-      <c r="I1" s="64"/>
-      <c r="J1" s="64"/>
+      <c r="G1" s="66"/>
+      <c r="H1" s="66"/>
+      <c r="I1" s="66"/>
+      <c r="J1" s="66"/>
     </row>
     <row r="2" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B2" s="39" t="s">
@@ -13293,11 +13296,11 @@
       <c r="D2" s="26" t="s">
         <v>24</v>
       </c>
-      <c r="F2" s="64"/>
-      <c r="G2" s="64"/>
-      <c r="H2" s="64"/>
-      <c r="I2" s="64"/>
-      <c r="J2" s="64"/>
+      <c r="F2" s="66"/>
+      <c r="G2" s="66"/>
+      <c r="H2" s="66"/>
+      <c r="I2" s="66"/>
+      <c r="J2" s="66"/>
     </row>
     <row r="3" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B3" s="39" t="s">
@@ -13309,11 +13312,11 @@
       <c r="D3" s="26" t="s">
         <v>16</v>
       </c>
-      <c r="F3" s="64"/>
-      <c r="G3" s="64"/>
-      <c r="H3" s="64"/>
-      <c r="I3" s="64"/>
-      <c r="J3" s="64"/>
+      <c r="F3" s="66"/>
+      <c r="G3" s="66"/>
+      <c r="H3" s="66"/>
+      <c r="I3" s="66"/>
+      <c r="J3" s="66"/>
     </row>
     <row r="4" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B4" s="39" t="s">
@@ -13325,11 +13328,11 @@
       <c r="D4" s="26" t="s">
         <v>21</v>
       </c>
-      <c r="F4" s="64"/>
-      <c r="G4" s="64"/>
-      <c r="H4" s="64"/>
-      <c r="I4" s="64"/>
-      <c r="J4" s="64"/>
+      <c r="F4" s="66"/>
+      <c r="G4" s="66"/>
+      <c r="H4" s="66"/>
+      <c r="I4" s="66"/>
+      <c r="J4" s="66"/>
     </row>
     <row r="5" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B5" s="39" t="s">
@@ -13341,11 +13344,11 @@
       <c r="D5" s="26" t="s">
         <v>21</v>
       </c>
-      <c r="F5" s="64"/>
-      <c r="G5" s="64"/>
-      <c r="H5" s="64"/>
-      <c r="I5" s="64"/>
-      <c r="J5" s="64"/>
+      <c r="F5" s="66"/>
+      <c r="G5" s="66"/>
+      <c r="H5" s="66"/>
+      <c r="I5" s="66"/>
+      <c r="J5" s="66"/>
     </row>
     <row r="6" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B6" s="39" t="s">
@@ -13357,11 +13360,11 @@
       <c r="D6" s="26" t="s">
         <v>21</v>
       </c>
-      <c r="F6" s="64"/>
-      <c r="G6" s="64"/>
-      <c r="H6" s="64"/>
-      <c r="I6" s="64"/>
-      <c r="J6" s="64"/>
+      <c r="F6" s="66"/>
+      <c r="G6" s="66"/>
+      <c r="H6" s="66"/>
+      <c r="I6" s="66"/>
+      <c r="J6" s="66"/>
     </row>
     <row r="7" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B7" s="39" t="s">
@@ -13373,11 +13376,11 @@
       <c r="D7" s="26" t="s">
         <v>24</v>
       </c>
-      <c r="F7" s="64"/>
-      <c r="G7" s="64"/>
-      <c r="H7" s="64"/>
-      <c r="I7" s="64"/>
-      <c r="J7" s="64"/>
+      <c r="F7" s="66"/>
+      <c r="G7" s="66"/>
+      <c r="H7" s="66"/>
+      <c r="I7" s="66"/>
+      <c r="J7" s="66"/>
     </row>
     <row r="9" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B9" s="37" t="s">
@@ -13560,13 +13563,13 @@
       <c r="D27" s="26" t="s">
         <v>21</v>
       </c>
-      <c r="F27" s="65" t="s">
+      <c r="F27" s="67" t="s">
         <v>253</v>
       </c>
-      <c r="G27" s="65"/>
-      <c r="H27" s="65"/>
-      <c r="I27" s="65"/>
-      <c r="J27" s="65"/>
+      <c r="G27" s="67"/>
+      <c r="H27" s="67"/>
+      <c r="I27" s="67"/>
+      <c r="J27" s="67"/>
     </row>
     <row r="28" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B28" s="39" t="s">
@@ -13578,13 +13581,13 @@
       <c r="D28" s="26" t="s">
         <v>21</v>
       </c>
-      <c r="F28" s="65" t="s">
+      <c r="F28" s="67" t="s">
         <v>254</v>
       </c>
-      <c r="G28" s="65"/>
-      <c r="H28" s="65"/>
-      <c r="I28" s="65"/>
-      <c r="J28" s="65"/>
+      <c r="G28" s="67"/>
+      <c r="H28" s="67"/>
+      <c r="I28" s="67"/>
+      <c r="J28" s="67"/>
     </row>
     <row r="29" spans="2:10" ht="31" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B29" s="39" t="s">
@@ -13596,13 +13599,13 @@
       <c r="D29" s="26" t="s">
         <v>21</v>
       </c>
-      <c r="F29" s="63" t="s">
+      <c r="F29" s="65" t="s">
         <v>255</v>
       </c>
-      <c r="G29" s="63"/>
-      <c r="H29" s="63"/>
-      <c r="I29" s="63"/>
-      <c r="J29" s="63"/>
+      <c r="G29" s="65"/>
+      <c r="H29" s="65"/>
+      <c r="I29" s="65"/>
+      <c r="J29" s="65"/>
     </row>
     <row r="30" spans="2:10" ht="29.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B30" s="39" t="s">
@@ -13614,13 +13617,13 @@
       <c r="D30" s="26" t="s">
         <v>21</v>
       </c>
-      <c r="F30" s="63" t="s">
+      <c r="F30" s="65" t="s">
         <v>256</v>
       </c>
-      <c r="G30" s="63"/>
-      <c r="H30" s="63"/>
-      <c r="I30" s="63"/>
-      <c r="J30" s="63"/>
+      <c r="G30" s="65"/>
+      <c r="H30" s="65"/>
+      <c r="I30" s="65"/>
+      <c r="J30" s="65"/>
     </row>
     <row r="31" spans="2:10" ht="20" x14ac:dyDescent="0.35">
       <c r="B31" s="39" t="s">
@@ -13632,13 +13635,13 @@
       <c r="D31" s="26" t="s">
         <v>24</v>
       </c>
-      <c r="F31" s="63" t="s">
+      <c r="F31" s="65" t="s">
         <v>257</v>
       </c>
-      <c r="G31" s="63"/>
-      <c r="H31" s="63"/>
-      <c r="I31" s="63"/>
-      <c r="J31" s="63"/>
+      <c r="G31" s="65"/>
+      <c r="H31" s="65"/>
+      <c r="I31" s="65"/>
+      <c r="J31" s="65"/>
     </row>
     <row r="32" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B32" s="45"/>
@@ -14306,6 +14309,15 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x010100FC102D493A39B2419B6834134514A928" ma:contentTypeVersion="15" ma:contentTypeDescription="Crear nuevo documento." ma:contentTypeScope="" ma:versionID="d01e0109bf6dea2fbada290e24a0079e">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="882a8f42-f1f9-4ba8-a024-a9506b2a3f1b" xmlns:ns3="f3dc767a-0b06-462e-8350-fa01f76d53d6" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="5475975345732b2580ec347e706b0322" ns2:_="" ns3:_="">
     <xsd:import namespace="882a8f42-f1f9-4ba8-a024-a9506b2a3f1b"/>
@@ -14542,15 +14554,6 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
@@ -14564,6 +14567,14 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F2F9F198-AAB3-4743-83B7-70E545DDE86B}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E69E7B37-066B-460B-9CC0-96F997D136F5}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -14578,14 +14589,6 @@
     <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
     <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F2F9F198-AAB3-4743-83B7-70E545DDE86B}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>

--- a/SAT-SDMA-7 Perfiles.xlsx
+++ b/SAT-SDMA-7 Perfiles.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\raquell.martinez\Documents\AISolutions\analyzeCV\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{48270E28-314C-46A5-AFAA-978C0A2F2BF4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EC002E76-3C11-4E71-842C-50B488CC06CA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="840" windowWidth="19360" windowHeight="10480" firstSheet="2" activeTab="2" xr2:uid="{D74C329F-941D-40F9-B295-21746B646AD6}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="2" activeTab="2" xr2:uid="{D74C329F-941D-40F9-B295-21746B646AD6}"/>
   </bookViews>
   <sheets>
     <sheet name="Líneas de acción" sheetId="5" state="hidden" r:id="rId1"/>
@@ -196,7 +196,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3331" uniqueCount="369">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3331" uniqueCount="370">
   <si>
     <t>Director de proyecto</t>
   </si>
@@ -412,12 +412,6 @@
   </si>
   <si>
     <t>Al menos 3 años en desarrollo de soluciones de BI, en servicios y aplicaciones web (frontend y backend), dashboards interactivos, tableros, informes automáticos, reportes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Al menos 5 años de experiencia centro de desarrollo de software. 
-Dominio de Tecnologías del AR y/o tecnologías open source
-Adicional: Al menos 1 recurso con experiencia en mantenimiento de aplicaciones en Sterling (soluciones de IBM)
-</t>
   </si>
   <si>
     <t>Al menos 2 años de experiencia en desarrollo de servicios y aplicaciones web (Frontend y Backend), dashboards, interactivos, tableros, informes automáticos, reportes.</t>
@@ -458,10 +452,6 @@
   <si>
     <t>Crear los sistemas (paquetes de software), implementarlos y hacer una puesta punto para que puedan ser funcionales, todo ello a través de lenguajes de programación.
 Habilidades en; Bases de Datos relacionales y no relacionales, y técnicas de diseño para el Modelado de Datos., Desarrollo, mantenimiento y soporte de procesos ETL (Extract, Transform, Load)., Manejo de herramientas de BI (Databricks, Fabric).</t>
-  </si>
-  <si>
-    <t>Validar que cada componente interactúe de forma sistémica en todas las iteraciones de un proyecto, para lograr congruencia al flujo de negocio y de información (proceso funcional). Identifica dependencias, duplicidades. Proponer soluciones a las necesidades de manera integrada.
-Habilidades en; Conocimiento de las plataformas de la AR, Resolución de problemas técnicos, Evaluación y optimización del rendimiento del sistema eligiendo las tecnologías más adecuadas</t>
   </si>
   <si>
     <t>Mantener y dar soporte a los aplicativos dominando varios lenguajes de programación.
@@ -1624,6 +1614,19 @@
     <t>RA1 - Requerido Alguno
 R1 - Requerido
 D1- Deseable</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Al menos 5 años de experiencia centro de desarrollo de software. 
+Dominio de Tecnologías de la Arquitectura de Referencia (AR) y/o tecnologías open source
+Adicional: Al menos 1 recurso con experiencia en mantenimiento de aplicaciones en Sterling (soluciones de IBM)
+</t>
+  </si>
+  <si>
+    <t>Validar que cada componente interactúe de forma sistémica en todas las iteraciones de un proyecto, para lograr congruencia al flujo de negocio y de información (proceso funcional). Identifica dependencias, duplicidades. Proponer soluciones a las necesidades de manera integrada.
+Habilidades en; Conocimiento de las plataformas de la Arquitectura de Referencia (AR), Resolución de problemas técnicos, Evaluación y optimización del rendimiento del sistema eligiendo las tecnologías más adecuadas</t>
+  </si>
+  <si>
+    <t>Creación+D22</t>
   </si>
 </sst>
 </file>
@@ -1785,7 +1788,7 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="14">
+  <fills count="13">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1854,13 +1857,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
+        <fgColor rgb="FF00B0F0"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1934,7 +1931,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="69">
+  <cellXfs count="67">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
@@ -2087,12 +2084,6 @@
     <xf numFmtId="0" fontId="1" fillId="11" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="12" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="13" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -2105,7 +2096,7 @@
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="10" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="12" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -2455,97 +2446,97 @@
   <sheetData>
     <row r="2" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B2" s="5" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
     </row>
     <row r="3" spans="2:4" x14ac:dyDescent="0.35">
       <c r="C3" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
     </row>
     <row r="4" spans="2:4" x14ac:dyDescent="0.35">
       <c r="D4" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
     </row>
     <row r="5" spans="2:4" x14ac:dyDescent="0.35">
       <c r="C5" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
     </row>
     <row r="6" spans="2:4" x14ac:dyDescent="0.35">
       <c r="C6" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
     </row>
     <row r="7" spans="2:4" x14ac:dyDescent="0.35">
       <c r="D7" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
     </row>
     <row r="8" spans="2:4" x14ac:dyDescent="0.35">
       <c r="C8" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
     </row>
     <row r="10" spans="2:4" x14ac:dyDescent="0.35">
       <c r="C10" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
     </row>
     <row r="11" spans="2:4" x14ac:dyDescent="0.35">
       <c r="D11" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
     </row>
     <row r="12" spans="2:4" x14ac:dyDescent="0.35">
       <c r="C12" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
     </row>
     <row r="13" spans="2:4" x14ac:dyDescent="0.35">
       <c r="D13" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
     </row>
     <row r="14" spans="2:4" x14ac:dyDescent="0.35">
       <c r="C14" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
     </row>
     <row r="15" spans="2:4" x14ac:dyDescent="0.35">
       <c r="D15" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
     </row>
     <row r="16" spans="2:4" x14ac:dyDescent="0.35">
       <c r="C16" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
     </row>
     <row r="17" spans="3:4" x14ac:dyDescent="0.35">
       <c r="D17" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
     </row>
     <row r="18" spans="3:4" x14ac:dyDescent="0.35">
       <c r="C18" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
     </row>
     <row r="19" spans="3:4" x14ac:dyDescent="0.35">
       <c r="D19" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
     </row>
     <row r="20" spans="3:4" x14ac:dyDescent="0.35">
       <c r="C20" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
     </row>
     <row r="21" spans="3:4" x14ac:dyDescent="0.35">
       <c r="C21" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
     </row>
   </sheetData>
@@ -2570,12 +2561,12 @@
   <sheetData>
     <row r="1" spans="2:17" x14ac:dyDescent="0.35">
       <c r="K1" s="40" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
     </row>
     <row r="2" spans="2:17" x14ac:dyDescent="0.35">
       <c r="B2" s="8" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="C2" s="6"/>
       <c r="D2" s="6"/>
@@ -2590,7 +2581,7 @@
     </row>
     <row r="3" spans="2:17" x14ac:dyDescent="0.35">
       <c r="C3" s="6" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="D3" s="6"/>
       <c r="E3" s="6"/>
@@ -2606,7 +2597,7 @@
     </row>
     <row r="4" spans="2:17" x14ac:dyDescent="0.35">
       <c r="C4" s="7" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="D4" s="7"/>
       <c r="E4" s="7"/>
@@ -2642,7 +2633,7 @@
     </row>
     <row r="6" spans="2:17" x14ac:dyDescent="0.35">
       <c r="C6" s="7" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="D6" s="7"/>
       <c r="E6" s="7"/>
@@ -2658,7 +2649,7 @@
     </row>
     <row r="7" spans="2:17" x14ac:dyDescent="0.35">
       <c r="C7" s="7" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="D7" s="7"/>
       <c r="E7" s="7"/>
@@ -2674,7 +2665,7 @@
     </row>
     <row r="9" spans="2:17" x14ac:dyDescent="0.35">
       <c r="B9" s="5" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="C9" s="5"/>
     </row>
@@ -2687,11 +2678,11 @@
         <v>1</v>
       </c>
       <c r="F10" s="7" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="G10" s="7"/>
       <c r="H10" s="7" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="K10" s="29" t="s">
         <v>17</v>
@@ -2706,13 +2697,13 @@
         <v>1</v>
       </c>
       <c r="F11" s="7" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="G11" s="7">
         <v>5</v>
       </c>
       <c r="H11" s="7" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="K11" s="29" t="s">
         <v>18</v>
@@ -2720,20 +2711,20 @@
     </row>
     <row r="12" spans="2:17" x14ac:dyDescent="0.35">
       <c r="C12" s="7" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="D12" s="7"/>
       <c r="E12" s="7">
         <v>1</v>
       </c>
       <c r="F12" s="7" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="G12" s="7">
         <v>30</v>
       </c>
       <c r="H12" s="7" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="K12" s="29" t="s">
         <v>19</v>
@@ -2741,15 +2732,15 @@
     </row>
     <row r="13" spans="2:17" x14ac:dyDescent="0.35">
       <c r="I13" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="J13" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
     </row>
     <row r="14" spans="2:17" x14ac:dyDescent="0.35">
       <c r="B14" s="8" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="C14" s="6"/>
       <c r="D14" s="6"/>
@@ -2775,7 +2766,7 @@
         <v>1</v>
       </c>
       <c r="F15" s="6" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="G15" s="6"/>
       <c r="H15" s="6" t="s">
@@ -2788,25 +2779,25 @@
         <v>1</v>
       </c>
       <c r="L15" s="29" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
     </row>
     <row r="16" spans="2:17" x14ac:dyDescent="0.35">
       <c r="C16" s="7" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="D16" s="7"/>
       <c r="E16" s="7">
         <v>1</v>
       </c>
       <c r="F16" s="7" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="G16" s="7">
         <v>5</v>
       </c>
       <c r="H16" s="7" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="I16" s="10">
         <v>1</v>
@@ -2815,27 +2806,27 @@
         <v>2</v>
       </c>
       <c r="L16" s="29" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
     </row>
     <row r="17" spans="2:18" x14ac:dyDescent="0.35">
       <c r="C17" s="7" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="D17" s="7" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="E17" s="7">
         <v>1</v>
       </c>
       <c r="F17" s="7" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="G17" s="7">
         <v>5</v>
       </c>
       <c r="H17" s="7" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="I17" s="10">
         <v>1</v>
@@ -2849,22 +2840,22 @@
     </row>
     <row r="18" spans="2:18" x14ac:dyDescent="0.35">
       <c r="C18" s="7" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="D18" s="7" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="E18" s="7">
         <v>2</v>
       </c>
       <c r="F18" s="7" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="G18" s="7">
         <v>1</v>
       </c>
       <c r="H18" s="7" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="I18" s="10">
         <v>8</v>
@@ -2878,22 +2869,22 @@
     </row>
     <row r="19" spans="2:18" x14ac:dyDescent="0.35">
       <c r="C19" s="7" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="D19" s="7" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="E19" s="7">
         <v>1</v>
       </c>
       <c r="F19" s="7" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="G19" s="7">
         <v>5</v>
       </c>
       <c r="H19" s="7" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="I19" s="10">
         <v>1</v>
@@ -2907,22 +2898,22 @@
     </row>
     <row r="20" spans="2:18" x14ac:dyDescent="0.35">
       <c r="C20" s="7" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="D20" s="7" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="E20" s="7">
         <v>1</v>
       </c>
       <c r="F20" s="7" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="G20" s="7">
         <v>5</v>
       </c>
       <c r="H20" s="7" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="I20" s="10">
         <v>1</v>
@@ -2936,22 +2927,22 @@
     </row>
     <row r="21" spans="2:18" x14ac:dyDescent="0.35">
       <c r="C21" s="7" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="D21" s="7" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="E21" s="7">
         <v>1</v>
       </c>
       <c r="F21" s="7" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="G21" s="7">
         <v>5</v>
       </c>
       <c r="H21" s="7" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="I21" s="10">
         <v>1</v>
@@ -2960,28 +2951,28 @@
         <v>2</v>
       </c>
       <c r="L21" s="29" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="R21" s="29"/>
     </row>
     <row r="22" spans="2:18" x14ac:dyDescent="0.35">
       <c r="C22" s="7" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="D22" s="7" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="E22" s="7">
         <v>4</v>
       </c>
       <c r="F22" s="7" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="G22" s="7">
         <v>1</v>
       </c>
       <c r="H22" s="7" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="I22" s="10">
         <v>16</v>
@@ -2990,29 +2981,29 @@
         <v>40</v>
       </c>
       <c r="L22" s="29" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="Q22" s="13" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="R22" s="29"/>
     </row>
     <row r="23" spans="2:18" x14ac:dyDescent="0.35">
       <c r="C23" s="7" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="D23" s="7"/>
       <c r="E23" s="7">
         <v>1</v>
       </c>
       <c r="F23" s="7" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="G23" s="7">
         <v>2</v>
       </c>
       <c r="H23" s="7" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="I23" s="10">
         <v>2</v>
@@ -3026,19 +3017,19 @@
     </row>
     <row r="24" spans="2:18" x14ac:dyDescent="0.35">
       <c r="C24" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="E24">
         <v>1</v>
       </c>
       <c r="F24" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="G24">
         <v>2</v>
       </c>
       <c r="H24" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="I24" s="44">
         <v>2</v>
@@ -3057,15 +3048,15 @@
     </row>
     <row r="26" spans="2:18" x14ac:dyDescent="0.35">
       <c r="I26" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="O26" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
     </row>
     <row r="27" spans="2:18" x14ac:dyDescent="0.35">
       <c r="B27" s="8" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="C27" s="6"/>
       <c r="D27" s="6"/>
@@ -3101,20 +3092,20 @@
     </row>
     <row r="28" spans="2:18" x14ac:dyDescent="0.35">
       <c r="C28" s="6" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="D28" s="6"/>
       <c r="E28" s="6">
         <v>1</v>
       </c>
       <c r="F28" s="6" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="G28" s="6">
         <v>30</v>
       </c>
       <c r="H28" s="6" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="I28" s="9">
         <v>1</v>
@@ -3146,20 +3137,20 @@
     </row>
     <row r="29" spans="2:18" x14ac:dyDescent="0.35">
       <c r="C29" s="7" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="D29" s="7"/>
       <c r="E29" s="7">
         <v>1</v>
       </c>
       <c r="F29" s="7" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="G29" s="7">
         <v>10</v>
       </c>
       <c r="H29" s="7" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="I29" s="10">
         <v>2</v>
@@ -3192,20 +3183,20 @@
     </row>
     <row r="30" spans="2:18" x14ac:dyDescent="0.35">
       <c r="C30" s="7" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="D30" s="7"/>
       <c r="E30" s="7">
         <v>1</v>
       </c>
       <c r="F30" s="7" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="G30" s="7">
         <v>10</v>
       </c>
       <c r="H30" s="7" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="I30" s="10">
         <v>1</v>
@@ -3238,7 +3229,7 @@
     </row>
     <row r="32" spans="2:18" x14ac:dyDescent="0.35">
       <c r="C32" s="13" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
     </row>
   </sheetData>
@@ -3279,12 +3270,12 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:41" ht="39" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="C1" s="64" t="s">
-        <v>368</v>
-      </c>
-      <c r="D1" s="64"/>
+      <c r="C1" s="62" t="s">
+        <v>366</v>
+      </c>
+      <c r="D1" s="62"/>
       <c r="L1" s="16" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="M1" s="16"/>
       <c r="N1" s="16"/>
@@ -3304,7 +3295,7 @@
       <c r="AB1" s="16"/>
       <c r="AC1" s="16"/>
       <c r="AE1" s="17" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="AF1" s="18"/>
       <c r="AG1" s="18"/>
@@ -3322,7 +3313,7 @@
         <v>2</v>
       </c>
       <c r="C2" s="30" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="D2" s="30" t="s">
         <v>27</v>
@@ -3343,16 +3334,16 @@
         <v>26</v>
       </c>
       <c r="J2" s="35" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="K2" s="30" t="s">
-        <v>367</v>
+        <v>365</v>
       </c>
       <c r="L2" s="20" t="s">
         <v>15</v>
       </c>
       <c r="M2" s="20" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="N2" s="20" t="s">
         <v>14</v>
@@ -3364,16 +3355,16 @@
         <v>38</v>
       </c>
       <c r="Q2" s="20" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="R2" s="32" t="s">
         <v>40</v>
       </c>
       <c r="S2" s="32" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="T2" s="38" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="U2" s="20" t="s">
         <v>44</v>
@@ -3394,32 +3385,32 @@
         <v>54</v>
       </c>
       <c r="AA2" s="20" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="AB2" s="20" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="AC2" s="20" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="AD2" s="33"/>
       <c r="AE2" s="20" t="s">
         <v>38</v>
       </c>
       <c r="AF2" s="32" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="AG2" s="20" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="AH2" s="20" t="s">
         <v>39</v>
       </c>
       <c r="AI2" s="20" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="AJ2" s="32" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="AK2" s="20" t="s">
         <v>49</v>
@@ -3431,18 +3422,18 @@
         <v>51</v>
       </c>
       <c r="AN2" s="38" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="AO2" s="34" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
     </row>
     <row r="3" spans="1:41" ht="90" x14ac:dyDescent="0.35">
-      <c r="B3" s="62" t="s">
+      <c r="B3" s="66" t="s">
         <v>66</v>
       </c>
       <c r="C3" s="21" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="D3" s="21" t="s">
         <v>21</v>
@@ -3451,13 +3442,13 @@
         <v>5</v>
       </c>
       <c r="F3" s="21" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="G3" s="21" t="s">
         <v>1</v>
       </c>
       <c r="H3" s="22" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="I3" s="22" t="s">
         <v>67</v>
@@ -3466,7 +3457,7 @@
         <v>2</v>
       </c>
       <c r="K3" s="36" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="L3" s="24" t="s">
         <v>11</v>
@@ -3487,7 +3478,7 @@
         <v>11</v>
       </c>
       <c r="R3" s="42" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="S3" s="24" t="s">
         <v>11</v>
@@ -3517,10 +3508,10 @@
         <v>11</v>
       </c>
       <c r="AB3" s="42" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="AC3" s="42" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="AD3" s="25"/>
       <c r="AE3" s="26" t="s">
@@ -3530,7 +3521,7 @@
         <v>11</v>
       </c>
       <c r="AG3" s="41" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="AH3" s="26" t="s">
         <v>11</v>
@@ -3577,16 +3568,16 @@
         <v>1</v>
       </c>
       <c r="H4" s="22" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="I4" s="36" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="J4" s="21">
         <v>5</v>
       </c>
       <c r="K4" s="36" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="L4" s="24" t="s">
         <v>11</v>
@@ -3613,7 +3604,7 @@
         <v>11</v>
       </c>
       <c r="T4" s="43" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="U4" s="24" t="s">
         <v>11</v>
@@ -3671,7 +3662,7 @@
         <v>11</v>
       </c>
       <c r="AN4" s="41" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="AO4" s="26" t="s">
         <v>11</v>
@@ -3697,16 +3688,16 @@
         <v>1</v>
       </c>
       <c r="H5" s="22" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="I5" s="36" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="J5" s="21">
         <v>5</v>
       </c>
       <c r="K5" s="36" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="L5" s="24" t="s">
         <v>11</v>
@@ -3733,7 +3724,7 @@
         <v>11</v>
       </c>
       <c r="T5" s="43" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="U5" s="24" t="s">
         <v>11</v>
@@ -3791,14 +3782,14 @@
         <v>11</v>
       </c>
       <c r="AN5" s="41" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="AO5" s="26" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="6" spans="1:41" ht="150" x14ac:dyDescent="0.35">
-      <c r="B6" s="62" t="s">
+      <c r="B6" s="66" t="s">
         <v>18</v>
       </c>
       <c r="C6" s="21" t="s">
@@ -3817,16 +3808,16 @@
         <v>1</v>
       </c>
       <c r="H6" s="22" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="I6" s="22" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="J6" s="21">
         <v>5</v>
       </c>
       <c r="K6" s="36" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="L6" s="23" t="s">
         <v>11</v>
@@ -3853,7 +3844,7 @@
         <v>11</v>
       </c>
       <c r="T6" s="43" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="U6" s="24" t="s">
         <v>11</v>
@@ -3890,10 +3881,10 @@
         <v>11</v>
       </c>
       <c r="AG6" s="41" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="AH6" s="41" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="AI6" s="26" t="s">
         <v>11</v>
@@ -3918,7 +3909,7 @@
       </c>
     </row>
     <row r="7" spans="1:41" ht="150" x14ac:dyDescent="0.35">
-      <c r="B7" s="62" t="s">
+      <c r="B7" s="66" t="s">
         <v>18</v>
       </c>
       <c r="C7" s="21" t="s">
@@ -3937,16 +3928,16 @@
         <v>1</v>
       </c>
       <c r="H7" s="22" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="I7" s="22" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="J7" s="21">
         <v>5</v>
       </c>
       <c r="K7" s="36" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="L7" s="23" t="s">
         <v>11</v>
@@ -3973,7 +3964,7 @@
         <v>11</v>
       </c>
       <c r="T7" s="43" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="U7" s="24" t="s">
         <v>11</v>
@@ -4010,10 +4001,10 @@
         <v>11</v>
       </c>
       <c r="AG7" s="41" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="AH7" s="41" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="AI7" s="26" t="s">
         <v>11</v>
@@ -4038,11 +4029,11 @@
       </c>
     </row>
     <row r="8" spans="1:41" ht="140" x14ac:dyDescent="0.35">
-      <c r="B8" s="62" t="s">
+      <c r="B8" s="66" t="s">
         <v>55</v>
       </c>
       <c r="C8" s="21" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="D8" s="21" t="s">
         <v>21</v>
@@ -4051,13 +4042,13 @@
         <v>2</v>
       </c>
       <c r="F8" s="21" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="G8" s="21" t="s">
         <v>1</v>
       </c>
       <c r="H8" s="22" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="I8" s="22" t="s">
         <v>56</v>
@@ -4066,7 +4057,7 @@
         <v>5</v>
       </c>
       <c r="K8" s="36" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="L8" s="23" t="s">
         <v>11</v>
@@ -4093,7 +4084,7 @@
         <v>11</v>
       </c>
       <c r="T8" s="43" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="U8" s="24" t="s">
         <v>11</v>
@@ -4151,18 +4142,18 @@
         <v>11</v>
       </c>
       <c r="AN8" s="41" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="AO8" s="26" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="9" spans="1:41" ht="140" x14ac:dyDescent="0.35">
-      <c r="B9" s="62" t="s">
+      <c r="B9" s="66" t="s">
         <v>57</v>
       </c>
       <c r="C9" s="21" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="D9" s="21" t="s">
         <v>21</v>
@@ -4171,13 +4162,13 @@
         <v>2</v>
       </c>
       <c r="F9" s="21" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="G9" s="21" t="s">
         <v>1</v>
       </c>
       <c r="H9" s="22" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="I9" s="22" t="s">
         <v>58</v>
@@ -4186,7 +4177,7 @@
         <v>2</v>
       </c>
       <c r="K9" s="36" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="L9" s="23" t="s">
         <v>11</v>
@@ -4213,7 +4204,7 @@
         <v>11</v>
       </c>
       <c r="T9" s="43" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="U9" s="24" t="s">
         <v>11</v>
@@ -4271,21 +4262,21 @@
         <v>11</v>
       </c>
       <c r="AN9" s="41" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="AO9" s="26" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="10" spans="1:41" ht="70" x14ac:dyDescent="0.35">
-      <c r="B10" s="62" t="s">
+      <c r="B10" s="66" t="s">
         <v>5</v>
       </c>
       <c r="C10" s="21" t="s">
         <v>30</v>
       </c>
       <c r="D10" s="21" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="E10" s="21">
         <v>2</v>
@@ -4298,19 +4289,19 @@
         <v>10</v>
       </c>
       <c r="I10" s="22" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="J10" s="21">
         <v>5</v>
       </c>
       <c r="K10" s="36" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="L10" s="43" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="M10" s="43" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="N10" s="23" t="s">
         <v>11</v>
@@ -4362,19 +4353,19 @@
       </c>
       <c r="AD10" s="25"/>
       <c r="AE10" s="41" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="AF10" s="27" t="s">
         <v>11</v>
       </c>
       <c r="AG10" s="41" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="AH10" s="41" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="AI10" s="41" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="AJ10" s="26" t="s">
         <v>11</v>
@@ -4396,14 +4387,14 @@
       </c>
     </row>
     <row r="11" spans="1:41" ht="70" x14ac:dyDescent="0.35">
-      <c r="B11" s="21" t="s">
+      <c r="B11" s="66" t="s">
         <v>6</v>
       </c>
       <c r="C11" s="21" t="s">
         <v>31</v>
       </c>
       <c r="D11" s="21" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="E11" s="21">
         <v>1</v>
@@ -4422,13 +4413,13 @@
         <v>5</v>
       </c>
       <c r="K11" s="36" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="L11" s="43" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="M11" s="43" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="N11" s="23" t="s">
         <v>11</v>
@@ -4489,7 +4480,7 @@
         <v>11</v>
       </c>
       <c r="AH11" s="41" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="AI11" s="26" t="s">
         <v>11</v>
@@ -4514,14 +4505,14 @@
       </c>
     </row>
     <row r="12" spans="1:41" ht="70" x14ac:dyDescent="0.35">
-      <c r="B12" s="21" t="s">
+      <c r="B12" s="66" t="s">
         <v>8</v>
       </c>
       <c r="C12" s="21" t="s">
         <v>30</v>
       </c>
       <c r="D12" s="21" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="E12" s="21">
         <v>1</v>
@@ -4540,7 +4531,7 @@
         <v>5</v>
       </c>
       <c r="K12" s="36" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="L12" s="23" t="s">
         <v>11</v>
@@ -4549,7 +4540,7 @@
         <v>11</v>
       </c>
       <c r="N12" s="43" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
       <c r="O12" s="23" t="s">
         <v>11</v>
@@ -4632,14 +4623,14 @@
       </c>
     </row>
     <row r="13" spans="1:41" ht="70" x14ac:dyDescent="0.35">
-      <c r="B13" s="21" t="s">
+      <c r="B13" s="66" t="s">
         <v>0</v>
       </c>
       <c r="C13" s="21" t="s">
         <v>32</v>
       </c>
       <c r="D13" s="21" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="E13" s="21">
         <v>1</v>
@@ -4658,10 +4649,10 @@
         <v>5</v>
       </c>
       <c r="K13" s="36" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="L13" s="43" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
       <c r="M13" s="23" t="s">
         <v>11</v>
@@ -4716,19 +4707,19 @@
       </c>
       <c r="AD13" s="25"/>
       <c r="AE13" s="41" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="AF13" s="41" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="AG13" s="41" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="AH13" s="41" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="AI13" s="41" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="AJ13" s="26" t="s">
         <v>11</v>
@@ -4750,11 +4741,11 @@
       </c>
     </row>
     <row r="14" spans="1:41" ht="140" x14ac:dyDescent="0.35">
-      <c r="B14" s="62" t="s">
+      <c r="B14" s="66" t="s">
         <v>60</v>
       </c>
       <c r="C14" s="21" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="D14" s="21" t="s">
         <v>21</v>
@@ -4763,13 +4754,13 @@
         <v>1</v>
       </c>
       <c r="F14" s="21" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="G14" s="21" t="s">
         <v>1</v>
       </c>
       <c r="H14" s="22" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="I14" s="22" t="s">
         <v>61</v>
@@ -4778,7 +4769,7 @@
         <v>5</v>
       </c>
       <c r="K14" s="36" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="L14" s="24" t="s">
         <v>11</v>
@@ -4799,13 +4790,13 @@
         <v>11</v>
       </c>
       <c r="R14" s="43" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="S14" s="24" t="s">
         <v>11</v>
       </c>
       <c r="T14" s="43" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="U14" s="24" t="s">
         <v>11</v>
@@ -4842,7 +4833,7 @@
         <v>11</v>
       </c>
       <c r="AG14" s="41" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="AH14" s="26" t="s">
         <v>11</v>
@@ -4863,14 +4854,14 @@
         <v>11</v>
       </c>
       <c r="AN14" s="41" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="AO14" s="26" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="15" spans="1:41" ht="140" x14ac:dyDescent="0.35">
-      <c r="B15" s="68" t="s">
+      <c r="B15" s="66" t="s">
         <v>59</v>
       </c>
       <c r="C15" s="21" t="s">
@@ -4883,22 +4874,22 @@
         <v>1</v>
       </c>
       <c r="F15" s="21" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="G15" s="21" t="s">
         <v>1</v>
       </c>
       <c r="H15" s="22" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="I15" s="22" t="s">
-        <v>71</v>
+        <v>367</v>
       </c>
       <c r="J15" s="21">
         <v>5</v>
       </c>
       <c r="K15" s="36" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="L15" s="24" t="s">
         <v>11</v>
@@ -4925,7 +4916,7 @@
         <v>11</v>
       </c>
       <c r="T15" s="43" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="U15" s="24" t="s">
         <v>11</v>
@@ -4962,7 +4953,7 @@
         <v>11</v>
       </c>
       <c r="AG15" s="41" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="AH15" s="26" t="s">
         <v>11</v>
@@ -4983,7 +4974,7 @@
         <v>11</v>
       </c>
       <c r="AN15" s="41" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="AO15" s="26" t="s">
         <v>11</v>
@@ -4991,11 +4982,11 @@
     </row>
     <row r="16" spans="1:41" ht="89" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A16" s="57"/>
-      <c r="B16" s="62" t="s">
+      <c r="B16" s="66" t="s">
         <v>64</v>
       </c>
       <c r="C16" s="21" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="D16" s="21" t="s">
         <v>21</v>
@@ -5004,22 +4995,22 @@
         <v>10</v>
       </c>
       <c r="F16" s="21" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="G16" s="21" t="s">
         <v>1</v>
       </c>
       <c r="H16" s="22" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="I16" s="22" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="J16" s="21">
         <v>2</v>
       </c>
       <c r="K16" s="36" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="L16" s="24" t="s">
         <v>11</v>
@@ -5046,7 +5037,7 @@
         <v>11</v>
       </c>
       <c r="T16" s="43" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="U16" s="24" t="s">
         <v>11</v>
@@ -5112,7 +5103,7 @@
     </row>
     <row r="17" spans="1:41" ht="70" x14ac:dyDescent="0.35">
       <c r="A17" s="58"/>
-      <c r="B17" s="63" t="s">
+      <c r="B17" s="66" t="s">
         <v>62</v>
       </c>
       <c r="C17" s="21" t="s">
@@ -5125,13 +5116,13 @@
         <v>30</v>
       </c>
       <c r="F17" s="21" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="G17" s="21" t="s">
         <v>1</v>
       </c>
       <c r="H17" s="22" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="I17" s="22" t="s">
         <v>63</v>
@@ -5140,7 +5131,7 @@
         <v>2</v>
       </c>
       <c r="K17" s="36" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="L17" s="24" t="s">
         <v>11</v>
@@ -5167,7 +5158,7 @@
         <v>11</v>
       </c>
       <c r="T17" s="43" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="U17" s="24" t="s">
         <v>11</v>
@@ -5246,22 +5237,22 @@
         <v>35</v>
       </c>
       <c r="F18" s="21" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="G18" s="21" t="s">
         <v>1</v>
       </c>
       <c r="H18" s="22" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="I18" s="22" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="J18" s="21">
         <v>3</v>
       </c>
       <c r="K18" s="36" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="L18" s="23" t="s">
         <v>11</v>
@@ -5288,7 +5279,7 @@
         <v>11</v>
       </c>
       <c r="T18" s="43" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="U18" s="23" t="s">
         <v>11</v>
@@ -5358,7 +5349,7 @@
         <v>69</v>
       </c>
       <c r="C19" s="21" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="D19" s="21" t="s">
         <v>24</v>
@@ -5367,13 +5358,13 @@
         <v>12</v>
       </c>
       <c r="F19" s="21" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="G19" s="21" t="s">
         <v>1</v>
       </c>
       <c r="H19" s="22" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="I19" s="22" t="s">
         <v>70</v>
@@ -5382,7 +5373,7 @@
         <v>3</v>
       </c>
       <c r="K19" s="36" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="L19" s="23" t="s">
         <v>11</v>
@@ -5409,7 +5400,7 @@
         <v>11</v>
       </c>
       <c r="T19" s="43" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="U19" s="24" t="s">
         <v>11</v>
@@ -5446,7 +5437,7 @@
         <v>11</v>
       </c>
       <c r="AG19" s="41" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="AH19" s="26" t="s">
         <v>11</v>
@@ -5475,7 +5466,7 @@
     </row>
     <row r="20" spans="1:41" ht="100" x14ac:dyDescent="0.35">
       <c r="A20" s="22"/>
-      <c r="B20" s="68" t="s">
+      <c r="B20" s="66" t="s">
         <v>65</v>
       </c>
       <c r="C20" s="21" t="s">
@@ -5488,22 +5479,22 @@
         <v>5</v>
       </c>
       <c r="F20" s="21" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="G20" s="21" t="s">
         <v>1</v>
       </c>
       <c r="H20" s="22" t="s">
-        <v>81</v>
+        <v>368</v>
       </c>
       <c r="I20" s="22" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="J20" s="21">
         <v>3</v>
       </c>
       <c r="K20" s="36" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="L20" s="24" t="s">
         <v>11</v>
@@ -5591,12 +5582,12 @@
         <v>11</v>
       </c>
       <c r="AO20" s="41" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
     </row>
     <row r="21" spans="1:41" ht="140" x14ac:dyDescent="0.35">
       <c r="A21" s="22"/>
-      <c r="B21" s="68" t="s">
+      <c r="B21" s="66" t="s">
         <v>42</v>
       </c>
       <c r="C21" s="21" t="s">
@@ -5609,13 +5600,13 @@
         <v>2</v>
       </c>
       <c r="F21" s="21" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="G21" s="21" t="s">
         <v>1</v>
       </c>
       <c r="H21" s="22" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="I21" s="22" t="s">
         <v>43</v>
@@ -5624,7 +5615,7 @@
         <v>5</v>
       </c>
       <c r="K21" s="36" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="L21" s="23" t="s">
         <v>11</v>
@@ -5654,19 +5645,19 @@
         <v>11</v>
       </c>
       <c r="U21" s="43" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="V21" s="43" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="W21" s="43" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="X21" s="43" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="Y21" s="43" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="Z21" s="23" t="s">
         <v>11</v>
@@ -5700,13 +5691,13 @@
         <v>11</v>
       </c>
       <c r="AK21" s="41" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="AL21" s="41" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="AM21" s="41" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="AN21" s="26" t="s">
         <v>11</v>
@@ -5717,26 +5708,26 @@
     </row>
     <row r="22" spans="1:41" ht="110" x14ac:dyDescent="0.35">
       <c r="A22" s="22"/>
-      <c r="B22" s="21" t="s">
+      <c r="B22" s="66" t="s">
         <v>52</v>
       </c>
       <c r="C22" s="21" t="s">
         <v>30</v>
       </c>
       <c r="D22" s="21" t="s">
-        <v>21</v>
+        <v>369</v>
       </c>
       <c r="E22" s="21">
         <v>20</v>
       </c>
       <c r="F22" s="21" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="G22" s="21" t="s">
         <v>1</v>
       </c>
       <c r="H22" s="22" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="I22" s="22" t="s">
         <v>53</v>
@@ -5745,7 +5736,7 @@
         <v>1</v>
       </c>
       <c r="K22" s="36" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="L22" s="24" t="s">
         <v>11</v>
@@ -5778,7 +5769,7 @@
         <v>11</v>
       </c>
       <c r="V22" s="43" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="W22" s="24" t="s">
         <v>11</v>
@@ -5790,10 +5781,10 @@
         <v>11</v>
       </c>
       <c r="Z22" s="43" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="AA22" s="43" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="AB22" s="23" t="s">
         <v>11</v>
@@ -5837,14 +5828,14 @@
       </c>
     </row>
     <row r="23" spans="1:41" ht="70" x14ac:dyDescent="0.35">
-      <c r="B23" s="68" t="s">
+      <c r="B23" s="66" t="s">
         <v>33</v>
       </c>
       <c r="C23" s="21" t="s">
         <v>30</v>
       </c>
       <c r="D23" s="21" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="E23" s="21">
         <v>4</v>
@@ -5865,7 +5856,7 @@
         <v>5</v>
       </c>
       <c r="K23" s="36" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="L23" s="23" t="s">
         <v>11</v>
@@ -5877,7 +5868,7 @@
         <v>11</v>
       </c>
       <c r="O23" s="42" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
       <c r="P23" s="23" t="s">
         <v>11</v>
@@ -5957,7 +5948,7 @@
       </c>
     </row>
     <row r="24" spans="1:41" ht="70" x14ac:dyDescent="0.35">
-      <c r="B24" s="21" t="s">
+      <c r="B24" s="66" t="s">
         <v>17</v>
       </c>
       <c r="C24" s="21" t="s">
@@ -5970,7 +5961,7 @@
         <v>1</v>
       </c>
       <c r="F24" s="21" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="G24" s="21" t="s">
         <v>1</v>
@@ -5985,7 +5976,7 @@
         <v>5</v>
       </c>
       <c r="K24" s="36" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="L24" s="23" t="s">
         <v>11</v>
@@ -6000,16 +5991,16 @@
         <v>11</v>
       </c>
       <c r="P24" s="42" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="Q24" s="42" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="R24" s="42" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="S24" s="42" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="T24" s="24" t="s">
         <v>11</v>
@@ -6043,22 +6034,22 @@
       </c>
       <c r="AD24" s="25"/>
       <c r="AE24" s="41" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="AF24" s="26" t="s">
         <v>11</v>
       </c>
       <c r="AG24" s="41" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="AH24" s="41" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="AI24" s="26" t="s">
         <v>11</v>
       </c>
       <c r="AJ24" s="41" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="AK24" s="26" t="s">
         <v>11</v>
@@ -6106,7 +6097,7 @@
   <sheetData>
     <row r="1" spans="2:35" x14ac:dyDescent="0.35">
       <c r="F1" s="16" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="G1" s="16"/>
       <c r="H1" s="16"/>
@@ -6126,7 +6117,7 @@
       <c r="V1" s="16"/>
       <c r="W1" s="16"/>
       <c r="Y1" s="17" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="Z1" s="18"/>
       <c r="AA1" s="18"/>
@@ -6144,7 +6135,7 @@
         <v>2</v>
       </c>
       <c r="C2" s="30" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="D2" s="30" t="s">
         <v>27</v>
@@ -6156,7 +6147,7 @@
         <v>15</v>
       </c>
       <c r="G2" s="20" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="H2" s="20" t="s">
         <v>14</v>
@@ -6168,16 +6159,16 @@
         <v>38</v>
       </c>
       <c r="K2" s="20" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="L2" s="32" t="s">
         <v>40</v>
       </c>
       <c r="M2" s="32" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="N2" s="38" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="O2" s="20" t="s">
         <v>44</v>
@@ -6198,32 +6189,32 @@
         <v>54</v>
       </c>
       <c r="U2" s="20" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="V2" s="20" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="W2" s="20" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="X2" s="33"/>
       <c r="Y2" s="20" t="s">
         <v>38</v>
       </c>
       <c r="Z2" s="32" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="AA2" s="20" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="AB2" s="20" t="s">
         <v>39</v>
       </c>
       <c r="AC2" s="20" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="AD2" s="32" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="AE2" s="20" t="s">
         <v>49</v>
@@ -6235,10 +6226,10 @@
         <v>51</v>
       </c>
       <c r="AH2" s="38" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="AI2" s="34" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
     </row>
     <row r="3" spans="2:35" x14ac:dyDescent="0.35">
@@ -6246,7 +6237,7 @@
         <v>66</v>
       </c>
       <c r="C3" s="21" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="D3" s="21" t="s">
         <v>21</v>
@@ -6273,7 +6264,7 @@
         <v>11</v>
       </c>
       <c r="L3" s="42" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="M3" s="24" t="s">
         <v>11</v>
@@ -6303,10 +6294,10 @@
         <v>11</v>
       </c>
       <c r="V3" s="42" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="W3" s="42" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="X3" s="25"/>
       <c r="Y3" s="26" t="s">
@@ -6316,7 +6307,7 @@
         <v>11</v>
       </c>
       <c r="AA3" s="41" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="AB3" s="26" t="s">
         <v>11</v>
@@ -6381,7 +6372,7 @@
         <v>11</v>
       </c>
       <c r="N4" s="43" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="O4" s="24" t="s">
         <v>11</v>
@@ -6439,7 +6430,7 @@
         <v>11</v>
       </c>
       <c r="AH4" s="41" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="AI4" s="26" t="s">
         <v>11</v>
@@ -6483,7 +6474,7 @@
         <v>11</v>
       </c>
       <c r="N5" s="43" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="O5" s="24" t="s">
         <v>11</v>
@@ -6541,7 +6532,7 @@
         <v>11</v>
       </c>
       <c r="AH5" s="41" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="AI5" s="26" t="s">
         <v>11</v>
@@ -6585,7 +6576,7 @@
         <v>11</v>
       </c>
       <c r="N6" s="43" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="O6" s="24" t="s">
         <v>11</v>
@@ -6622,10 +6613,10 @@
         <v>11</v>
       </c>
       <c r="AA6" s="41" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="AB6" s="41" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="AC6" s="26" t="s">
         <v>11</v>
@@ -6687,7 +6678,7 @@
         <v>11</v>
       </c>
       <c r="N7" s="43" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="O7" s="24" t="s">
         <v>11</v>
@@ -6724,10 +6715,10 @@
         <v>11</v>
       </c>
       <c r="AA7" s="41" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="AB7" s="41" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="AC7" s="26" t="s">
         <v>11</v>
@@ -6756,7 +6747,7 @@
         <v>55</v>
       </c>
       <c r="C8" s="21" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="D8" s="21" t="s">
         <v>21</v>
@@ -6789,7 +6780,7 @@
         <v>11</v>
       </c>
       <c r="N8" s="43" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="O8" s="24" t="s">
         <v>11</v>
@@ -6847,7 +6838,7 @@
         <v>11</v>
       </c>
       <c r="AH8" s="41" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="AI8" s="26" t="s">
         <v>11</v>
@@ -6858,7 +6849,7 @@
         <v>57</v>
       </c>
       <c r="C9" s="21" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="D9" s="21" t="s">
         <v>21</v>
@@ -6891,7 +6882,7 @@
         <v>11</v>
       </c>
       <c r="N9" s="43" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="O9" s="24" t="s">
         <v>11</v>
@@ -6949,7 +6940,7 @@
         <v>11</v>
       </c>
       <c r="AH9" s="41" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="AI9" s="26" t="s">
         <v>11</v>
@@ -6963,16 +6954,16 @@
         <v>30</v>
       </c>
       <c r="D10" s="21" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="E10" s="21">
         <v>2</v>
       </c>
       <c r="F10" s="43" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="G10" s="43" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="H10" s="23" t="s">
         <v>11</v>
@@ -7024,19 +7015,19 @@
       </c>
       <c r="X10" s="25"/>
       <c r="Y10" s="41" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="Z10" s="27" t="s">
         <v>11</v>
       </c>
       <c r="AA10" s="41" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="AB10" s="41" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="AC10" s="41" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="AD10" s="26" t="s">
         <v>11</v>
@@ -7065,16 +7056,16 @@
         <v>31</v>
       </c>
       <c r="D11" s="21" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="E11" s="21">
         <v>1</v>
       </c>
       <c r="F11" s="43" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="G11" s="43" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="H11" s="23" t="s">
         <v>11</v>
@@ -7135,7 +7126,7 @@
         <v>11</v>
       </c>
       <c r="AB11" s="41" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="AC11" s="26" t="s">
         <v>11</v>
@@ -7167,7 +7158,7 @@
         <v>30</v>
       </c>
       <c r="D12" s="21" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="E12" s="21">
         <v>1</v>
@@ -7179,7 +7170,7 @@
         <v>11</v>
       </c>
       <c r="H12" s="43" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
       <c r="I12" s="23" t="s">
         <v>11</v>
@@ -7269,13 +7260,13 @@
         <v>32</v>
       </c>
       <c r="D13" s="21" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="E13" s="21">
         <v>1</v>
       </c>
       <c r="F13" s="43" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
       <c r="G13" s="23" t="s">
         <v>11</v>
@@ -7330,19 +7321,19 @@
       </c>
       <c r="X13" s="25"/>
       <c r="Y13" s="41" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="Z13" s="41" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="AA13" s="41" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="AB13" s="41" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="AC13" s="41" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="AD13" s="26" t="s">
         <v>11</v>
@@ -7368,7 +7359,7 @@
         <v>60</v>
       </c>
       <c r="C14" s="21" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="D14" s="21" t="s">
         <v>21</v>
@@ -7395,13 +7386,13 @@
         <v>11</v>
       </c>
       <c r="L14" s="43" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="M14" s="24" t="s">
         <v>11</v>
       </c>
       <c r="N14" s="43" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="O14" s="24" t="s">
         <v>11</v>
@@ -7438,7 +7429,7 @@
         <v>11</v>
       </c>
       <c r="AA14" s="41" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="AB14" s="26" t="s">
         <v>11</v>
@@ -7459,7 +7450,7 @@
         <v>11</v>
       </c>
       <c r="AH14" s="41" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="AI14" s="26" t="s">
         <v>11</v>
@@ -7503,7 +7494,7 @@
         <v>11</v>
       </c>
       <c r="N15" s="43" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="O15" s="24" t="s">
         <v>11</v>
@@ -7540,7 +7531,7 @@
         <v>11</v>
       </c>
       <c r="AA15" s="41" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="AB15" s="26" t="s">
         <v>11</v>
@@ -7561,7 +7552,7 @@
         <v>11</v>
       </c>
       <c r="AH15" s="41" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="AI15" s="26" t="s">
         <v>11</v>
@@ -7572,7 +7563,7 @@
         <v>64</v>
       </c>
       <c r="C16" s="21" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="D16" s="21" t="s">
         <v>21</v>
@@ -7605,7 +7596,7 @@
         <v>11</v>
       </c>
       <c r="N16" s="43" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="O16" s="24" t="s">
         <v>11</v>
@@ -7707,7 +7698,7 @@
         <v>11</v>
       </c>
       <c r="N17" s="43" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="O17" s="24" t="s">
         <v>11</v>
@@ -7809,7 +7800,7 @@
         <v>11</v>
       </c>
       <c r="N18" s="43" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="O18" s="23" t="s">
         <v>11</v>
@@ -7878,7 +7869,7 @@
         <v>69</v>
       </c>
       <c r="C19" s="21" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="D19" s="21" t="s">
         <v>24</v>
@@ -7911,7 +7902,7 @@
         <v>11</v>
       </c>
       <c r="N19" s="43" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="O19" s="24" t="s">
         <v>11</v>
@@ -7948,7 +7939,7 @@
         <v>11</v>
       </c>
       <c r="AA19" s="41" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="AB19" s="26" t="s">
         <v>11</v>
@@ -8074,7 +8065,7 @@
         <v>11</v>
       </c>
       <c r="AI20" s="41" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
     </row>
     <row r="21" spans="2:35" x14ac:dyDescent="0.35">
@@ -8118,19 +8109,19 @@
         <v>11</v>
       </c>
       <c r="O21" s="43" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="P21" s="43" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="Q21" s="43" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="R21" s="43" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="S21" s="43" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="T21" s="23" t="s">
         <v>11</v>
@@ -8164,13 +8155,13 @@
         <v>11</v>
       </c>
       <c r="AE21" s="41" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="AF21" s="41" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="AG21" s="41" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="AH21" s="26" t="s">
         <v>11</v>
@@ -8223,7 +8214,7 @@
         <v>11</v>
       </c>
       <c r="P22" s="43" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="Q22" s="24" t="s">
         <v>11</v>
@@ -8235,10 +8226,10 @@
         <v>11</v>
       </c>
       <c r="T22" s="43" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="U22" s="43" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="V22" s="23" t="s">
         <v>11</v>
@@ -8289,7 +8280,7 @@
         <v>30</v>
       </c>
       <c r="D23" s="21" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="E23" s="21">
         <v>4</v>
@@ -8304,7 +8295,7 @@
         <v>11</v>
       </c>
       <c r="I23" s="42" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
       <c r="J23" s="23" t="s">
         <v>11</v>
@@ -8409,16 +8400,16 @@
         <v>11</v>
       </c>
       <c r="J24" s="42" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="K24" s="42" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="L24" s="42" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="M24" s="42" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="N24" s="24" t="s">
         <v>11</v>
@@ -8452,22 +8443,22 @@
       </c>
       <c r="X24" s="25"/>
       <c r="Y24" s="41" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="Z24" s="26" t="s">
         <v>11</v>
       </c>
       <c r="AA24" s="41" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="AB24" s="41" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="AC24" s="26" t="s">
         <v>11</v>
       </c>
       <c r="AD24" s="41" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="AE24" s="26" t="s">
         <v>11</v>
@@ -8493,12 +8484,12 @@
     </row>
     <row r="28" spans="2:35" x14ac:dyDescent="0.35">
       <c r="F28" s="16" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="G28" s="16"/>
       <c r="H28" s="16"/>
       <c r="J28" s="17" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
     </row>
     <row r="29" spans="2:35" ht="80" x14ac:dyDescent="0.35">
@@ -8506,7 +8497,7 @@
         <v>2</v>
       </c>
       <c r="C29" s="30" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="D29" s="30" t="s">
         <v>27</v>
@@ -8518,14 +8509,14 @@
         <v>40</v>
       </c>
       <c r="G29" s="20" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="H29" s="20" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="I29" s="33"/>
       <c r="J29" s="20" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
     </row>
     <row r="30" spans="2:35" x14ac:dyDescent="0.35">
@@ -8533,7 +8524,7 @@
         <v>66</v>
       </c>
       <c r="C30" s="58" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="D30" s="21" t="s">
         <v>21</v>
@@ -8542,17 +8533,17 @@
         <v>5</v>
       </c>
       <c r="F30" s="42" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="G30" s="42" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="H30" s="42" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="I30" s="25"/>
       <c r="J30" s="41" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
     </row>
     <row r="31" spans="2:35" x14ac:dyDescent="0.35">
@@ -8562,12 +8553,12 @@
     </row>
     <row r="33" spans="2:33" x14ac:dyDescent="0.35">
       <c r="F33" s="16" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="G33" s="16"/>
       <c r="H33" s="16"/>
       <c r="J33" s="17" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="K33" s="18"/>
       <c r="L33" s="19"/>
@@ -8577,7 +8568,7 @@
         <v>2</v>
       </c>
       <c r="C34" s="30" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="D34" s="30" t="s">
         <v>27</v>
@@ -8589,20 +8580,20 @@
         <v>15</v>
       </c>
       <c r="G34" s="20" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="H34" s="38" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="I34" s="33"/>
       <c r="J34" s="20" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="K34" s="20" t="s">
         <v>39</v>
       </c>
       <c r="L34" s="38" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
     </row>
     <row r="35" spans="2:33" ht="30" x14ac:dyDescent="0.35">
@@ -8625,7 +8616,7 @@
         <v>11</v>
       </c>
       <c r="H35" s="43" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="I35" s="25"/>
       <c r="J35" s="27" t="s">
@@ -8635,7 +8626,7 @@
         <v>11</v>
       </c>
       <c r="L35" s="41" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
     </row>
     <row r="36" spans="2:33" ht="30" x14ac:dyDescent="0.35">
@@ -8658,7 +8649,7 @@
         <v>11</v>
       </c>
       <c r="H36" s="43" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="I36" s="25"/>
       <c r="J36" s="27" t="s">
@@ -8668,7 +8659,7 @@
         <v>11</v>
       </c>
       <c r="L36" s="41" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
     </row>
     <row r="37" spans="2:33" ht="30" x14ac:dyDescent="0.35">
@@ -8679,16 +8670,16 @@
         <v>31</v>
       </c>
       <c r="D37" s="21" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="E37" s="21">
         <v>1</v>
       </c>
       <c r="F37" s="43" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="G37" s="43" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="H37" s="23" t="s">
         <v>11</v>
@@ -8698,7 +8689,7 @@
         <v>11</v>
       </c>
       <c r="K37" s="41" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="L37" s="26" t="s">
         <v>11</v>
@@ -8724,7 +8715,7 @@
         <v>11</v>
       </c>
       <c r="H38" s="43" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="I38" s="25"/>
       <c r="J38" s="26" t="s">
@@ -8742,7 +8733,7 @@
         <v>69</v>
       </c>
       <c r="C39" s="60" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="D39" s="21" t="s">
         <v>24</v>
@@ -8757,11 +8748,11 @@
         <v>11</v>
       </c>
       <c r="H39" s="43" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="I39" s="25"/>
       <c r="J39" s="41" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="K39" s="26" t="s">
         <v>11</v>
@@ -8778,7 +8769,7 @@
     </row>
     <row r="42" spans="2:33" x14ac:dyDescent="0.35">
       <c r="F42" s="16" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="G42" s="16"/>
       <c r="H42" s="16"/>
@@ -8796,7 +8787,7 @@
       <c r="T42" s="16"/>
       <c r="U42" s="16"/>
       <c r="W42" s="17" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="X42" s="18"/>
       <c r="Y42" s="18"/>
@@ -8814,7 +8805,7 @@
         <v>2</v>
       </c>
       <c r="C43" s="30" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="D43" s="30" t="s">
         <v>27</v>
@@ -8826,7 +8817,7 @@
         <v>15</v>
       </c>
       <c r="G43" s="20" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="H43" s="20" t="s">
         <v>14</v>
@@ -8838,16 +8829,16 @@
         <v>38</v>
       </c>
       <c r="K43" s="20" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="L43" s="32" t="s">
         <v>40</v>
       </c>
       <c r="M43" s="32" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="N43" s="38" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="O43" s="20" t="s">
         <v>44</v>
@@ -8868,26 +8859,26 @@
         <v>54</v>
       </c>
       <c r="U43" s="20" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="V43" s="33"/>
       <c r="W43" s="20" t="s">
         <v>38</v>
       </c>
       <c r="X43" s="32" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="Y43" s="20" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="Z43" s="20" t="s">
         <v>39</v>
       </c>
       <c r="AA43" s="20" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="AB43" s="32" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="AC43" s="20" t="s">
         <v>49</v>
@@ -8899,10 +8890,10 @@
         <v>51</v>
       </c>
       <c r="AF43" s="38" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="AG43" s="34" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
     </row>
     <row r="44" spans="2:33" ht="20" x14ac:dyDescent="0.35">
@@ -8943,7 +8934,7 @@
         <v>11</v>
       </c>
       <c r="N44" s="43" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="O44" s="24" t="s">
         <v>11</v>
@@ -8974,10 +8965,10 @@
         <v>11</v>
       </c>
       <c r="Y44" s="41" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="Z44" s="41" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="AA44" s="26" t="s">
         <v>11</v>
@@ -9039,7 +9030,7 @@
         <v>11</v>
       </c>
       <c r="N45" s="43" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="O45" s="24" t="s">
         <v>11</v>
@@ -9070,10 +9061,10 @@
         <v>11</v>
       </c>
       <c r="Y45" s="41" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="Z45" s="41" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="AA45" s="26" t="s">
         <v>11</v>
@@ -9105,16 +9096,16 @@
         <v>30</v>
       </c>
       <c r="D46" s="21" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="E46" s="21">
         <v>2</v>
       </c>
       <c r="F46" s="43" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="G46" s="43" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="H46" s="23" t="s">
         <v>11</v>
@@ -9160,19 +9151,19 @@
       </c>
       <c r="V46" s="25"/>
       <c r="W46" s="41" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="X46" s="27" t="s">
         <v>11</v>
       </c>
       <c r="Y46" s="41" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="Z46" s="41" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="AA46" s="41" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="AB46" s="26" t="s">
         <v>11</v>
@@ -9201,7 +9192,7 @@
         <v>30</v>
       </c>
       <c r="D47" s="21" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="E47" s="21">
         <v>1</v>
@@ -9213,7 +9204,7 @@
         <v>11</v>
       </c>
       <c r="H47" s="43" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
       <c r="I47" s="23" t="s">
         <v>11</v>
@@ -9327,7 +9318,7 @@
         <v>11</v>
       </c>
       <c r="N48" s="43" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="O48" s="24" t="s">
         <v>11</v>
@@ -9358,7 +9349,7 @@
         <v>11</v>
       </c>
       <c r="Y48" s="41" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="Z48" s="26" t="s">
         <v>11</v>
@@ -9379,7 +9370,7 @@
         <v>11</v>
       </c>
       <c r="AF48" s="41" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="AG48" s="26" t="s">
         <v>11</v>
@@ -9423,7 +9414,7 @@
         <v>11</v>
       </c>
       <c r="N49" s="43" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="O49" s="24" t="s">
         <v>11</v>
@@ -9574,7 +9565,7 @@
         <v>11</v>
       </c>
       <c r="AG50" s="41" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
     </row>
     <row r="51" spans="2:33" x14ac:dyDescent="0.35">
@@ -9618,19 +9609,19 @@
         <v>11</v>
       </c>
       <c r="O51" s="43" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="P51" s="43" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="Q51" s="43" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="R51" s="43" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="S51" s="43" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="T51" s="23" t="s">
         <v>11</v>
@@ -9658,13 +9649,13 @@
         <v>11</v>
       </c>
       <c r="AC51" s="41" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="AD51" s="41" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="AE51" s="41" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="AF51" s="26" t="s">
         <v>11</v>
@@ -9717,7 +9708,7 @@
         <v>11</v>
       </c>
       <c r="P52" s="43" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="Q52" s="24" t="s">
         <v>11</v>
@@ -9729,10 +9720,10 @@
         <v>11</v>
       </c>
       <c r="T52" s="43" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="U52" s="43" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="V52" s="25"/>
       <c r="W52" s="26" t="s">
@@ -9777,7 +9768,7 @@
         <v>30</v>
       </c>
       <c r="D53" s="21" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="E53" s="21">
         <v>4</v>
@@ -9792,7 +9783,7 @@
         <v>11</v>
       </c>
       <c r="I53" s="42" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
       <c r="J53" s="23" t="s">
         <v>11</v>
@@ -9891,16 +9882,16 @@
         <v>11</v>
       </c>
       <c r="J54" s="42" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="K54" s="42" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="L54" s="42" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="M54" s="42" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="N54" s="24" t="s">
         <v>11</v>
@@ -9928,22 +9919,22 @@
       </c>
       <c r="V54" s="25"/>
       <c r="W54" s="41" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="X54" s="26" t="s">
         <v>11</v>
       </c>
       <c r="Y54" s="41" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="Z54" s="41" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="AA54" s="26" t="s">
         <v>11</v>
       </c>
       <c r="AB54" s="41" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="AC54" s="26" t="s">
         <v>11</v>
@@ -9969,10 +9960,10 @@
     </row>
     <row r="57" spans="2:33" x14ac:dyDescent="0.35">
       <c r="F57" s="16" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="H57" s="17" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="I57" s="18"/>
       <c r="J57" s="18"/>
@@ -9984,7 +9975,7 @@
         <v>2</v>
       </c>
       <c r="C58" s="30" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="D58" s="30" t="s">
         <v>27</v>
@@ -10000,16 +9991,16 @@
         <v>38</v>
       </c>
       <c r="I58" s="32" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="J58" s="20" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="K58" s="20" t="s">
         <v>39</v>
       </c>
       <c r="L58" s="20" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
     </row>
     <row r="59" spans="2:33" ht="20" x14ac:dyDescent="0.35">
@@ -10020,29 +10011,29 @@
         <v>32</v>
       </c>
       <c r="D59" s="21" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="E59" s="21">
         <v>1</v>
       </c>
       <c r="F59" s="43" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
       <c r="G59" s="25"/>
       <c r="H59" s="41" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="I59" s="41" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="J59" s="41" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="K59" s="41" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="L59" s="41" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
     </row>
     <row r="60" spans="2:33" x14ac:dyDescent="0.35">
@@ -10052,11 +10043,11 @@
     </row>
     <row r="62" spans="2:33" x14ac:dyDescent="0.35">
       <c r="F62" s="16" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="G62" s="16"/>
       <c r="I62" s="17" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="J62" s="19"/>
     </row>
@@ -10065,7 +10056,7 @@
         <v>2</v>
       </c>
       <c r="C63" s="30" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="D63" s="30" t="s">
         <v>27</v>
@@ -10077,14 +10068,14 @@
         <v>40</v>
       </c>
       <c r="G63" s="38" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="H63" s="33"/>
       <c r="I63" s="20" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="J63" s="38" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
     </row>
     <row r="64" spans="2:33" ht="20" x14ac:dyDescent="0.35">
@@ -10092,7 +10083,7 @@
         <v>55</v>
       </c>
       <c r="C64" s="58" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="D64" s="21" t="s">
         <v>21</v>
@@ -10104,14 +10095,14 @@
         <v>11</v>
       </c>
       <c r="G64" s="43" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="H64" s="25"/>
       <c r="I64" s="26" t="s">
         <v>11</v>
       </c>
       <c r="J64" s="41" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
     </row>
     <row r="65" spans="2:10" ht="20" x14ac:dyDescent="0.35">
@@ -10119,7 +10110,7 @@
         <v>57</v>
       </c>
       <c r="C65" s="58" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="D65" s="21" t="s">
         <v>21</v>
@@ -10131,14 +10122,14 @@
         <v>11</v>
       </c>
       <c r="G65" s="43" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="H65" s="25"/>
       <c r="I65" s="26" t="s">
         <v>11</v>
       </c>
       <c r="J65" s="41" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
     </row>
     <row r="66" spans="2:10" ht="20" x14ac:dyDescent="0.35">
@@ -10146,7 +10137,7 @@
         <v>60</v>
       </c>
       <c r="C66" s="58" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="D66" s="21" t="s">
         <v>21</v>
@@ -10155,17 +10146,17 @@
         <v>1</v>
       </c>
       <c r="F66" s="43" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="G66" s="43" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="H66" s="25"/>
       <c r="I66" s="41" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="J66" s="41" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
     </row>
     <row r="67" spans="2:10" ht="20" x14ac:dyDescent="0.35">
@@ -10173,7 +10164,7 @@
         <v>64</v>
       </c>
       <c r="C67" s="58" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="D67" s="21" t="s">
         <v>21</v>
@@ -10185,7 +10176,7 @@
         <v>11</v>
       </c>
       <c r="G67" s="43" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="H67" s="25"/>
       <c r="I67" s="26" t="s">
@@ -10219,7 +10210,7 @@
   <sheetData>
     <row r="1" spans="2:35" x14ac:dyDescent="0.35">
       <c r="F1" s="16" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="G1" s="16"/>
       <c r="H1" s="16"/>
@@ -10239,7 +10230,7 @@
       <c r="V1" s="16"/>
       <c r="W1" s="16"/>
       <c r="Y1" s="17" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="Z1" s="18"/>
       <c r="AA1" s="18"/>
@@ -10257,7 +10248,7 @@
         <v>2</v>
       </c>
       <c r="C2" s="30" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="D2" s="30" t="s">
         <v>27</v>
@@ -10269,7 +10260,7 @@
         <v>15</v>
       </c>
       <c r="G2" s="20" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="H2" s="20" t="s">
         <v>14</v>
@@ -10281,16 +10272,16 @@
         <v>38</v>
       </c>
       <c r="K2" s="20" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="L2" s="32" t="s">
         <v>40</v>
       </c>
       <c r="M2" s="32" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="N2" s="38" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="O2" s="20" t="s">
         <v>44</v>
@@ -10311,32 +10302,32 @@
         <v>54</v>
       </c>
       <c r="U2" s="20" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="V2" s="20" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="W2" s="20" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="X2" s="33"/>
       <c r="Y2" s="20" t="s">
         <v>38</v>
       </c>
       <c r="Z2" s="32" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="AA2" s="20" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="AB2" s="20" t="s">
         <v>39</v>
       </c>
       <c r="AC2" s="20" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="AD2" s="32" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="AE2" s="20" t="s">
         <v>49</v>
@@ -10348,10 +10339,10 @@
         <v>51</v>
       </c>
       <c r="AH2" s="38" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="AI2" s="34" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
     </row>
     <row r="3" spans="2:35" hidden="1" x14ac:dyDescent="0.35">
@@ -10359,7 +10350,7 @@
         <v>66</v>
       </c>
       <c r="C3" s="21" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="D3" s="21" t="s">
         <v>21</v>
@@ -10386,7 +10377,7 @@
         <v>11</v>
       </c>
       <c r="L3" s="42" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="M3" s="24" t="s">
         <v>11</v>
@@ -10416,10 +10407,10 @@
         <v>11</v>
       </c>
       <c r="V3" s="42" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="W3" s="42" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="X3" s="25"/>
       <c r="Y3" s="26" t="s">
@@ -10429,7 +10420,7 @@
         <v>11</v>
       </c>
       <c r="AA3" s="41" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="AB3" s="26" t="s">
         <v>11</v>
@@ -10494,7 +10485,7 @@
         <v>11</v>
       </c>
       <c r="N4" s="43" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="O4" s="24" t="s">
         <v>11</v>
@@ -10552,7 +10543,7 @@
         <v>11</v>
       </c>
       <c r="AH4" s="41" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="AI4" s="26" t="s">
         <v>11</v>
@@ -10596,7 +10587,7 @@
         <v>11</v>
       </c>
       <c r="N5" s="43" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="O5" s="24" t="s">
         <v>11</v>
@@ -10654,7 +10645,7 @@
         <v>11</v>
       </c>
       <c r="AH5" s="41" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="AI5" s="26" t="s">
         <v>11</v>
@@ -10698,7 +10689,7 @@
         <v>11</v>
       </c>
       <c r="N6" s="43" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="O6" s="24" t="s">
         <v>11</v>
@@ -10735,10 +10726,10 @@
         <v>11</v>
       </c>
       <c r="AA6" s="41" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="AB6" s="41" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="AC6" s="26" t="s">
         <v>11</v>
@@ -10800,7 +10791,7 @@
         <v>11</v>
       </c>
       <c r="N7" s="43" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="O7" s="24" t="s">
         <v>11</v>
@@ -10837,10 +10828,10 @@
         <v>11</v>
       </c>
       <c r="AA7" s="41" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="AB7" s="41" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="AC7" s="26" t="s">
         <v>11</v>
@@ -10869,7 +10860,7 @@
         <v>55</v>
       </c>
       <c r="C8" s="21" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="D8" s="21" t="s">
         <v>21</v>
@@ -10902,7 +10893,7 @@
         <v>11</v>
       </c>
       <c r="N8" s="43" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="O8" s="24" t="s">
         <v>11</v>
@@ -10960,7 +10951,7 @@
         <v>11</v>
       </c>
       <c r="AH8" s="41" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="AI8" s="26" t="s">
         <v>11</v>
@@ -10971,7 +10962,7 @@
         <v>57</v>
       </c>
       <c r="C9" s="21" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="D9" s="21" t="s">
         <v>21</v>
@@ -11004,7 +10995,7 @@
         <v>11</v>
       </c>
       <c r="N9" s="43" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="O9" s="24" t="s">
         <v>11</v>
@@ -11062,7 +11053,7 @@
         <v>11</v>
       </c>
       <c r="AH9" s="41" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="AI9" s="26" t="s">
         <v>11</v>
@@ -11076,16 +11067,16 @@
         <v>30</v>
       </c>
       <c r="D10" s="21" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="E10" s="21">
         <v>2</v>
       </c>
       <c r="F10" s="43" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="G10" s="43" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="H10" s="23" t="s">
         <v>11</v>
@@ -11137,19 +11128,19 @@
       </c>
       <c r="X10" s="25"/>
       <c r="Y10" s="41" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="Z10" s="27" t="s">
         <v>11</v>
       </c>
       <c r="AA10" s="41" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="AB10" s="41" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="AC10" s="41" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="AD10" s="26" t="s">
         <v>11</v>
@@ -11178,16 +11169,16 @@
         <v>31</v>
       </c>
       <c r="D11" s="21" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="E11" s="21">
         <v>1</v>
       </c>
       <c r="F11" s="43" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="G11" s="43" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="H11" s="23" t="s">
         <v>11</v>
@@ -11248,7 +11239,7 @@
         <v>11</v>
       </c>
       <c r="AB11" s="41" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="AC11" s="26" t="s">
         <v>11</v>
@@ -11280,7 +11271,7 @@
         <v>30</v>
       </c>
       <c r="D12" s="21" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="E12" s="21">
         <v>1</v>
@@ -11292,7 +11283,7 @@
         <v>11</v>
       </c>
       <c r="H12" s="43" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
       <c r="I12" s="23" t="s">
         <v>11</v>
@@ -11382,13 +11373,13 @@
         <v>32</v>
       </c>
       <c r="D13" s="21" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="E13" s="21">
         <v>1</v>
       </c>
       <c r="F13" s="43" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
       <c r="G13" s="23" t="s">
         <v>11</v>
@@ -11443,19 +11434,19 @@
       </c>
       <c r="X13" s="25"/>
       <c r="Y13" s="41" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="Z13" s="41" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="AA13" s="41" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="AB13" s="41" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="AC13" s="41" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="AD13" s="26" t="s">
         <v>11</v>
@@ -11481,7 +11472,7 @@
         <v>60</v>
       </c>
       <c r="C14" s="21" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="D14" s="21" t="s">
         <v>21</v>
@@ -11508,13 +11499,13 @@
         <v>11</v>
       </c>
       <c r="L14" s="43" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="M14" s="24" t="s">
         <v>11</v>
       </c>
       <c r="N14" s="43" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="O14" s="24" t="s">
         <v>11</v>
@@ -11551,7 +11542,7 @@
         <v>11</v>
       </c>
       <c r="AA14" s="41" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="AB14" s="26" t="s">
         <v>11</v>
@@ -11572,7 +11563,7 @@
         <v>11</v>
       </c>
       <c r="AH14" s="41" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="AI14" s="26" t="s">
         <v>11</v>
@@ -11616,7 +11607,7 @@
         <v>11</v>
       </c>
       <c r="N15" s="43" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="O15" s="24" t="s">
         <v>11</v>
@@ -11653,7 +11644,7 @@
         <v>11</v>
       </c>
       <c r="AA15" s="41" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="AB15" s="26" t="s">
         <v>11</v>
@@ -11674,7 +11665,7 @@
         <v>11</v>
       </c>
       <c r="AH15" s="41" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="AI15" s="26" t="s">
         <v>11</v>
@@ -11685,7 +11676,7 @@
         <v>64</v>
       </c>
       <c r="C16" s="21" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="D16" s="21" t="s">
         <v>21</v>
@@ -11718,7 +11709,7 @@
         <v>11</v>
       </c>
       <c r="N16" s="43" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="O16" s="24" t="s">
         <v>11</v>
@@ -11820,7 +11811,7 @@
         <v>11</v>
       </c>
       <c r="N17" s="43" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="O17" s="24" t="s">
         <v>11</v>
@@ -11922,7 +11913,7 @@
         <v>11</v>
       </c>
       <c r="N18" s="43" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="O18" s="23" t="s">
         <v>11</v>
@@ -11991,7 +11982,7 @@
         <v>69</v>
       </c>
       <c r="C19" s="21" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="D19" s="21" t="s">
         <v>24</v>
@@ -12024,7 +12015,7 @@
         <v>11</v>
       </c>
       <c r="N19" s="43" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="O19" s="24" t="s">
         <v>11</v>
@@ -12061,7 +12052,7 @@
         <v>11</v>
       </c>
       <c r="AA19" s="41" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="AB19" s="26" t="s">
         <v>11</v>
@@ -12187,7 +12178,7 @@
         <v>11</v>
       </c>
       <c r="AI20" s="41" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
     </row>
     <row r="21" spans="2:35" ht="20" hidden="1" x14ac:dyDescent="0.35">
@@ -12231,19 +12222,19 @@
         <v>11</v>
       </c>
       <c r="O21" s="43" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="P21" s="43" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="Q21" s="43" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="R21" s="43" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="S21" s="43" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="T21" s="23" t="s">
         <v>11</v>
@@ -12277,13 +12268,13 @@
         <v>11</v>
       </c>
       <c r="AE21" s="41" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="AF21" s="41" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="AG21" s="41" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="AH21" s="26" t="s">
         <v>11</v>
@@ -12336,7 +12327,7 @@
         <v>11</v>
       </c>
       <c r="P22" s="43" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="Q22" s="24" t="s">
         <v>11</v>
@@ -12348,10 +12339,10 @@
         <v>11</v>
       </c>
       <c r="T22" s="43" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="U22" s="43" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="V22" s="23" t="s">
         <v>11</v>
@@ -12402,7 +12393,7 @@
         <v>30</v>
       </c>
       <c r="D23" s="21" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="E23" s="21">
         <v>4</v>
@@ -12417,7 +12408,7 @@
         <v>11</v>
       </c>
       <c r="I23" s="42" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
       <c r="J23" s="23" t="s">
         <v>11</v>
@@ -12522,16 +12513,16 @@
         <v>11</v>
       </c>
       <c r="J24" s="42" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="K24" s="42" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="L24" s="42" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="M24" s="42" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="N24" s="24" t="s">
         <v>11</v>
@@ -12565,22 +12556,22 @@
       </c>
       <c r="X24" s="25"/>
       <c r="Y24" s="41" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="Z24" s="26" t="s">
         <v>11</v>
       </c>
       <c r="AA24" s="41" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="AB24" s="41" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="AC24" s="26" t="s">
         <v>11</v>
       </c>
       <c r="AD24" s="41" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="AE24" s="26" t="s">
         <v>11</v>
@@ -12632,12 +12623,12 @@
   <sheetData>
     <row r="2" spans="2:11" x14ac:dyDescent="0.35">
       <c r="F2" s="16" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="G2" s="16"/>
       <c r="H2" s="16"/>
       <c r="J2" s="17" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="K2" s="19"/>
     </row>
@@ -12646,7 +12637,7 @@
         <v>2</v>
       </c>
       <c r="C3" s="30" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="D3" s="30" t="s">
         <v>27</v>
@@ -12658,17 +12649,17 @@
         <v>15</v>
       </c>
       <c r="G3" s="20" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="H3" s="38" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="I3" s="33"/>
       <c r="J3" s="20" t="s">
         <v>39</v>
       </c>
       <c r="K3" s="38" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
     </row>
     <row r="4" spans="2:11" ht="30" x14ac:dyDescent="0.35">
@@ -12691,14 +12682,14 @@
         <v>11</v>
       </c>
       <c r="H4" s="43" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="I4" s="25"/>
       <c r="J4" s="27" t="s">
         <v>11</v>
       </c>
       <c r="K4" s="41" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
     </row>
     <row r="5" spans="2:11" ht="30" x14ac:dyDescent="0.35">
@@ -12721,14 +12712,14 @@
         <v>11</v>
       </c>
       <c r="H5" s="43" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="I5" s="25"/>
       <c r="J5" s="27" t="s">
         <v>11</v>
       </c>
       <c r="K5" s="41" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
     </row>
     <row r="6" spans="2:11" ht="30" x14ac:dyDescent="0.35">
@@ -12739,23 +12730,23 @@
         <v>31</v>
       </c>
       <c r="D6" s="21" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="E6" s="21">
         <v>1</v>
       </c>
       <c r="F6" s="43" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="G6" s="43" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="H6" s="23" t="s">
         <v>11</v>
       </c>
       <c r="I6" s="25"/>
       <c r="J6" s="41" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="K6" s="26" t="s">
         <v>11</v>
@@ -12781,7 +12772,7 @@
         <v>11</v>
       </c>
       <c r="H7" s="43" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="I7" s="25"/>
       <c r="J7" s="26" t="s">
@@ -12806,7 +12797,7 @@
   <sheetData>
     <row r="1" spans="1:1" ht="23" x14ac:dyDescent="0.35">
       <c r="A1" s="46" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.35">
@@ -12814,52 +12805,52 @@
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A3" s="48" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A4" s="48" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A5" s="48" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A6" s="48" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A7" s="48" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
     </row>
     <row r="8" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A8" s="48" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
     </row>
     <row r="9" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A9" s="48" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
     </row>
     <row r="10" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A10" s="48" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
     </row>
     <row r="11" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A11" s="48" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
     </row>
     <row r="12" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A12" s="48" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
     </row>
     <row r="13" spans="1:1" x14ac:dyDescent="0.35">
@@ -12870,7 +12861,7 @@
     </row>
     <row r="15" spans="1:1" ht="23" x14ac:dyDescent="0.35">
       <c r="A15" s="46" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
     </row>
     <row r="16" spans="1:1" x14ac:dyDescent="0.35">
@@ -12878,57 +12869,57 @@
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A17" s="48" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
     </row>
     <row r="18" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A18" s="48" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
     </row>
     <row r="19" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A19" s="48" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
     </row>
     <row r="20" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A20" s="48" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
     </row>
     <row r="21" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A21" s="48" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
     </row>
     <row r="22" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A22" s="48" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
     </row>
     <row r="23" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A23" s="48" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
     </row>
     <row r="24" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A24" s="48" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
     </row>
     <row r="25" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A25" s="48" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
     </row>
     <row r="26" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A26" s="48" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
     </row>
     <row r="27" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A27" s="48" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
     </row>
     <row r="28" spans="1:1" x14ac:dyDescent="0.35">
@@ -12942,7 +12933,7 @@
     </row>
     <row r="31" spans="1:1" ht="23" x14ac:dyDescent="0.35">
       <c r="A31" s="46" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
     </row>
     <row r="32" spans="1:1" x14ac:dyDescent="0.35">
@@ -12950,42 +12941,42 @@
     </row>
     <row r="33" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A33" s="48" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
     </row>
     <row r="34" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A34" s="48" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
     </row>
     <row r="35" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A35" s="48" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
     </row>
     <row r="36" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A36" s="48" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
     </row>
     <row r="37" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A37" s="48" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
     </row>
     <row r="38" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A38" s="48" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
     </row>
     <row r="39" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A39" s="48" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
     </row>
     <row r="40" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A40" s="48" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
     </row>
     <row r="41" spans="1:1" x14ac:dyDescent="0.35">
@@ -12999,7 +12990,7 @@
     </row>
     <row r="44" spans="1:1" ht="23" x14ac:dyDescent="0.35">
       <c r="A44" s="46" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
     </row>
     <row r="45" spans="1:1" x14ac:dyDescent="0.35">
@@ -13007,47 +12998,47 @@
     </row>
     <row r="46" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A46" s="48" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
     </row>
     <row r="47" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A47" s="48" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
     </row>
     <row r="48" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A48" s="48" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
     </row>
     <row r="49" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A49" s="48" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
     </row>
     <row r="50" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A50" s="48" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
     </row>
     <row r="51" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A51" s="48" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
     </row>
     <row r="52" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A52" s="48" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
     </row>
     <row r="53" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A53" s="48" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
     </row>
     <row r="54" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A54" s="48" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
     </row>
     <row r="55" spans="1:1" x14ac:dyDescent="0.35">
@@ -13061,7 +13052,7 @@
     </row>
     <row r="58" spans="1:1" ht="23" x14ac:dyDescent="0.35">
       <c r="A58" s="46" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
     </row>
     <row r="59" spans="1:1" x14ac:dyDescent="0.35">
@@ -13069,52 +13060,52 @@
     </row>
     <row r="60" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A60" s="48" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
     </row>
     <row r="61" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A61" s="48" t="s">
-        <v>339</v>
+        <v>337</v>
       </c>
     </row>
     <row r="62" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A62" s="48" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
     </row>
     <row r="63" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A63" s="48" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
     </row>
     <row r="64" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A64" s="48" t="s">
-        <v>342</v>
+        <v>340</v>
       </c>
     </row>
     <row r="65" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A65" s="48" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
     </row>
     <row r="66" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A66" s="48" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
     </row>
     <row r="67" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A67" s="48" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
     </row>
     <row r="68" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A68" s="48" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
     </row>
     <row r="69" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A69" s="48" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
     </row>
     <row r="70" spans="1:1" x14ac:dyDescent="0.35">
@@ -13128,7 +13119,7 @@
     </row>
     <row r="73" spans="1:1" ht="23" x14ac:dyDescent="0.35">
       <c r="A73" s="46" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
     </row>
     <row r="74" spans="1:1" x14ac:dyDescent="0.35">
@@ -13136,47 +13127,47 @@
     </row>
     <row r="75" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A75" s="48" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
     </row>
     <row r="76" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A76" s="48" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
     </row>
     <row r="77" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A77" s="48" t="s">
-        <v>350</v>
+        <v>348</v>
       </c>
     </row>
     <row r="78" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A78" s="48" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
     </row>
     <row r="79" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A79" s="48" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
     </row>
     <row r="80" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A80" s="48" t="s">
-        <v>352</v>
+        <v>350</v>
       </c>
     </row>
     <row r="81" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A81" s="48" t="s">
-        <v>353</v>
+        <v>351</v>
       </c>
     </row>
     <row r="82" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A82" s="48" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
     </row>
     <row r="83" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A83" s="48" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
     </row>
     <row r="84" spans="1:1" x14ac:dyDescent="0.35">
@@ -13190,7 +13181,7 @@
     </row>
     <row r="87" spans="1:1" ht="23" x14ac:dyDescent="0.35">
       <c r="A87" s="46" t="s">
-        <v>356</v>
+        <v>354</v>
       </c>
     </row>
     <row r="88" spans="1:1" x14ac:dyDescent="0.35">
@@ -13198,52 +13189,52 @@
     </row>
     <row r="89" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A89" s="48" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
     </row>
     <row r="90" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A90" s="48" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
     </row>
     <row r="91" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A91" s="48" t="s">
-        <v>359</v>
+        <v>357</v>
       </c>
     </row>
     <row r="92" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A92" s="48" t="s">
-        <v>360</v>
+        <v>358</v>
       </c>
     </row>
     <row r="93" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A93" s="48" t="s">
-        <v>361</v>
+        <v>359</v>
       </c>
     </row>
     <row r="94" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A94" s="48" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
     </row>
     <row r="95" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A95" s="48" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
     </row>
     <row r="96" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A96" s="48" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
     </row>
     <row r="97" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A97" s="48" t="s">
-        <v>365</v>
+        <v>363</v>
       </c>
     </row>
     <row r="98" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A98" s="48" t="s">
-        <v>366</v>
+        <v>364</v>
       </c>
     </row>
   </sheetData>
@@ -13278,13 +13269,13 @@
       <c r="D1" s="26" t="s">
         <v>16</v>
       </c>
-      <c r="F1" s="66" t="s">
-        <v>242</v>
-      </c>
-      <c r="G1" s="66"/>
-      <c r="H1" s="66"/>
-      <c r="I1" s="66"/>
-      <c r="J1" s="66"/>
+      <c r="F1" s="64" t="s">
+        <v>240</v>
+      </c>
+      <c r="G1" s="64"/>
+      <c r="H1" s="64"/>
+      <c r="I1" s="64"/>
+      <c r="J1" s="64"/>
     </row>
     <row r="2" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B2" s="39" t="s">
@@ -13296,11 +13287,11 @@
       <c r="D2" s="26" t="s">
         <v>24</v>
       </c>
-      <c r="F2" s="66"/>
-      <c r="G2" s="66"/>
-      <c r="H2" s="66"/>
-      <c r="I2" s="66"/>
-      <c r="J2" s="66"/>
+      <c r="F2" s="64"/>
+      <c r="G2" s="64"/>
+      <c r="H2" s="64"/>
+      <c r="I2" s="64"/>
+      <c r="J2" s="64"/>
     </row>
     <row r="3" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B3" s="39" t="s">
@@ -13312,11 +13303,11 @@
       <c r="D3" s="26" t="s">
         <v>16</v>
       </c>
-      <c r="F3" s="66"/>
-      <c r="G3" s="66"/>
-      <c r="H3" s="66"/>
-      <c r="I3" s="66"/>
-      <c r="J3" s="66"/>
+      <c r="F3" s="64"/>
+      <c r="G3" s="64"/>
+      <c r="H3" s="64"/>
+      <c r="I3" s="64"/>
+      <c r="J3" s="64"/>
     </row>
     <row r="4" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B4" s="39" t="s">
@@ -13328,11 +13319,11 @@
       <c r="D4" s="26" t="s">
         <v>21</v>
       </c>
-      <c r="F4" s="66"/>
-      <c r="G4" s="66"/>
-      <c r="H4" s="66"/>
-      <c r="I4" s="66"/>
-      <c r="J4" s="66"/>
+      <c r="F4" s="64"/>
+      <c r="G4" s="64"/>
+      <c r="H4" s="64"/>
+      <c r="I4" s="64"/>
+      <c r="J4" s="64"/>
     </row>
     <row r="5" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B5" s="39" t="s">
@@ -13344,11 +13335,11 @@
       <c r="D5" s="26" t="s">
         <v>21</v>
       </c>
-      <c r="F5" s="66"/>
-      <c r="G5" s="66"/>
-      <c r="H5" s="66"/>
-      <c r="I5" s="66"/>
-      <c r="J5" s="66"/>
+      <c r="F5" s="64"/>
+      <c r="G5" s="64"/>
+      <c r="H5" s="64"/>
+      <c r="I5" s="64"/>
+      <c r="J5" s="64"/>
     </row>
     <row r="6" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B6" s="39" t="s">
@@ -13360,11 +13351,11 @@
       <c r="D6" s="26" t="s">
         <v>21</v>
       </c>
-      <c r="F6" s="66"/>
-      <c r="G6" s="66"/>
-      <c r="H6" s="66"/>
-      <c r="I6" s="66"/>
-      <c r="J6" s="66"/>
+      <c r="F6" s="64"/>
+      <c r="G6" s="64"/>
+      <c r="H6" s="64"/>
+      <c r="I6" s="64"/>
+      <c r="J6" s="64"/>
     </row>
     <row r="7" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B7" s="39" t="s">
@@ -13376,181 +13367,181 @@
       <c r="D7" s="26" t="s">
         <v>24</v>
       </c>
-      <c r="F7" s="66"/>
-      <c r="G7" s="66"/>
-      <c r="H7" s="66"/>
-      <c r="I7" s="66"/>
-      <c r="J7" s="66"/>
+      <c r="F7" s="64"/>
+      <c r="G7" s="64"/>
+      <c r="H7" s="64"/>
+      <c r="I7" s="64"/>
+      <c r="J7" s="64"/>
     </row>
     <row r="9" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B9" s="37" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="D9" s="37" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="F9" s="37" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="H9" s="37" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="J9" s="37" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
     </row>
     <row r="10" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B10" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="D10" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="F10" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="H10" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="J10" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
     </row>
     <row r="11" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B11" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="D11" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="F11" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="H11" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="J11" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
     </row>
     <row r="12" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B12" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="D12" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="F12" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="H12" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="J12" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
     </row>
     <row r="13" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B13" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="D13" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="F13" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="H13" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="J13" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
     </row>
     <row r="14" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B14" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="D14" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="F14" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="H14" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="J14" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
     </row>
     <row r="15" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B15" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="D15" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="F15" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
     </row>
     <row r="16" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B16" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="D16" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="F16" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
     </row>
     <row r="17" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B17" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="F17" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
     </row>
     <row r="18" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B18" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="F18" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
     </row>
     <row r="19" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B19" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="F19" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
     </row>
     <row r="20" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B20" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="F20" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
     </row>
     <row r="21" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B21" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
     </row>
     <row r="22" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B22" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
     </row>
     <row r="23" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B23" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
     </row>
     <row r="27" spans="2:10" x14ac:dyDescent="0.35">
@@ -13558,279 +13549,279 @@
         <v>55</v>
       </c>
       <c r="C27" s="26" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="D27" s="26" t="s">
         <v>21</v>
       </c>
-      <c r="F27" s="67" t="s">
-        <v>253</v>
-      </c>
-      <c r="G27" s="67"/>
-      <c r="H27" s="67"/>
-      <c r="I27" s="67"/>
-      <c r="J27" s="67"/>
+      <c r="F27" s="65" t="s">
+        <v>251</v>
+      </c>
+      <c r="G27" s="65"/>
+      <c r="H27" s="65"/>
+      <c r="I27" s="65"/>
+      <c r="J27" s="65"/>
     </row>
     <row r="28" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B28" s="39" t="s">
         <v>57</v>
       </c>
       <c r="C28" s="26" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="D28" s="26" t="s">
         <v>21</v>
       </c>
-      <c r="F28" s="67" t="s">
-        <v>254</v>
-      </c>
-      <c r="G28" s="67"/>
-      <c r="H28" s="67"/>
-      <c r="I28" s="67"/>
-      <c r="J28" s="67"/>
+      <c r="F28" s="65" t="s">
+        <v>252</v>
+      </c>
+      <c r="G28" s="65"/>
+      <c r="H28" s="65"/>
+      <c r="I28" s="65"/>
+      <c r="J28" s="65"/>
     </row>
     <row r="29" spans="2:10" ht="31" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B29" s="39" t="s">
         <v>60</v>
       </c>
       <c r="C29" s="26" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="D29" s="26" t="s">
         <v>21</v>
       </c>
-      <c r="F29" s="65" t="s">
-        <v>255</v>
-      </c>
-      <c r="G29" s="65"/>
-      <c r="H29" s="65"/>
-      <c r="I29" s="65"/>
-      <c r="J29" s="65"/>
+      <c r="F29" s="63" t="s">
+        <v>253</v>
+      </c>
+      <c r="G29" s="63"/>
+      <c r="H29" s="63"/>
+      <c r="I29" s="63"/>
+      <c r="J29" s="63"/>
     </row>
     <row r="30" spans="2:10" ht="29.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B30" s="39" t="s">
         <v>64</v>
       </c>
       <c r="C30" s="26" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="D30" s="26" t="s">
         <v>21</v>
       </c>
-      <c r="F30" s="65" t="s">
-        <v>256</v>
-      </c>
-      <c r="G30" s="65"/>
-      <c r="H30" s="65"/>
-      <c r="I30" s="65"/>
-      <c r="J30" s="65"/>
+      <c r="F30" s="63" t="s">
+        <v>254</v>
+      </c>
+      <c r="G30" s="63"/>
+      <c r="H30" s="63"/>
+      <c r="I30" s="63"/>
+      <c r="J30" s="63"/>
     </row>
     <row r="31" spans="2:10" ht="20" x14ac:dyDescent="0.35">
       <c r="B31" s="39" t="s">
         <v>69</v>
       </c>
       <c r="C31" s="26" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="D31" s="26" t="s">
         <v>24</v>
       </c>
-      <c r="F31" s="65" t="s">
-        <v>257</v>
-      </c>
-      <c r="G31" s="65"/>
-      <c r="H31" s="65"/>
-      <c r="I31" s="65"/>
-      <c r="J31" s="65"/>
+      <c r="F31" s="63" t="s">
+        <v>255</v>
+      </c>
+      <c r="G31" s="63"/>
+      <c r="H31" s="63"/>
+      <c r="I31" s="63"/>
+      <c r="J31" s="63"/>
     </row>
     <row r="32" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B32" s="45"/>
     </row>
     <row r="34" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B34" s="37" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="D34" s="37" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="F34" s="37" t="s">
+        <v>214</v>
+      </c>
+      <c r="H34" s="37" t="s">
         <v>216</v>
-      </c>
-      <c r="H34" s="37" t="s">
-        <v>218</v>
       </c>
     </row>
     <row r="35" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B35" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="D35" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="F35" t="s">
+        <v>215</v>
+      </c>
+      <c r="H35" t="s">
         <v>217</v>
-      </c>
-      <c r="H35" t="s">
-        <v>219</v>
       </c>
     </row>
     <row r="36" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B36" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="D36" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="F36" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="H36" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
     </row>
     <row r="37" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B37" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="D37" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="F37" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="H37" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
     </row>
     <row r="38" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B38" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="D38" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="F38" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="H38" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
     </row>
     <row r="39" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B39" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
     </row>
     <row r="41" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B41" s="37" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="D41" s="37" t="s">
+        <v>223</v>
+      </c>
+      <c r="F41" s="37" t="s">
         <v>225</v>
       </c>
-      <c r="F41" s="37" t="s">
-        <v>227</v>
-      </c>
       <c r="H41" s="37" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
     </row>
     <row r="42" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B42" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="D42" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="F42" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="H42" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
     </row>
     <row r="43" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B43" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="D43" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="F43" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
     </row>
     <row r="44" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B44" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="D44" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="F44" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
     </row>
     <row r="45" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B45" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="D45" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
     </row>
     <row r="46" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B46" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="D46" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
     </row>
     <row r="47" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B47" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="D47" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
     </row>
     <row r="49" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B49" s="37" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="D49" s="37" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="F49" s="37" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
     </row>
     <row r="50" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B50" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="D50" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="F50" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
     </row>
     <row r="51" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B51" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="D51" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
     </row>
     <row r="52" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B52" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="D52" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
     </row>
   </sheetData>
@@ -13853,454 +13844,454 @@
   <sheetData>
     <row r="4" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B4" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
     </row>
     <row r="5" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B5" t="s">
+        <v>257</v>
+      </c>
+      <c r="C5" t="s">
+        <v>258</v>
+      </c>
+      <c r="D5" t="s">
         <v>259</v>
       </c>
-      <c r="C5" t="s">
+      <c r="E5" t="s">
         <v>260</v>
       </c>
-      <c r="D5" t="s">
+      <c r="F5" t="s">
         <v>261</v>
       </c>
-      <c r="E5" t="s">
+      <c r="G5" t="s">
         <v>262</v>
       </c>
-      <c r="F5" t="s">
+      <c r="H5" t="s">
         <v>263</v>
       </c>
-      <c r="G5" t="s">
+      <c r="I5" t="s">
         <v>264</v>
-      </c>
-      <c r="H5" t="s">
-        <v>265</v>
-      </c>
-      <c r="I5" t="s">
-        <v>266</v>
       </c>
     </row>
     <row r="6" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B6" t="s">
+        <v>265</v>
+      </c>
+      <c r="C6" t="s">
+        <v>266</v>
+      </c>
+      <c r="D6" t="s">
+        <v>266</v>
+      </c>
+      <c r="E6" t="s">
+        <v>184</v>
+      </c>
+      <c r="F6" t="s">
         <v>267</v>
       </c>
-      <c r="C6" t="s">
+      <c r="G6" t="s">
+        <v>267</v>
+      </c>
+      <c r="H6" t="s">
         <v>268</v>
       </c>
-      <c r="D6" t="s">
-        <v>268</v>
-      </c>
-      <c r="E6" t="s">
-        <v>186</v>
-      </c>
-      <c r="F6" t="s">
+      <c r="I6" t="s">
         <v>269</v>
-      </c>
-      <c r="G6" t="s">
-        <v>269</v>
-      </c>
-      <c r="H6" t="s">
-        <v>270</v>
-      </c>
-      <c r="I6" t="s">
-        <v>271</v>
       </c>
     </row>
     <row r="7" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B7" t="s">
+        <v>265</v>
+      </c>
+      <c r="C7" t="s">
+        <v>222</v>
+      </c>
+      <c r="D7" t="s">
+        <v>172</v>
+      </c>
+      <c r="E7" t="s">
         <v>267</v>
       </c>
-      <c r="C7" t="s">
-        <v>224</v>
-      </c>
-      <c r="D7" t="s">
-        <v>174</v>
-      </c>
-      <c r="E7" t="s">
-        <v>269</v>
-      </c>
       <c r="F7" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="G7" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="H7" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="I7" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
     </row>
     <row r="8" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B8" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="C8" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="D8" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="E8" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="F8" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="G8" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="H8" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="I8" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
     </row>
     <row r="9" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B9" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="C9" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="D9" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="E9" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="F9" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="G9" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="H9" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="I9" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
     </row>
     <row r="10" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B10" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="C10" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="D10" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="E10" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="F10" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="G10" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="H10" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="I10" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
     </row>
     <row r="11" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B11" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="C11" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="D11" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="E11" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="F11" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="G11" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="H11" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="I11" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
     </row>
     <row r="12" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B12" t="s">
+        <v>265</v>
+      </c>
+      <c r="C12" t="s">
+        <v>222</v>
+      </c>
+      <c r="D12" t="s">
+        <v>172</v>
+      </c>
+      <c r="E12" t="s">
+        <v>184</v>
+      </c>
+      <c r="F12" t="s">
         <v>267</v>
       </c>
-      <c r="C12" t="s">
-        <v>224</v>
-      </c>
-      <c r="D12" t="s">
-        <v>174</v>
-      </c>
-      <c r="E12" t="s">
-        <v>186</v>
-      </c>
-      <c r="F12" t="s">
-        <v>269</v>
-      </c>
       <c r="G12" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="H12" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="I12" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
     </row>
     <row r="15" spans="2:9" ht="15" x14ac:dyDescent="0.4">
       <c r="B15" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
     </row>
     <row r="16" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B16" t="s">
+        <v>257</v>
+      </c>
+      <c r="C16" t="s">
+        <v>258</v>
+      </c>
+      <c r="D16" t="s">
         <v>259</v>
       </c>
-      <c r="C16" t="s">
+      <c r="E16" t="s">
         <v>260</v>
       </c>
-      <c r="D16" t="s">
+      <c r="F16" t="s">
         <v>261</v>
       </c>
-      <c r="E16" t="s">
+      <c r="G16" t="s">
         <v>262</v>
       </c>
-      <c r="F16" t="s">
+      <c r="H16" t="s">
         <v>263</v>
       </c>
-      <c r="G16" t="s">
+      <c r="I16" t="s">
         <v>264</v>
-      </c>
-      <c r="H16" t="s">
-        <v>265</v>
-      </c>
-      <c r="I16" t="s">
-        <v>266</v>
       </c>
     </row>
     <row r="17" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B17" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="C17" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="D17" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="E17" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="F17" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="G17" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="H17" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="I17" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
     </row>
     <row r="18" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B18" t="s">
+        <v>278</v>
+      </c>
+      <c r="C18" t="s">
+        <v>279</v>
+      </c>
+      <c r="D18" t="s">
         <v>280</v>
       </c>
-      <c r="C18" t="s">
+      <c r="E18" t="s">
         <v>281</v>
       </c>
-      <c r="D18" t="s">
+      <c r="F18" t="s">
+        <v>267</v>
+      </c>
+      <c r="G18" t="s">
         <v>282</v>
       </c>
-      <c r="E18" t="s">
+      <c r="H18" t="s">
+        <v>268</v>
+      </c>
+      <c r="I18" t="s">
         <v>283</v>
-      </c>
-      <c r="F18" t="s">
-        <v>269</v>
-      </c>
-      <c r="G18" t="s">
-        <v>284</v>
-      </c>
-      <c r="H18" t="s">
-        <v>270</v>
-      </c>
-      <c r="I18" t="s">
-        <v>285</v>
       </c>
     </row>
     <row r="19" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B19" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="C19" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="D19" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="E19" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="F19" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="G19" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="H19" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="I19" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
     </row>
     <row r="20" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B20" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="C20" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="D20" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="E20" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="F20" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="G20" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="H20" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="I20" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
     </row>
     <row r="21" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B21" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="C21" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="D21" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="E21" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="F21" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="G21" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="H21" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="I21" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
     </row>
     <row r="22" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B22" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="C22" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="D22" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="E22" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="F22" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="G22" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="H22" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="I22" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
     </row>
     <row r="23" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B23" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="C23" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="D23" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="E23" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="F23" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="G23" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="H23" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="I23" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
     </row>
     <row r="24" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B24" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="C24" t="s">
+        <v>287</v>
+      </c>
+      <c r="D24" t="s">
+        <v>172</v>
+      </c>
+      <c r="E24" t="s">
         <v>289</v>
       </c>
-      <c r="D24" t="s">
-        <v>174</v>
-      </c>
-      <c r="E24" t="s">
-        <v>291</v>
-      </c>
       <c r="F24" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="G24" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="H24" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="I24" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
     </row>
   </sheetData>
@@ -14309,12 +14300,15 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="882a8f42-f1f9-4ba8-a024-a9506b2a3f1b" xsi:nil="true"/>
+    <Comentario xmlns="f3dc767a-0b06-462e-8350-fa01f76d53d6" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="f3dc767a-0b06-462e-8350-fa01f76d53d6">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -14555,21 +14549,27 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="882a8f42-f1f9-4ba8-a024-a9506b2a3f1b" xsi:nil="true"/>
-    <Comentario xmlns="f3dc767a-0b06-462e-8350-fa01f76d53d6" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="f3dc767a-0b06-462e-8350-fa01f76d53d6">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F2F9F198-AAB3-4743-83B7-70E545DDE86B}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{784A4964-F218-48FA-B8A8-6EC1F8CC6785}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="882a8f42-f1f9-4ba8-a024-a9506b2a3f1b"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="f3dc767a-0b06-462e-8350-fa01f76d53d6"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -14594,18 +14594,9 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{784A4964-F218-48FA-B8A8-6EC1F8CC6785}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F2F9F198-AAB3-4743-83B7-70E545DDE86B}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="882a8f42-f1f9-4ba8-a024-a9506b2a3f1b"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="f3dc767a-0b06-462e-8350-fa01f76d53d6"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
--- a/SAT-SDMA-7 Perfiles.xlsx
+++ b/SAT-SDMA-7 Perfiles.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\raquell.martinez\Documents\AISolutions\analyzeCV\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EC002E76-3C11-4E71-842C-50B488CC06CA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EA40D273-99EB-4793-8B74-8F950E1FE931}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="2" activeTab="2" xr2:uid="{D74C329F-941D-40F9-B295-21746B646AD6}"/>
   </bookViews>
@@ -196,7 +196,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3331" uniqueCount="370">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3329" uniqueCount="370">
   <si>
     <t>Director de proyecto</t>
   </si>
@@ -419,11 +419,6 @@
   <si>
     <t>Al menos 3 años de experiencia centro de desarrollo de software. 
 Adicional: 5 años de experiencia en análisis de sistemas y manejo de equipos de trabajo</t>
-  </si>
-  <si>
-    <t>Al menos 3 años de experiencia centro de desarrollo de software.
-Dominio de Tecnologías del AR y/o tecnologías open source
-Adicional: 1 recurso con experiencia en mantenimiento de aplicaciones en Sterling (soluciones de IBM)</t>
   </si>
   <si>
     <t>Analizar las propuestas de requerimientos de mejora tecnológica y procesos con el fin de apoyar en tareas como; Levantamiento y documentación de requerimientos complejos, Coordinación con desarrolladores, testers y áreas de negocio, Validación funcional (pruebas de aceptación, seguimiento a QA), Interlocución con usuarios, Responsables de coordinar las actividades de los Analistas junior, Conocimiento total de los requerimientos del proyecto asignado
@@ -1616,24 +1611,60 @@
 D1- Deseable</t>
   </si>
   <si>
-    <t xml:space="preserve">Al menos 5 años de experiencia centro de desarrollo de software. 
-Dominio de Tecnologías de la Arquitectura de Referencia (AR) y/o tecnologías open source
-Adicional: Al menos 1 recurso con experiencia en mantenimiento de aplicaciones en Sterling (soluciones de IBM)
-</t>
-  </si>
-  <si>
     <t>Validar que cada componente interactúe de forma sistémica en todas las iteraciones de un proyecto, para lograr congruencia al flujo de negocio y de información (proceso funcional). Identifica dependencias, duplicidades. Proponer soluciones a las necesidades de manera integrada.
 Habilidades en; Conocimiento de las plataformas de la Arquitectura de Referencia (AR), Resolución de problemas técnicos, Evaluación y optimización del rendimiento del sistema eligiendo las tecnologías más adecuadas</t>
   </si>
   <si>
     <t>Creación+D22</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Al menos 3 años de experiencia centro de desarrollo de software.
+Dominio de Tecnologías del AR y/o tecnologías open source
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Adicional: 1 recurso con experiencia en mantenimiento de aplicaciones en Sterling (soluciones de IBM)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Al menos 5 años de experiencia centro de desarrollo de software. 
+Dominio de Tecnologías de la Arquitectura de Referencia (AR) y/o tecnologías open source
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Adicional: Al menos 1 recurso con experiencia en mantenimiento de aplicaciones en Sterling (soluciones de IBM)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="22" x14ac:knownFonts="1">
+  <fonts count="23" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1787,8 +1818,14 @@
       <name val="Arial"/>
       <family val="2"/>
     </font>
+    <font>
+      <sz val="8"/>
+      <color rgb="FFFF0000"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
   </fonts>
-  <fills count="13">
+  <fills count="14">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1861,8 +1898,14 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF00B050"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="6">
+  <borders count="8">
     <border>
       <left/>
       <right/>
@@ -1927,11 +1970,37 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="hair">
+        <color indexed="64"/>
+      </left>
+      <right style="hair">
+        <color indexed="64"/>
+      </right>
+      <top style="hair">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="hair">
+        <color indexed="64"/>
+      </left>
+      <right style="hair">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="hair">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="67">
+  <cellXfs count="70">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
@@ -2084,8 +2153,20 @@
     <xf numFmtId="0" fontId="1" fillId="11" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="12" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="13" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="13" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="13" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
@@ -2095,9 +2176,6 @@
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="12" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2446,97 +2524,97 @@
   <sheetData>
     <row r="2" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B2" s="5" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
     </row>
     <row r="3" spans="2:4" x14ac:dyDescent="0.35">
       <c r="C3" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
     </row>
     <row r="4" spans="2:4" x14ac:dyDescent="0.35">
       <c r="D4" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
     </row>
     <row r="5" spans="2:4" x14ac:dyDescent="0.35">
       <c r="C5" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
     </row>
     <row r="6" spans="2:4" x14ac:dyDescent="0.35">
       <c r="C6" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
     </row>
     <row r="7" spans="2:4" x14ac:dyDescent="0.35">
       <c r="D7" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
     </row>
     <row r="8" spans="2:4" x14ac:dyDescent="0.35">
       <c r="C8" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
     </row>
     <row r="10" spans="2:4" x14ac:dyDescent="0.35">
       <c r="C10" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
     <row r="11" spans="2:4" x14ac:dyDescent="0.35">
       <c r="D11" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
     </row>
     <row r="12" spans="2:4" x14ac:dyDescent="0.35">
       <c r="C12" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
     </row>
     <row r="13" spans="2:4" x14ac:dyDescent="0.35">
       <c r="D13" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
     </row>
     <row r="14" spans="2:4" x14ac:dyDescent="0.35">
       <c r="C14" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
     </row>
     <row r="15" spans="2:4" x14ac:dyDescent="0.35">
       <c r="D15" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
     </row>
     <row r="16" spans="2:4" x14ac:dyDescent="0.35">
       <c r="C16" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
     </row>
     <row r="17" spans="3:4" x14ac:dyDescent="0.35">
       <c r="D17" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
     </row>
     <row r="18" spans="3:4" x14ac:dyDescent="0.35">
       <c r="C18" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
     </row>
     <row r="19" spans="3:4" x14ac:dyDescent="0.35">
       <c r="D19" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
     </row>
     <row r="20" spans="3:4" x14ac:dyDescent="0.35">
       <c r="C20" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
     </row>
     <row r="21" spans="3:4" x14ac:dyDescent="0.35">
       <c r="C21" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
     </row>
   </sheetData>
@@ -2561,12 +2639,12 @@
   <sheetData>
     <row r="1" spans="2:17" x14ac:dyDescent="0.35">
       <c r="K1" s="40" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
     </row>
     <row r="2" spans="2:17" x14ac:dyDescent="0.35">
       <c r="B2" s="8" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C2" s="6"/>
       <c r="D2" s="6"/>
@@ -2581,7 +2659,7 @@
     </row>
     <row r="3" spans="2:17" x14ac:dyDescent="0.35">
       <c r="C3" s="6" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="D3" s="6"/>
       <c r="E3" s="6"/>
@@ -2597,7 +2675,7 @@
     </row>
     <row r="4" spans="2:17" x14ac:dyDescent="0.35">
       <c r="C4" s="7" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D4" s="7"/>
       <c r="E4" s="7"/>
@@ -2633,7 +2711,7 @@
     </row>
     <row r="6" spans="2:17" x14ac:dyDescent="0.35">
       <c r="C6" s="7" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="D6" s="7"/>
       <c r="E6" s="7"/>
@@ -2649,7 +2727,7 @@
     </row>
     <row r="7" spans="2:17" x14ac:dyDescent="0.35">
       <c r="C7" s="7" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D7" s="7"/>
       <c r="E7" s="7"/>
@@ -2665,7 +2743,7 @@
     </row>
     <row r="9" spans="2:17" x14ac:dyDescent="0.35">
       <c r="B9" s="5" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="C9" s="5"/>
     </row>
@@ -2678,11 +2756,11 @@
         <v>1</v>
       </c>
       <c r="F10" s="7" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="G10" s="7"/>
       <c r="H10" s="7" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="K10" s="29" t="s">
         <v>17</v>
@@ -2697,13 +2775,13 @@
         <v>1</v>
       </c>
       <c r="F11" s="7" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="G11" s="7">
         <v>5</v>
       </c>
       <c r="H11" s="7" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="K11" s="29" t="s">
         <v>18</v>
@@ -2711,20 +2789,20 @@
     </row>
     <row r="12" spans="2:17" x14ac:dyDescent="0.35">
       <c r="C12" s="7" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="D12" s="7"/>
       <c r="E12" s="7">
         <v>1</v>
       </c>
       <c r="F12" s="7" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="G12" s="7">
         <v>30</v>
       </c>
       <c r="H12" s="7" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="K12" s="29" t="s">
         <v>19</v>
@@ -2732,15 +2810,15 @@
     </row>
     <row r="13" spans="2:17" x14ac:dyDescent="0.35">
       <c r="I13" t="s">
+        <v>112</v>
+      </c>
+      <c r="J13" t="s">
         <v>113</v>
-      </c>
-      <c r="J13" t="s">
-        <v>114</v>
       </c>
     </row>
     <row r="14" spans="2:17" x14ac:dyDescent="0.35">
       <c r="B14" s="8" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="C14" s="6"/>
       <c r="D14" s="6"/>
@@ -2766,7 +2844,7 @@
         <v>1</v>
       </c>
       <c r="F15" s="6" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="G15" s="6"/>
       <c r="H15" s="6" t="s">
@@ -2779,25 +2857,25 @@
         <v>1</v>
       </c>
       <c r="L15" s="29" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
     </row>
     <row r="16" spans="2:17" x14ac:dyDescent="0.35">
       <c r="C16" s="7" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="D16" s="7"/>
       <c r="E16" s="7">
         <v>1</v>
       </c>
       <c r="F16" s="7" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="G16" s="7">
         <v>5</v>
       </c>
       <c r="H16" s="7" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="I16" s="10">
         <v>1</v>
@@ -2806,27 +2884,27 @@
         <v>2</v>
       </c>
       <c r="L16" s="29" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
     </row>
     <row r="17" spans="2:18" x14ac:dyDescent="0.35">
       <c r="C17" s="7" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D17" s="7" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="E17" s="7">
         <v>1</v>
       </c>
       <c r="F17" s="7" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="G17" s="7">
         <v>5</v>
       </c>
       <c r="H17" s="7" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="I17" s="10">
         <v>1</v>
@@ -2840,22 +2918,22 @@
     </row>
     <row r="18" spans="2:18" x14ac:dyDescent="0.35">
       <c r="C18" s="7" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D18" s="7" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="E18" s="7">
         <v>2</v>
       </c>
       <c r="F18" s="7" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="G18" s="7">
         <v>1</v>
       </c>
       <c r="H18" s="7" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="I18" s="10">
         <v>8</v>
@@ -2869,22 +2947,22 @@
     </row>
     <row r="19" spans="2:18" x14ac:dyDescent="0.35">
       <c r="C19" s="7" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="D19" s="7" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="E19" s="7">
         <v>1</v>
       </c>
       <c r="F19" s="7" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="G19" s="7">
         <v>5</v>
       </c>
       <c r="H19" s="7" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="I19" s="10">
         <v>1</v>
@@ -2898,22 +2976,22 @@
     </row>
     <row r="20" spans="2:18" x14ac:dyDescent="0.35">
       <c r="C20" s="7" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="D20" s="7" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="E20" s="7">
         <v>1</v>
       </c>
       <c r="F20" s="7" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="G20" s="7">
         <v>5</v>
       </c>
       <c r="H20" s="7" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="I20" s="10">
         <v>1</v>
@@ -2927,22 +3005,22 @@
     </row>
     <row r="21" spans="2:18" x14ac:dyDescent="0.35">
       <c r="C21" s="7" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D21" s="7" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="E21" s="7">
         <v>1</v>
       </c>
       <c r="F21" s="7" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="G21" s="7">
         <v>5</v>
       </c>
       <c r="H21" s="7" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="I21" s="10">
         <v>1</v>
@@ -2951,28 +3029,28 @@
         <v>2</v>
       </c>
       <c r="L21" s="29" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="R21" s="29"/>
     </row>
     <row r="22" spans="2:18" x14ac:dyDescent="0.35">
       <c r="C22" s="7" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D22" s="7" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="E22" s="7">
         <v>4</v>
       </c>
       <c r="F22" s="7" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="G22" s="7">
         <v>1</v>
       </c>
       <c r="H22" s="7" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="I22" s="10">
         <v>16</v>
@@ -2981,29 +3059,29 @@
         <v>40</v>
       </c>
       <c r="L22" s="29" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="Q22" s="13" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="R22" s="29"/>
     </row>
     <row r="23" spans="2:18" x14ac:dyDescent="0.35">
       <c r="C23" s="7" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="D23" s="7"/>
       <c r="E23" s="7">
         <v>1</v>
       </c>
       <c r="F23" s="7" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="G23" s="7">
         <v>2</v>
       </c>
       <c r="H23" s="7" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="I23" s="10">
         <v>2</v>
@@ -3017,19 +3095,19 @@
     </row>
     <row r="24" spans="2:18" x14ac:dyDescent="0.35">
       <c r="C24" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="E24">
         <v>1</v>
       </c>
       <c r="F24" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="G24">
         <v>2</v>
       </c>
       <c r="H24" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="I24" s="44">
         <v>2</v>
@@ -3048,15 +3126,15 @@
     </row>
     <row r="26" spans="2:18" x14ac:dyDescent="0.35">
       <c r="I26" t="s">
+        <v>112</v>
+      </c>
+      <c r="O26" t="s">
         <v>113</v>
-      </c>
-      <c r="O26" t="s">
-        <v>114</v>
       </c>
     </row>
     <row r="27" spans="2:18" x14ac:dyDescent="0.35">
       <c r="B27" s="8" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="C27" s="6"/>
       <c r="D27" s="6"/>
@@ -3092,20 +3170,20 @@
     </row>
     <row r="28" spans="2:18" x14ac:dyDescent="0.35">
       <c r="C28" s="6" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D28" s="6"/>
       <c r="E28" s="6">
         <v>1</v>
       </c>
       <c r="F28" s="6" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="G28" s="6">
         <v>30</v>
       </c>
       <c r="H28" s="6" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="I28" s="9">
         <v>1</v>
@@ -3137,20 +3215,20 @@
     </row>
     <row r="29" spans="2:18" x14ac:dyDescent="0.35">
       <c r="C29" s="7" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="D29" s="7"/>
       <c r="E29" s="7">
         <v>1</v>
       </c>
       <c r="F29" s="7" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="G29" s="7">
         <v>10</v>
       </c>
       <c r="H29" s="7" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="I29" s="10">
         <v>2</v>
@@ -3183,20 +3261,20 @@
     </row>
     <row r="30" spans="2:18" x14ac:dyDescent="0.35">
       <c r="C30" s="7" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="D30" s="7"/>
       <c r="E30" s="7">
         <v>1</v>
       </c>
       <c r="F30" s="7" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="G30" s="7">
         <v>10</v>
       </c>
       <c r="H30" s="7" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="I30" s="10">
         <v>1</v>
@@ -3229,7 +3307,7 @@
     </row>
     <row r="32" spans="2:18" x14ac:dyDescent="0.35">
       <c r="C32" s="13" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
     </row>
   </sheetData>
@@ -3270,12 +3348,12 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:41" ht="39" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="C1" s="62" t="s">
-        <v>366</v>
-      </c>
-      <c r="D1" s="62"/>
+      <c r="C1" s="64" t="s">
+        <v>365</v>
+      </c>
+      <c r="D1" s="64"/>
       <c r="L1" s="16" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="M1" s="16"/>
       <c r="N1" s="16"/>
@@ -3295,7 +3373,7 @@
       <c r="AB1" s="16"/>
       <c r="AC1" s="16"/>
       <c r="AE1" s="17" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="AF1" s="18"/>
       <c r="AG1" s="18"/>
@@ -3313,7 +3391,7 @@
         <v>2</v>
       </c>
       <c r="C2" s="30" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D2" s="30" t="s">
         <v>27</v>
@@ -3334,16 +3412,16 @@
         <v>26</v>
       </c>
       <c r="J2" s="35" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="K2" s="30" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="L2" s="20" t="s">
         <v>15</v>
       </c>
       <c r="M2" s="20" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="N2" s="20" t="s">
         <v>14</v>
@@ -3355,16 +3433,16 @@
         <v>38</v>
       </c>
       <c r="Q2" s="20" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="R2" s="32" t="s">
         <v>40</v>
       </c>
       <c r="S2" s="32" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="T2" s="38" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="U2" s="20" t="s">
         <v>44</v>
@@ -3385,32 +3463,32 @@
         <v>54</v>
       </c>
       <c r="AA2" s="20" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="AB2" s="20" t="s">
+        <v>136</v>
+      </c>
+      <c r="AC2" s="20" t="s">
         <v>137</v>
-      </c>
-      <c r="AC2" s="20" t="s">
-        <v>138</v>
       </c>
       <c r="AD2" s="33"/>
       <c r="AE2" s="20" t="s">
         <v>38</v>
       </c>
       <c r="AF2" s="32" t="s">
+        <v>131</v>
+      </c>
+      <c r="AG2" s="20" t="s">
         <v>132</v>
-      </c>
-      <c r="AG2" s="20" t="s">
-        <v>133</v>
       </c>
       <c r="AH2" s="20" t="s">
         <v>39</v>
       </c>
       <c r="AI2" s="20" t="s">
+        <v>133</v>
+      </c>
+      <c r="AJ2" s="32" t="s">
         <v>134</v>
-      </c>
-      <c r="AJ2" s="32" t="s">
-        <v>135</v>
       </c>
       <c r="AK2" s="20" t="s">
         <v>49</v>
@@ -3422,18 +3500,18 @@
         <v>51</v>
       </c>
       <c r="AN2" s="38" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="AO2" s="34" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
     </row>
     <row r="3" spans="1:41" ht="90" x14ac:dyDescent="0.35">
-      <c r="B3" s="66" t="s">
+      <c r="B3" s="63" t="s">
         <v>66</v>
       </c>
       <c r="C3" s="21" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="D3" s="21" t="s">
         <v>21</v>
@@ -3442,13 +3520,13 @@
         <v>5</v>
       </c>
       <c r="F3" s="21" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="G3" s="21" t="s">
         <v>1</v>
       </c>
       <c r="H3" s="22" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="I3" s="22" t="s">
         <v>67</v>
@@ -3457,7 +3535,7 @@
         <v>2</v>
       </c>
       <c r="K3" s="36" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="L3" s="24" t="s">
         <v>11</v>
@@ -3478,7 +3556,7 @@
         <v>11</v>
       </c>
       <c r="R3" s="42" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="S3" s="24" t="s">
         <v>11</v>
@@ -3508,10 +3586,10 @@
         <v>11</v>
       </c>
       <c r="AB3" s="42" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="AC3" s="42" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="AD3" s="25"/>
       <c r="AE3" s="26" t="s">
@@ -3521,7 +3599,7 @@
         <v>11</v>
       </c>
       <c r="AG3" s="41" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="AH3" s="26" t="s">
         <v>11</v>
@@ -3549,7 +3627,7 @@
       </c>
     </row>
     <row r="4" spans="1:41" ht="100" x14ac:dyDescent="0.35">
-      <c r="B4" s="21" t="s">
+      <c r="B4" s="65" t="s">
         <v>19</v>
       </c>
       <c r="C4" s="21" t="s">
@@ -3568,16 +3646,16 @@
         <v>1</v>
       </c>
       <c r="H4" s="22" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="I4" s="36" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="J4" s="21">
         <v>5</v>
       </c>
       <c r="K4" s="36" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="L4" s="24" t="s">
         <v>11</v>
@@ -3604,7 +3682,7 @@
         <v>11</v>
       </c>
       <c r="T4" s="43" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="U4" s="24" t="s">
         <v>11</v>
@@ -3662,16 +3740,14 @@
         <v>11</v>
       </c>
       <c r="AN4" s="41" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="AO4" s="26" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="5" spans="1:41" ht="100" x14ac:dyDescent="0.35">
-      <c r="B5" s="21" t="s">
-        <v>19</v>
-      </c>
+      <c r="B5" s="66"/>
       <c r="C5" s="21" t="s">
         <v>31</v>
       </c>
@@ -3688,16 +3764,16 @@
         <v>1</v>
       </c>
       <c r="H5" s="22" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="I5" s="36" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="J5" s="21">
         <v>5</v>
       </c>
       <c r="K5" s="36" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="L5" s="24" t="s">
         <v>11</v>
@@ -3724,7 +3800,7 @@
         <v>11</v>
       </c>
       <c r="T5" s="43" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="U5" s="24" t="s">
         <v>11</v>
@@ -3782,14 +3858,14 @@
         <v>11</v>
       </c>
       <c r="AN5" s="41" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="AO5" s="26" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="6" spans="1:41" ht="150" x14ac:dyDescent="0.35">
-      <c r="B6" s="66" t="s">
+      <c r="B6" s="65" t="s">
         <v>18</v>
       </c>
       <c r="C6" s="21" t="s">
@@ -3808,16 +3884,16 @@
         <v>1</v>
       </c>
       <c r="H6" s="22" t="s">
+        <v>196</v>
+      </c>
+      <c r="I6" s="22" t="s">
         <v>197</v>
-      </c>
-      <c r="I6" s="22" t="s">
-        <v>198</v>
       </c>
       <c r="J6" s="21">
         <v>5</v>
       </c>
       <c r="K6" s="36" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="L6" s="23" t="s">
         <v>11</v>
@@ -3844,7 +3920,7 @@
         <v>11</v>
       </c>
       <c r="T6" s="43" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="U6" s="24" t="s">
         <v>11</v>
@@ -3881,10 +3957,10 @@
         <v>11</v>
       </c>
       <c r="AG6" s="41" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="AH6" s="41" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="AI6" s="26" t="s">
         <v>11</v>
@@ -3909,9 +3985,7 @@
       </c>
     </row>
     <row r="7" spans="1:41" ht="150" x14ac:dyDescent="0.35">
-      <c r="B7" s="66" t="s">
-        <v>18</v>
-      </c>
+      <c r="B7" s="66"/>
       <c r="C7" s="21" t="s">
         <v>30</v>
       </c>
@@ -3928,16 +4002,16 @@
         <v>1</v>
       </c>
       <c r="H7" s="22" t="s">
+        <v>200</v>
+      </c>
+      <c r="I7" s="22" t="s">
         <v>201</v>
-      </c>
-      <c r="I7" s="22" t="s">
-        <v>202</v>
       </c>
       <c r="J7" s="21">
         <v>5</v>
       </c>
       <c r="K7" s="36" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="L7" s="23" t="s">
         <v>11</v>
@@ -3964,7 +4038,7 @@
         <v>11</v>
       </c>
       <c r="T7" s="43" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="U7" s="24" t="s">
         <v>11</v>
@@ -4001,10 +4075,10 @@
         <v>11</v>
       </c>
       <c r="AG7" s="41" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="AH7" s="41" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="AI7" s="26" t="s">
         <v>11</v>
@@ -4029,11 +4103,11 @@
       </c>
     </row>
     <row r="8" spans="1:41" ht="140" x14ac:dyDescent="0.35">
-      <c r="B8" s="66" t="s">
+      <c r="B8" s="63" t="s">
         <v>55</v>
       </c>
       <c r="C8" s="21" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D8" s="21" t="s">
         <v>21</v>
@@ -4042,13 +4116,13 @@
         <v>2</v>
       </c>
       <c r="F8" s="21" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="G8" s="21" t="s">
         <v>1</v>
       </c>
       <c r="H8" s="22" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="I8" s="22" t="s">
         <v>56</v>
@@ -4057,7 +4131,7 @@
         <v>5</v>
       </c>
       <c r="K8" s="36" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="L8" s="23" t="s">
         <v>11</v>
@@ -4084,7 +4158,7 @@
         <v>11</v>
       </c>
       <c r="T8" s="43" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="U8" s="24" t="s">
         <v>11</v>
@@ -4142,18 +4216,18 @@
         <v>11</v>
       </c>
       <c r="AN8" s="41" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="AO8" s="26" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="9" spans="1:41" ht="140" x14ac:dyDescent="0.35">
-      <c r="B9" s="66" t="s">
+      <c r="B9" s="63" t="s">
         <v>57</v>
       </c>
       <c r="C9" s="21" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D9" s="21" t="s">
         <v>21</v>
@@ -4162,13 +4236,13 @@
         <v>2</v>
       </c>
       <c r="F9" s="21" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="G9" s="21" t="s">
         <v>1</v>
       </c>
       <c r="H9" s="22" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="I9" s="22" t="s">
         <v>58</v>
@@ -4177,7 +4251,7 @@
         <v>2</v>
       </c>
       <c r="K9" s="36" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="L9" s="23" t="s">
         <v>11</v>
@@ -4204,7 +4278,7 @@
         <v>11</v>
       </c>
       <c r="T9" s="43" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="U9" s="24" t="s">
         <v>11</v>
@@ -4262,21 +4336,21 @@
         <v>11</v>
       </c>
       <c r="AN9" s="41" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="AO9" s="26" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="10" spans="1:41" ht="70" x14ac:dyDescent="0.35">
-      <c r="B10" s="66" t="s">
+      <c r="B10" s="63" t="s">
         <v>5</v>
       </c>
       <c r="C10" s="21" t="s">
         <v>30</v>
       </c>
       <c r="D10" s="21" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="E10" s="21">
         <v>2</v>
@@ -4289,19 +4363,19 @@
         <v>10</v>
       </c>
       <c r="I10" s="22" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="J10" s="21">
         <v>5</v>
       </c>
       <c r="K10" s="36" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="L10" s="43" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="M10" s="43" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="N10" s="23" t="s">
         <v>11</v>
@@ -4353,19 +4427,19 @@
       </c>
       <c r="AD10" s="25"/>
       <c r="AE10" s="41" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="AF10" s="27" t="s">
         <v>11</v>
       </c>
       <c r="AG10" s="41" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="AH10" s="41" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="AI10" s="41" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="AJ10" s="26" t="s">
         <v>11</v>
@@ -4387,14 +4461,14 @@
       </c>
     </row>
     <row r="11" spans="1:41" ht="70" x14ac:dyDescent="0.35">
-      <c r="B11" s="66" t="s">
+      <c r="B11" s="63" t="s">
         <v>6</v>
       </c>
       <c r="C11" s="21" t="s">
         <v>31</v>
       </c>
       <c r="D11" s="21" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="E11" s="21">
         <v>1</v>
@@ -4413,13 +4487,13 @@
         <v>5</v>
       </c>
       <c r="K11" s="36" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="L11" s="43" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="M11" s="43" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="N11" s="23" t="s">
         <v>11</v>
@@ -4480,7 +4554,7 @@
         <v>11</v>
       </c>
       <c r="AH11" s="41" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="AI11" s="26" t="s">
         <v>11</v>
@@ -4505,14 +4579,14 @@
       </c>
     </row>
     <row r="12" spans="1:41" ht="70" x14ac:dyDescent="0.35">
-      <c r="B12" s="66" t="s">
+      <c r="B12" s="63" t="s">
         <v>8</v>
       </c>
       <c r="C12" s="21" t="s">
         <v>30</v>
       </c>
       <c r="D12" s="21" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="E12" s="21">
         <v>1</v>
@@ -4531,7 +4605,7 @@
         <v>5</v>
       </c>
       <c r="K12" s="36" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="L12" s="23" t="s">
         <v>11</v>
@@ -4540,7 +4614,7 @@
         <v>11</v>
       </c>
       <c r="N12" s="43" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="O12" s="23" t="s">
         <v>11</v>
@@ -4623,14 +4697,14 @@
       </c>
     </row>
     <row r="13" spans="1:41" ht="70" x14ac:dyDescent="0.35">
-      <c r="B13" s="66" t="s">
+      <c r="B13" s="62" t="s">
         <v>0</v>
       </c>
       <c r="C13" s="21" t="s">
         <v>32</v>
       </c>
       <c r="D13" s="21" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="E13" s="21">
         <v>1</v>
@@ -4649,10 +4723,10 @@
         <v>5</v>
       </c>
       <c r="K13" s="36" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="L13" s="43" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="M13" s="23" t="s">
         <v>11</v>
@@ -4707,19 +4781,19 @@
       </c>
       <c r="AD13" s="25"/>
       <c r="AE13" s="41" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="AF13" s="41" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="AG13" s="41" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="AH13" s="41" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="AI13" s="41" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="AJ13" s="26" t="s">
         <v>11</v>
@@ -4741,11 +4815,11 @@
       </c>
     </row>
     <row r="14" spans="1:41" ht="140" x14ac:dyDescent="0.35">
-      <c r="B14" s="66" t="s">
+      <c r="B14" s="63" t="s">
         <v>60</v>
       </c>
       <c r="C14" s="21" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D14" s="21" t="s">
         <v>21</v>
@@ -4754,13 +4828,13 @@
         <v>1</v>
       </c>
       <c r="F14" s="21" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="G14" s="21" t="s">
         <v>1</v>
       </c>
       <c r="H14" s="22" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="I14" s="22" t="s">
         <v>61</v>
@@ -4769,7 +4843,7 @@
         <v>5</v>
       </c>
       <c r="K14" s="36" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="L14" s="24" t="s">
         <v>11</v>
@@ -4790,13 +4864,13 @@
         <v>11</v>
       </c>
       <c r="R14" s="43" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="S14" s="24" t="s">
         <v>11</v>
       </c>
       <c r="T14" s="43" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="U14" s="24" t="s">
         <v>11</v>
@@ -4833,7 +4907,7 @@
         <v>11</v>
       </c>
       <c r="AG14" s="41" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="AH14" s="26" t="s">
         <v>11</v>
@@ -4854,14 +4928,14 @@
         <v>11</v>
       </c>
       <c r="AN14" s="41" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="AO14" s="26" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="15" spans="1:41" ht="140" x14ac:dyDescent="0.35">
-      <c r="B15" s="66" t="s">
+      <c r="B15" s="63" t="s">
         <v>59</v>
       </c>
       <c r="C15" s="21" t="s">
@@ -4874,22 +4948,22 @@
         <v>1</v>
       </c>
       <c r="F15" s="21" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="G15" s="21" t="s">
         <v>1</v>
       </c>
       <c r="H15" s="22" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="I15" s="22" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="J15" s="21">
         <v>5</v>
       </c>
       <c r="K15" s="36" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="L15" s="24" t="s">
         <v>11</v>
@@ -4916,7 +4990,7 @@
         <v>11</v>
       </c>
       <c r="T15" s="43" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="U15" s="24" t="s">
         <v>11</v>
@@ -4953,7 +5027,7 @@
         <v>11</v>
       </c>
       <c r="AG15" s="41" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="AH15" s="26" t="s">
         <v>11</v>
@@ -4974,7 +5048,7 @@
         <v>11</v>
       </c>
       <c r="AN15" s="41" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="AO15" s="26" t="s">
         <v>11</v>
@@ -4982,11 +5056,11 @@
     </row>
     <row r="16" spans="1:41" ht="89" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A16" s="57"/>
-      <c r="B16" s="66" t="s">
+      <c r="B16" s="63" t="s">
         <v>64</v>
       </c>
       <c r="C16" s="21" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D16" s="21" t="s">
         <v>21</v>
@@ -4995,13 +5069,13 @@
         <v>10</v>
       </c>
       <c r="F16" s="21" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="G16" s="21" t="s">
         <v>1</v>
       </c>
       <c r="H16" s="22" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="I16" s="22" t="s">
         <v>71</v>
@@ -5010,7 +5084,7 @@
         <v>2</v>
       </c>
       <c r="K16" s="36" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="L16" s="24" t="s">
         <v>11</v>
@@ -5037,7 +5111,7 @@
         <v>11</v>
       </c>
       <c r="T16" s="43" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="U16" s="24" t="s">
         <v>11</v>
@@ -5103,7 +5177,7 @@
     </row>
     <row r="17" spans="1:41" ht="70" x14ac:dyDescent="0.35">
       <c r="A17" s="58"/>
-      <c r="B17" s="66" t="s">
+      <c r="B17" s="63" t="s">
         <v>62</v>
       </c>
       <c r="C17" s="21" t="s">
@@ -5116,13 +5190,13 @@
         <v>30</v>
       </c>
       <c r="F17" s="21" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="G17" s="21" t="s">
         <v>1</v>
       </c>
       <c r="H17" s="22" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="I17" s="22" t="s">
         <v>63</v>
@@ -5131,7 +5205,7 @@
         <v>2</v>
       </c>
       <c r="K17" s="36" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="L17" s="24" t="s">
         <v>11</v>
@@ -5158,7 +5232,7 @@
         <v>11</v>
       </c>
       <c r="T17" s="43" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="U17" s="24" t="s">
         <v>11</v>
@@ -5224,7 +5298,7 @@
     </row>
     <row r="18" spans="1:41" ht="70" x14ac:dyDescent="0.35">
       <c r="A18" s="22"/>
-      <c r="B18" s="21" t="s">
+      <c r="B18" s="63" t="s">
         <v>68</v>
       </c>
       <c r="C18" s="21" t="s">
@@ -5237,22 +5311,22 @@
         <v>35</v>
       </c>
       <c r="F18" s="21" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="G18" s="21" t="s">
         <v>1</v>
       </c>
       <c r="H18" s="22" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="I18" s="22" t="s">
-        <v>73</v>
+        <v>368</v>
       </c>
       <c r="J18" s="21">
         <v>3</v>
       </c>
       <c r="K18" s="36" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="L18" s="23" t="s">
         <v>11</v>
@@ -5279,7 +5353,7 @@
         <v>11</v>
       </c>
       <c r="T18" s="43" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="U18" s="23" t="s">
         <v>11</v>
@@ -5345,11 +5419,11 @@
     </row>
     <row r="19" spans="1:41" ht="70" x14ac:dyDescent="0.35">
       <c r="A19" s="21"/>
-      <c r="B19" s="21" t="s">
+      <c r="B19" s="63" t="s">
         <v>69</v>
       </c>
       <c r="C19" s="21" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="D19" s="21" t="s">
         <v>24</v>
@@ -5358,13 +5432,13 @@
         <v>12</v>
       </c>
       <c r="F19" s="21" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="G19" s="21" t="s">
         <v>1</v>
       </c>
       <c r="H19" s="22" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="I19" s="22" t="s">
         <v>70</v>
@@ -5373,7 +5447,7 @@
         <v>3</v>
       </c>
       <c r="K19" s="36" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="L19" s="23" t="s">
         <v>11</v>
@@ -5400,7 +5474,7 @@
         <v>11</v>
       </c>
       <c r="T19" s="43" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="U19" s="24" t="s">
         <v>11</v>
@@ -5437,7 +5511,7 @@
         <v>11</v>
       </c>
       <c r="AG19" s="41" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="AH19" s="26" t="s">
         <v>11</v>
@@ -5466,7 +5540,7 @@
     </row>
     <row r="20" spans="1:41" ht="100" x14ac:dyDescent="0.35">
       <c r="A20" s="22"/>
-      <c r="B20" s="66" t="s">
+      <c r="B20" s="63" t="s">
         <v>65</v>
       </c>
       <c r="C20" s="21" t="s">
@@ -5479,13 +5553,13 @@
         <v>5</v>
       </c>
       <c r="F20" s="21" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="G20" s="21" t="s">
         <v>1</v>
       </c>
       <c r="H20" s="22" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
       <c r="I20" s="22" t="s">
         <v>72</v>
@@ -5494,7 +5568,7 @@
         <v>3</v>
       </c>
       <c r="K20" s="36" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="L20" s="24" t="s">
         <v>11</v>
@@ -5582,12 +5656,12 @@
         <v>11</v>
       </c>
       <c r="AO20" s="41" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
     </row>
     <row r="21" spans="1:41" ht="140" x14ac:dyDescent="0.35">
       <c r="A21" s="22"/>
-      <c r="B21" s="66" t="s">
+      <c r="B21" s="63" t="s">
         <v>42</v>
       </c>
       <c r="C21" s="21" t="s">
@@ -5600,13 +5674,13 @@
         <v>2</v>
       </c>
       <c r="F21" s="21" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="G21" s="21" t="s">
         <v>1</v>
       </c>
       <c r="H21" s="22" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="I21" s="22" t="s">
         <v>43</v>
@@ -5615,7 +5689,7 @@
         <v>5</v>
       </c>
       <c r="K21" s="36" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="L21" s="23" t="s">
         <v>11</v>
@@ -5645,19 +5719,19 @@
         <v>11</v>
       </c>
       <c r="U21" s="43" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="V21" s="43" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="W21" s="43" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="X21" s="43" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="Y21" s="43" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="Z21" s="23" t="s">
         <v>11</v>
@@ -5691,13 +5765,13 @@
         <v>11</v>
       </c>
       <c r="AK21" s="41" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="AL21" s="41" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="AM21" s="41" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="AN21" s="26" t="s">
         <v>11</v>
@@ -5708,26 +5782,26 @@
     </row>
     <row r="22" spans="1:41" ht="110" x14ac:dyDescent="0.35">
       <c r="A22" s="22"/>
-      <c r="B22" s="66" t="s">
+      <c r="B22" s="63" t="s">
         <v>52</v>
       </c>
       <c r="C22" s="21" t="s">
         <v>30</v>
       </c>
       <c r="D22" s="21" t="s">
-        <v>369</v>
+        <v>367</v>
       </c>
       <c r="E22" s="21">
         <v>20</v>
       </c>
       <c r="F22" s="21" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="G22" s="21" t="s">
         <v>1</v>
       </c>
       <c r="H22" s="22" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="I22" s="22" t="s">
         <v>53</v>
@@ -5736,7 +5810,7 @@
         <v>1</v>
       </c>
       <c r="K22" s="36" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="L22" s="24" t="s">
         <v>11</v>
@@ -5769,7 +5843,7 @@
         <v>11</v>
       </c>
       <c r="V22" s="43" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="W22" s="24" t="s">
         <v>11</v>
@@ -5781,10 +5855,10 @@
         <v>11</v>
       </c>
       <c r="Z22" s="43" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="AA22" s="43" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="AB22" s="23" t="s">
         <v>11</v>
@@ -5828,14 +5902,14 @@
       </c>
     </row>
     <row r="23" spans="1:41" ht="70" x14ac:dyDescent="0.35">
-      <c r="B23" s="66" t="s">
+      <c r="B23" s="63" t="s">
         <v>33</v>
       </c>
       <c r="C23" s="21" t="s">
         <v>30</v>
       </c>
       <c r="D23" s="21" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="E23" s="21">
         <v>4</v>
@@ -5856,7 +5930,7 @@
         <v>5</v>
       </c>
       <c r="K23" s="36" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="L23" s="23" t="s">
         <v>11</v>
@@ -5868,7 +5942,7 @@
         <v>11</v>
       </c>
       <c r="O23" s="42" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="P23" s="23" t="s">
         <v>11</v>
@@ -5948,7 +6022,7 @@
       </c>
     </row>
     <row r="24" spans="1:41" ht="70" x14ac:dyDescent="0.35">
-      <c r="B24" s="66" t="s">
+      <c r="B24" s="63" t="s">
         <v>17</v>
       </c>
       <c r="C24" s="21" t="s">
@@ -5961,7 +6035,7 @@
         <v>1</v>
       </c>
       <c r="F24" s="21" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="G24" s="21" t="s">
         <v>1</v>
@@ -5976,7 +6050,7 @@
         <v>5</v>
       </c>
       <c r="K24" s="36" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="L24" s="23" t="s">
         <v>11</v>
@@ -5991,16 +6065,16 @@
         <v>11</v>
       </c>
       <c r="P24" s="42" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="Q24" s="42" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="R24" s="42" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="S24" s="42" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="T24" s="24" t="s">
         <v>11</v>
@@ -6034,22 +6108,22 @@
       </c>
       <c r="AD24" s="25"/>
       <c r="AE24" s="41" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="AF24" s="26" t="s">
         <v>11</v>
       </c>
       <c r="AG24" s="41" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="AH24" s="41" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="AI24" s="26" t="s">
         <v>11</v>
       </c>
       <c r="AJ24" s="41" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="AK24" s="26" t="s">
         <v>11</v>
@@ -6075,8 +6149,10 @@
     </row>
   </sheetData>
   <autoFilter ref="A2:AO25" xr:uid="{A7C1F66D-2DBF-4141-9060-E5D01F40CB0A}"/>
-  <mergeCells count="1">
+  <mergeCells count="3">
     <mergeCell ref="C1:D1"/>
+    <mergeCell ref="B4:B5"/>
+    <mergeCell ref="B6:B7"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
@@ -6097,7 +6173,7 @@
   <sheetData>
     <row r="1" spans="2:35" x14ac:dyDescent="0.35">
       <c r="F1" s="16" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="G1" s="16"/>
       <c r="H1" s="16"/>
@@ -6117,7 +6193,7 @@
       <c r="V1" s="16"/>
       <c r="W1" s="16"/>
       <c r="Y1" s="17" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="Z1" s="18"/>
       <c r="AA1" s="18"/>
@@ -6135,7 +6211,7 @@
         <v>2</v>
       </c>
       <c r="C2" s="30" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D2" s="30" t="s">
         <v>27</v>
@@ -6147,7 +6223,7 @@
         <v>15</v>
       </c>
       <c r="G2" s="20" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="H2" s="20" t="s">
         <v>14</v>
@@ -6159,16 +6235,16 @@
         <v>38</v>
       </c>
       <c r="K2" s="20" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="L2" s="32" t="s">
         <v>40</v>
       </c>
       <c r="M2" s="32" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="N2" s="38" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="O2" s="20" t="s">
         <v>44</v>
@@ -6189,32 +6265,32 @@
         <v>54</v>
       </c>
       <c r="U2" s="20" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="V2" s="20" t="s">
+        <v>136</v>
+      </c>
+      <c r="W2" s="20" t="s">
         <v>137</v>
-      </c>
-      <c r="W2" s="20" t="s">
-        <v>138</v>
       </c>
       <c r="X2" s="33"/>
       <c r="Y2" s="20" t="s">
         <v>38</v>
       </c>
       <c r="Z2" s="32" t="s">
+        <v>131</v>
+      </c>
+      <c r="AA2" s="20" t="s">
         <v>132</v>
-      </c>
-      <c r="AA2" s="20" t="s">
-        <v>133</v>
       </c>
       <c r="AB2" s="20" t="s">
         <v>39</v>
       </c>
       <c r="AC2" s="20" t="s">
+        <v>133</v>
+      </c>
+      <c r="AD2" s="32" t="s">
         <v>134</v>
-      </c>
-      <c r="AD2" s="32" t="s">
-        <v>135</v>
       </c>
       <c r="AE2" s="20" t="s">
         <v>49</v>
@@ -6226,10 +6302,10 @@
         <v>51</v>
       </c>
       <c r="AH2" s="38" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="AI2" s="34" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
     </row>
     <row r="3" spans="2:35" x14ac:dyDescent="0.35">
@@ -6237,7 +6313,7 @@
         <v>66</v>
       </c>
       <c r="C3" s="21" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="D3" s="21" t="s">
         <v>21</v>
@@ -6264,7 +6340,7 @@
         <v>11</v>
       </c>
       <c r="L3" s="42" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="M3" s="24" t="s">
         <v>11</v>
@@ -6294,10 +6370,10 @@
         <v>11</v>
       </c>
       <c r="V3" s="42" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="W3" s="42" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="X3" s="25"/>
       <c r="Y3" s="26" t="s">
@@ -6307,7 +6383,7 @@
         <v>11</v>
       </c>
       <c r="AA3" s="41" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="AB3" s="26" t="s">
         <v>11</v>
@@ -6372,7 +6448,7 @@
         <v>11</v>
       </c>
       <c r="N4" s="43" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="O4" s="24" t="s">
         <v>11</v>
@@ -6430,7 +6506,7 @@
         <v>11</v>
       </c>
       <c r="AH4" s="41" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="AI4" s="26" t="s">
         <v>11</v>
@@ -6474,7 +6550,7 @@
         <v>11</v>
       </c>
       <c r="N5" s="43" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="O5" s="24" t="s">
         <v>11</v>
@@ -6532,7 +6608,7 @@
         <v>11</v>
       </c>
       <c r="AH5" s="41" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="AI5" s="26" t="s">
         <v>11</v>
@@ -6576,7 +6652,7 @@
         <v>11</v>
       </c>
       <c r="N6" s="43" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="O6" s="24" t="s">
         <v>11</v>
@@ -6613,10 +6689,10 @@
         <v>11</v>
       </c>
       <c r="AA6" s="41" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="AB6" s="41" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="AC6" s="26" t="s">
         <v>11</v>
@@ -6678,7 +6754,7 @@
         <v>11</v>
       </c>
       <c r="N7" s="43" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="O7" s="24" t="s">
         <v>11</v>
@@ -6715,10 +6791,10 @@
         <v>11</v>
       </c>
       <c r="AA7" s="41" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="AB7" s="41" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="AC7" s="26" t="s">
         <v>11</v>
@@ -6747,7 +6823,7 @@
         <v>55</v>
       </c>
       <c r="C8" s="21" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D8" s="21" t="s">
         <v>21</v>
@@ -6780,7 +6856,7 @@
         <v>11</v>
       </c>
       <c r="N8" s="43" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="O8" s="24" t="s">
         <v>11</v>
@@ -6838,7 +6914,7 @@
         <v>11</v>
       </c>
       <c r="AH8" s="41" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="AI8" s="26" t="s">
         <v>11</v>
@@ -6849,7 +6925,7 @@
         <v>57</v>
       </c>
       <c r="C9" s="21" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D9" s="21" t="s">
         <v>21</v>
@@ -6882,7 +6958,7 @@
         <v>11</v>
       </c>
       <c r="N9" s="43" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="O9" s="24" t="s">
         <v>11</v>
@@ -6940,7 +7016,7 @@
         <v>11</v>
       </c>
       <c r="AH9" s="41" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="AI9" s="26" t="s">
         <v>11</v>
@@ -6954,16 +7030,16 @@
         <v>30</v>
       </c>
       <c r="D10" s="21" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="E10" s="21">
         <v>2</v>
       </c>
       <c r="F10" s="43" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="G10" s="43" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="H10" s="23" t="s">
         <v>11</v>
@@ -7015,19 +7091,19 @@
       </c>
       <c r="X10" s="25"/>
       <c r="Y10" s="41" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="Z10" s="27" t="s">
         <v>11</v>
       </c>
       <c r="AA10" s="41" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="AB10" s="41" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="AC10" s="41" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="AD10" s="26" t="s">
         <v>11</v>
@@ -7056,16 +7132,16 @@
         <v>31</v>
       </c>
       <c r="D11" s="21" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="E11" s="21">
         <v>1</v>
       </c>
       <c r="F11" s="43" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="G11" s="43" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="H11" s="23" t="s">
         <v>11</v>
@@ -7126,7 +7202,7 @@
         <v>11</v>
       </c>
       <c r="AB11" s="41" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="AC11" s="26" t="s">
         <v>11</v>
@@ -7158,7 +7234,7 @@
         <v>30</v>
       </c>
       <c r="D12" s="21" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="E12" s="21">
         <v>1</v>
@@ -7170,7 +7246,7 @@
         <v>11</v>
       </c>
       <c r="H12" s="43" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="I12" s="23" t="s">
         <v>11</v>
@@ -7260,13 +7336,13 @@
         <v>32</v>
       </c>
       <c r="D13" s="21" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="E13" s="21">
         <v>1</v>
       </c>
       <c r="F13" s="43" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="G13" s="23" t="s">
         <v>11</v>
@@ -7321,19 +7397,19 @@
       </c>
       <c r="X13" s="25"/>
       <c r="Y13" s="41" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="Z13" s="41" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="AA13" s="41" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="AB13" s="41" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="AC13" s="41" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="AD13" s="26" t="s">
         <v>11</v>
@@ -7359,7 +7435,7 @@
         <v>60</v>
       </c>
       <c r="C14" s="21" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D14" s="21" t="s">
         <v>21</v>
@@ -7386,13 +7462,13 @@
         <v>11</v>
       </c>
       <c r="L14" s="43" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="M14" s="24" t="s">
         <v>11</v>
       </c>
       <c r="N14" s="43" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="O14" s="24" t="s">
         <v>11</v>
@@ -7429,7 +7505,7 @@
         <v>11</v>
       </c>
       <c r="AA14" s="41" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="AB14" s="26" t="s">
         <v>11</v>
@@ -7450,7 +7526,7 @@
         <v>11</v>
       </c>
       <c r="AH14" s="41" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="AI14" s="26" t="s">
         <v>11</v>
@@ -7494,7 +7570,7 @@
         <v>11</v>
       </c>
       <c r="N15" s="43" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="O15" s="24" t="s">
         <v>11</v>
@@ -7531,7 +7607,7 @@
         <v>11</v>
       </c>
       <c r="AA15" s="41" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="AB15" s="26" t="s">
         <v>11</v>
@@ -7552,7 +7628,7 @@
         <v>11</v>
       </c>
       <c r="AH15" s="41" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="AI15" s="26" t="s">
         <v>11</v>
@@ -7563,7 +7639,7 @@
         <v>64</v>
       </c>
       <c r="C16" s="21" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D16" s="21" t="s">
         <v>21</v>
@@ -7596,7 +7672,7 @@
         <v>11</v>
       </c>
       <c r="N16" s="43" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="O16" s="24" t="s">
         <v>11</v>
@@ -7698,7 +7774,7 @@
         <v>11</v>
       </c>
       <c r="N17" s="43" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="O17" s="24" t="s">
         <v>11</v>
@@ -7800,7 +7876,7 @@
         <v>11</v>
       </c>
       <c r="N18" s="43" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="O18" s="23" t="s">
         <v>11</v>
@@ -7869,7 +7945,7 @@
         <v>69</v>
       </c>
       <c r="C19" s="21" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="D19" s="21" t="s">
         <v>24</v>
@@ -7902,7 +7978,7 @@
         <v>11</v>
       </c>
       <c r="N19" s="43" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="O19" s="24" t="s">
         <v>11</v>
@@ -7939,7 +8015,7 @@
         <v>11</v>
       </c>
       <c r="AA19" s="41" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="AB19" s="26" t="s">
         <v>11</v>
@@ -8065,7 +8141,7 @@
         <v>11</v>
       </c>
       <c r="AI20" s="41" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
     </row>
     <row r="21" spans="2:35" x14ac:dyDescent="0.35">
@@ -8109,19 +8185,19 @@
         <v>11</v>
       </c>
       <c r="O21" s="43" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="P21" s="43" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="Q21" s="43" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="R21" s="43" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="S21" s="43" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="T21" s="23" t="s">
         <v>11</v>
@@ -8155,13 +8231,13 @@
         <v>11</v>
       </c>
       <c r="AE21" s="41" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="AF21" s="41" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="AG21" s="41" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="AH21" s="26" t="s">
         <v>11</v>
@@ -8214,7 +8290,7 @@
         <v>11</v>
       </c>
       <c r="P22" s="43" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="Q22" s="24" t="s">
         <v>11</v>
@@ -8226,10 +8302,10 @@
         <v>11</v>
       </c>
       <c r="T22" s="43" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="U22" s="43" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="V22" s="23" t="s">
         <v>11</v>
@@ -8280,7 +8356,7 @@
         <v>30</v>
       </c>
       <c r="D23" s="21" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="E23" s="21">
         <v>4</v>
@@ -8295,7 +8371,7 @@
         <v>11</v>
       </c>
       <c r="I23" s="42" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="J23" s="23" t="s">
         <v>11</v>
@@ -8400,16 +8476,16 @@
         <v>11</v>
       </c>
       <c r="J24" s="42" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="K24" s="42" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="L24" s="42" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="M24" s="42" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="N24" s="24" t="s">
         <v>11</v>
@@ -8443,22 +8519,22 @@
       </c>
       <c r="X24" s="25"/>
       <c r="Y24" s="41" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="Z24" s="26" t="s">
         <v>11</v>
       </c>
       <c r="AA24" s="41" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="AB24" s="41" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="AC24" s="26" t="s">
         <v>11</v>
       </c>
       <c r="AD24" s="41" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="AE24" s="26" t="s">
         <v>11</v>
@@ -8484,12 +8560,12 @@
     </row>
     <row r="28" spans="2:35" x14ac:dyDescent="0.35">
       <c r="F28" s="16" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="G28" s="16"/>
       <c r="H28" s="16"/>
       <c r="J28" s="17" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
     </row>
     <row r="29" spans="2:35" ht="80" x14ac:dyDescent="0.35">
@@ -8497,7 +8573,7 @@
         <v>2</v>
       </c>
       <c r="C29" s="30" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D29" s="30" t="s">
         <v>27</v>
@@ -8509,14 +8585,14 @@
         <v>40</v>
       </c>
       <c r="G29" s="20" t="s">
+        <v>136</v>
+      </c>
+      <c r="H29" s="20" t="s">
         <v>137</v>
-      </c>
-      <c r="H29" s="20" t="s">
-        <v>138</v>
       </c>
       <c r="I29" s="33"/>
       <c r="J29" s="20" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
     </row>
     <row r="30" spans="2:35" x14ac:dyDescent="0.35">
@@ -8524,7 +8600,7 @@
         <v>66</v>
       </c>
       <c r="C30" s="58" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="D30" s="21" t="s">
         <v>21</v>
@@ -8533,17 +8609,17 @@
         <v>5</v>
       </c>
       <c r="F30" s="42" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="G30" s="42" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="H30" s="42" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="I30" s="25"/>
       <c r="J30" s="41" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
     </row>
     <row r="31" spans="2:35" x14ac:dyDescent="0.35">
@@ -8553,12 +8629,12 @@
     </row>
     <row r="33" spans="2:33" x14ac:dyDescent="0.35">
       <c r="F33" s="16" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="G33" s="16"/>
       <c r="H33" s="16"/>
       <c r="J33" s="17" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="K33" s="18"/>
       <c r="L33" s="19"/>
@@ -8568,7 +8644,7 @@
         <v>2</v>
       </c>
       <c r="C34" s="30" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D34" s="30" t="s">
         <v>27</v>
@@ -8580,20 +8656,20 @@
         <v>15</v>
       </c>
       <c r="G34" s="20" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="H34" s="38" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="I34" s="33"/>
       <c r="J34" s="20" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="K34" s="20" t="s">
         <v>39</v>
       </c>
       <c r="L34" s="38" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
     </row>
     <row r="35" spans="2:33" ht="30" x14ac:dyDescent="0.35">
@@ -8616,7 +8692,7 @@
         <v>11</v>
       </c>
       <c r="H35" s="43" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="I35" s="25"/>
       <c r="J35" s="27" t="s">
@@ -8626,7 +8702,7 @@
         <v>11</v>
       </c>
       <c r="L35" s="41" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
     </row>
     <row r="36" spans="2:33" ht="30" x14ac:dyDescent="0.35">
@@ -8649,7 +8725,7 @@
         <v>11</v>
       </c>
       <c r="H36" s="43" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="I36" s="25"/>
       <c r="J36" s="27" t="s">
@@ -8659,7 +8735,7 @@
         <v>11</v>
       </c>
       <c r="L36" s="41" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
     </row>
     <row r="37" spans="2:33" ht="30" x14ac:dyDescent="0.35">
@@ -8670,16 +8746,16 @@
         <v>31</v>
       </c>
       <c r="D37" s="21" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="E37" s="21">
         <v>1</v>
       </c>
       <c r="F37" s="43" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="G37" s="43" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="H37" s="23" t="s">
         <v>11</v>
@@ -8689,7 +8765,7 @@
         <v>11</v>
       </c>
       <c r="K37" s="41" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="L37" s="26" t="s">
         <v>11</v>
@@ -8715,7 +8791,7 @@
         <v>11</v>
       </c>
       <c r="H38" s="43" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="I38" s="25"/>
       <c r="J38" s="26" t="s">
@@ -8733,7 +8809,7 @@
         <v>69</v>
       </c>
       <c r="C39" s="60" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="D39" s="21" t="s">
         <v>24</v>
@@ -8748,11 +8824,11 @@
         <v>11</v>
       </c>
       <c r="H39" s="43" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="I39" s="25"/>
       <c r="J39" s="41" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="K39" s="26" t="s">
         <v>11</v>
@@ -8769,7 +8845,7 @@
     </row>
     <row r="42" spans="2:33" x14ac:dyDescent="0.35">
       <c r="F42" s="16" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="G42" s="16"/>
       <c r="H42" s="16"/>
@@ -8787,7 +8863,7 @@
       <c r="T42" s="16"/>
       <c r="U42" s="16"/>
       <c r="W42" s="17" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="X42" s="18"/>
       <c r="Y42" s="18"/>
@@ -8805,7 +8881,7 @@
         <v>2</v>
       </c>
       <c r="C43" s="30" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D43" s="30" t="s">
         <v>27</v>
@@ -8817,7 +8893,7 @@
         <v>15</v>
       </c>
       <c r="G43" s="20" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="H43" s="20" t="s">
         <v>14</v>
@@ -8829,16 +8905,16 @@
         <v>38</v>
       </c>
       <c r="K43" s="20" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="L43" s="32" t="s">
         <v>40</v>
       </c>
       <c r="M43" s="32" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="N43" s="38" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="O43" s="20" t="s">
         <v>44</v>
@@ -8859,26 +8935,26 @@
         <v>54</v>
       </c>
       <c r="U43" s="20" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="V43" s="33"/>
       <c r="W43" s="20" t="s">
         <v>38</v>
       </c>
       <c r="X43" s="32" t="s">
+        <v>131</v>
+      </c>
+      <c r="Y43" s="20" t="s">
         <v>132</v>
-      </c>
-      <c r="Y43" s="20" t="s">
-        <v>133</v>
       </c>
       <c r="Z43" s="20" t="s">
         <v>39</v>
       </c>
       <c r="AA43" s="20" t="s">
+        <v>133</v>
+      </c>
+      <c r="AB43" s="32" t="s">
         <v>134</v>
-      </c>
-      <c r="AB43" s="32" t="s">
-        <v>135</v>
       </c>
       <c r="AC43" s="20" t="s">
         <v>49</v>
@@ -8890,10 +8966,10 @@
         <v>51</v>
       </c>
       <c r="AF43" s="38" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="AG43" s="34" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
     </row>
     <row r="44" spans="2:33" ht="20" x14ac:dyDescent="0.35">
@@ -8934,7 +9010,7 @@
         <v>11</v>
       </c>
       <c r="N44" s="43" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="O44" s="24" t="s">
         <v>11</v>
@@ -8965,10 +9041,10 @@
         <v>11</v>
       </c>
       <c r="Y44" s="41" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="Z44" s="41" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="AA44" s="26" t="s">
         <v>11</v>
@@ -9030,7 +9106,7 @@
         <v>11</v>
       </c>
       <c r="N45" s="43" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="O45" s="24" t="s">
         <v>11</v>
@@ -9061,10 +9137,10 @@
         <v>11</v>
       </c>
       <c r="Y45" s="41" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="Z45" s="41" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="AA45" s="26" t="s">
         <v>11</v>
@@ -9096,16 +9172,16 @@
         <v>30</v>
       </c>
       <c r="D46" s="21" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="E46" s="21">
         <v>2</v>
       </c>
       <c r="F46" s="43" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="G46" s="43" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="H46" s="23" t="s">
         <v>11</v>
@@ -9151,19 +9227,19 @@
       </c>
       <c r="V46" s="25"/>
       <c r="W46" s="41" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="X46" s="27" t="s">
         <v>11</v>
       </c>
       <c r="Y46" s="41" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="Z46" s="41" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="AA46" s="41" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="AB46" s="26" t="s">
         <v>11</v>
@@ -9192,7 +9268,7 @@
         <v>30</v>
       </c>
       <c r="D47" s="21" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="E47" s="21">
         <v>1</v>
@@ -9204,7 +9280,7 @@
         <v>11</v>
       </c>
       <c r="H47" s="43" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="I47" s="23" t="s">
         <v>11</v>
@@ -9318,7 +9394,7 @@
         <v>11</v>
       </c>
       <c r="N48" s="43" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="O48" s="24" t="s">
         <v>11</v>
@@ -9349,7 +9425,7 @@
         <v>11</v>
       </c>
       <c r="Y48" s="41" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="Z48" s="26" t="s">
         <v>11</v>
@@ -9370,7 +9446,7 @@
         <v>11</v>
       </c>
       <c r="AF48" s="41" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="AG48" s="26" t="s">
         <v>11</v>
@@ -9414,7 +9490,7 @@
         <v>11</v>
       </c>
       <c r="N49" s="43" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="O49" s="24" t="s">
         <v>11</v>
@@ -9565,7 +9641,7 @@
         <v>11</v>
       </c>
       <c r="AG50" s="41" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
     </row>
     <row r="51" spans="2:33" x14ac:dyDescent="0.35">
@@ -9609,19 +9685,19 @@
         <v>11</v>
       </c>
       <c r="O51" s="43" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="P51" s="43" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="Q51" s="43" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="R51" s="43" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="S51" s="43" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="T51" s="23" t="s">
         <v>11</v>
@@ -9649,13 +9725,13 @@
         <v>11</v>
       </c>
       <c r="AC51" s="41" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="AD51" s="41" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="AE51" s="41" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="AF51" s="26" t="s">
         <v>11</v>
@@ -9708,7 +9784,7 @@
         <v>11</v>
       </c>
       <c r="P52" s="43" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="Q52" s="24" t="s">
         <v>11</v>
@@ -9720,10 +9796,10 @@
         <v>11</v>
       </c>
       <c r="T52" s="43" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="U52" s="43" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="V52" s="25"/>
       <c r="W52" s="26" t="s">
@@ -9768,7 +9844,7 @@
         <v>30</v>
       </c>
       <c r="D53" s="21" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="E53" s="21">
         <v>4</v>
@@ -9783,7 +9859,7 @@
         <v>11</v>
       </c>
       <c r="I53" s="42" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="J53" s="23" t="s">
         <v>11</v>
@@ -9882,16 +9958,16 @@
         <v>11</v>
       </c>
       <c r="J54" s="42" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="K54" s="42" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="L54" s="42" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="M54" s="42" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="N54" s="24" t="s">
         <v>11</v>
@@ -9919,22 +9995,22 @@
       </c>
       <c r="V54" s="25"/>
       <c r="W54" s="41" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="X54" s="26" t="s">
         <v>11</v>
       </c>
       <c r="Y54" s="41" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="Z54" s="41" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="AA54" s="26" t="s">
         <v>11</v>
       </c>
       <c r="AB54" s="41" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="AC54" s="26" t="s">
         <v>11</v>
@@ -9960,10 +10036,10 @@
     </row>
     <row r="57" spans="2:33" x14ac:dyDescent="0.35">
       <c r="F57" s="16" t="s">
+        <v>129</v>
+      </c>
+      <c r="H57" s="17" t="s">
         <v>130</v>
-      </c>
-      <c r="H57" s="17" t="s">
-        <v>131</v>
       </c>
       <c r="I57" s="18"/>
       <c r="J57" s="18"/>
@@ -9975,7 +10051,7 @@
         <v>2</v>
       </c>
       <c r="C58" s="30" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D58" s="30" t="s">
         <v>27</v>
@@ -9991,16 +10067,16 @@
         <v>38</v>
       </c>
       <c r="I58" s="32" t="s">
+        <v>131</v>
+      </c>
+      <c r="J58" s="20" t="s">
         <v>132</v>
-      </c>
-      <c r="J58" s="20" t="s">
-        <v>133</v>
       </c>
       <c r="K58" s="20" t="s">
         <v>39</v>
       </c>
       <c r="L58" s="20" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
     </row>
     <row r="59" spans="2:33" ht="20" x14ac:dyDescent="0.35">
@@ -10011,29 +10087,29 @@
         <v>32</v>
       </c>
       <c r="D59" s="21" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="E59" s="21">
         <v>1</v>
       </c>
       <c r="F59" s="43" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="G59" s="25"/>
       <c r="H59" s="41" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="I59" s="41" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="J59" s="41" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="K59" s="41" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="L59" s="41" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
     </row>
     <row r="60" spans="2:33" x14ac:dyDescent="0.35">
@@ -10043,11 +10119,11 @@
     </row>
     <row r="62" spans="2:33" x14ac:dyDescent="0.35">
       <c r="F62" s="16" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="G62" s="16"/>
       <c r="I62" s="17" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="J62" s="19"/>
     </row>
@@ -10056,7 +10132,7 @@
         <v>2</v>
       </c>
       <c r="C63" s="30" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D63" s="30" t="s">
         <v>27</v>
@@ -10068,14 +10144,14 @@
         <v>40</v>
       </c>
       <c r="G63" s="38" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="H63" s="33"/>
       <c r="I63" s="20" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="J63" s="38" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
     </row>
     <row r="64" spans="2:33" ht="20" x14ac:dyDescent="0.35">
@@ -10083,7 +10159,7 @@
         <v>55</v>
       </c>
       <c r="C64" s="58" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D64" s="21" t="s">
         <v>21</v>
@@ -10095,14 +10171,14 @@
         <v>11</v>
       </c>
       <c r="G64" s="43" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="H64" s="25"/>
       <c r="I64" s="26" t="s">
         <v>11</v>
       </c>
       <c r="J64" s="41" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
     </row>
     <row r="65" spans="2:10" ht="20" x14ac:dyDescent="0.35">
@@ -10110,7 +10186,7 @@
         <v>57</v>
       </c>
       <c r="C65" s="58" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D65" s="21" t="s">
         <v>21</v>
@@ -10122,14 +10198,14 @@
         <v>11</v>
       </c>
       <c r="G65" s="43" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="H65" s="25"/>
       <c r="I65" s="26" t="s">
         <v>11</v>
       </c>
       <c r="J65" s="41" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
     </row>
     <row r="66" spans="2:10" ht="20" x14ac:dyDescent="0.35">
@@ -10137,7 +10213,7 @@
         <v>60</v>
       </c>
       <c r="C66" s="58" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D66" s="21" t="s">
         <v>21</v>
@@ -10146,17 +10222,17 @@
         <v>1</v>
       </c>
       <c r="F66" s="43" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="G66" s="43" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="H66" s="25"/>
       <c r="I66" s="41" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="J66" s="41" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
     </row>
     <row r="67" spans="2:10" ht="20" x14ac:dyDescent="0.35">
@@ -10164,7 +10240,7 @@
         <v>64</v>
       </c>
       <c r="C67" s="58" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D67" s="21" t="s">
         <v>21</v>
@@ -10176,7 +10252,7 @@
         <v>11</v>
       </c>
       <c r="G67" s="43" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="H67" s="25"/>
       <c r="I67" s="26" t="s">
@@ -10210,7 +10286,7 @@
   <sheetData>
     <row r="1" spans="2:35" x14ac:dyDescent="0.35">
       <c r="F1" s="16" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="G1" s="16"/>
       <c r="H1" s="16"/>
@@ -10230,7 +10306,7 @@
       <c r="V1" s="16"/>
       <c r="W1" s="16"/>
       <c r="Y1" s="17" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="Z1" s="18"/>
       <c r="AA1" s="18"/>
@@ -10248,7 +10324,7 @@
         <v>2</v>
       </c>
       <c r="C2" s="30" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D2" s="30" t="s">
         <v>27</v>
@@ -10260,7 +10336,7 @@
         <v>15</v>
       </c>
       <c r="G2" s="20" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="H2" s="20" t="s">
         <v>14</v>
@@ -10272,16 +10348,16 @@
         <v>38</v>
       </c>
       <c r="K2" s="20" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="L2" s="32" t="s">
         <v>40</v>
       </c>
       <c r="M2" s="32" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="N2" s="38" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="O2" s="20" t="s">
         <v>44</v>
@@ -10302,32 +10378,32 @@
         <v>54</v>
       </c>
       <c r="U2" s="20" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="V2" s="20" t="s">
+        <v>136</v>
+      </c>
+      <c r="W2" s="20" t="s">
         <v>137</v>
-      </c>
-      <c r="W2" s="20" t="s">
-        <v>138</v>
       </c>
       <c r="X2" s="33"/>
       <c r="Y2" s="20" t="s">
         <v>38</v>
       </c>
       <c r="Z2" s="32" t="s">
+        <v>131</v>
+      </c>
+      <c r="AA2" s="20" t="s">
         <v>132</v>
-      </c>
-      <c r="AA2" s="20" t="s">
-        <v>133</v>
       </c>
       <c r="AB2" s="20" t="s">
         <v>39</v>
       </c>
       <c r="AC2" s="20" t="s">
+        <v>133</v>
+      </c>
+      <c r="AD2" s="32" t="s">
         <v>134</v>
-      </c>
-      <c r="AD2" s="32" t="s">
-        <v>135</v>
       </c>
       <c r="AE2" s="20" t="s">
         <v>49</v>
@@ -10339,10 +10415,10 @@
         <v>51</v>
       </c>
       <c r="AH2" s="38" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="AI2" s="34" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
     </row>
     <row r="3" spans="2:35" hidden="1" x14ac:dyDescent="0.35">
@@ -10350,7 +10426,7 @@
         <v>66</v>
       </c>
       <c r="C3" s="21" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="D3" s="21" t="s">
         <v>21</v>
@@ -10377,7 +10453,7 @@
         <v>11</v>
       </c>
       <c r="L3" s="42" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="M3" s="24" t="s">
         <v>11</v>
@@ -10407,10 +10483,10 @@
         <v>11</v>
       </c>
       <c r="V3" s="42" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="W3" s="42" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="X3" s="25"/>
       <c r="Y3" s="26" t="s">
@@ -10420,7 +10496,7 @@
         <v>11</v>
       </c>
       <c r="AA3" s="41" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="AB3" s="26" t="s">
         <v>11</v>
@@ -10485,7 +10561,7 @@
         <v>11</v>
       </c>
       <c r="N4" s="43" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="O4" s="24" t="s">
         <v>11</v>
@@ -10543,7 +10619,7 @@
         <v>11</v>
       </c>
       <c r="AH4" s="41" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="AI4" s="26" t="s">
         <v>11</v>
@@ -10587,7 +10663,7 @@
         <v>11</v>
       </c>
       <c r="N5" s="43" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="O5" s="24" t="s">
         <v>11</v>
@@ -10645,7 +10721,7 @@
         <v>11</v>
       </c>
       <c r="AH5" s="41" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="AI5" s="26" t="s">
         <v>11</v>
@@ -10689,7 +10765,7 @@
         <v>11</v>
       </c>
       <c r="N6" s="43" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="O6" s="24" t="s">
         <v>11</v>
@@ -10726,10 +10802,10 @@
         <v>11</v>
       </c>
       <c r="AA6" s="41" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="AB6" s="41" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="AC6" s="26" t="s">
         <v>11</v>
@@ -10791,7 +10867,7 @@
         <v>11</v>
       </c>
       <c r="N7" s="43" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="O7" s="24" t="s">
         <v>11</v>
@@ -10828,10 +10904,10 @@
         <v>11</v>
       </c>
       <c r="AA7" s="41" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="AB7" s="41" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="AC7" s="26" t="s">
         <v>11</v>
@@ -10860,7 +10936,7 @@
         <v>55</v>
       </c>
       <c r="C8" s="21" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D8" s="21" t="s">
         <v>21</v>
@@ -10893,7 +10969,7 @@
         <v>11</v>
       </c>
       <c r="N8" s="43" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="O8" s="24" t="s">
         <v>11</v>
@@ -10951,7 +11027,7 @@
         <v>11</v>
       </c>
       <c r="AH8" s="41" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="AI8" s="26" t="s">
         <v>11</v>
@@ -10962,7 +11038,7 @@
         <v>57</v>
       </c>
       <c r="C9" s="21" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D9" s="21" t="s">
         <v>21</v>
@@ -10995,7 +11071,7 @@
         <v>11</v>
       </c>
       <c r="N9" s="43" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="O9" s="24" t="s">
         <v>11</v>
@@ -11053,7 +11129,7 @@
         <v>11</v>
       </c>
       <c r="AH9" s="41" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="AI9" s="26" t="s">
         <v>11</v>
@@ -11067,16 +11143,16 @@
         <v>30</v>
       </c>
       <c r="D10" s="21" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="E10" s="21">
         <v>2</v>
       </c>
       <c r="F10" s="43" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="G10" s="43" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="H10" s="23" t="s">
         <v>11</v>
@@ -11128,19 +11204,19 @@
       </c>
       <c r="X10" s="25"/>
       <c r="Y10" s="41" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="Z10" s="27" t="s">
         <v>11</v>
       </c>
       <c r="AA10" s="41" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="AB10" s="41" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="AC10" s="41" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="AD10" s="26" t="s">
         <v>11</v>
@@ -11169,16 +11245,16 @@
         <v>31</v>
       </c>
       <c r="D11" s="21" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="E11" s="21">
         <v>1</v>
       </c>
       <c r="F11" s="43" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="G11" s="43" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="H11" s="23" t="s">
         <v>11</v>
@@ -11239,7 +11315,7 @@
         <v>11</v>
       </c>
       <c r="AB11" s="41" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="AC11" s="26" t="s">
         <v>11</v>
@@ -11271,7 +11347,7 @@
         <v>30</v>
       </c>
       <c r="D12" s="21" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="E12" s="21">
         <v>1</v>
@@ -11283,7 +11359,7 @@
         <v>11</v>
       </c>
       <c r="H12" s="43" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="I12" s="23" t="s">
         <v>11</v>
@@ -11373,13 +11449,13 @@
         <v>32</v>
       </c>
       <c r="D13" s="21" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="E13" s="21">
         <v>1</v>
       </c>
       <c r="F13" s="43" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="G13" s="23" t="s">
         <v>11</v>
@@ -11434,19 +11510,19 @@
       </c>
       <c r="X13" s="25"/>
       <c r="Y13" s="41" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="Z13" s="41" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="AA13" s="41" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="AB13" s="41" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="AC13" s="41" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="AD13" s="26" t="s">
         <v>11</v>
@@ -11472,7 +11548,7 @@
         <v>60</v>
       </c>
       <c r="C14" s="21" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D14" s="21" t="s">
         <v>21</v>
@@ -11499,13 +11575,13 @@
         <v>11</v>
       </c>
       <c r="L14" s="43" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="M14" s="24" t="s">
         <v>11</v>
       </c>
       <c r="N14" s="43" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="O14" s="24" t="s">
         <v>11</v>
@@ -11542,7 +11618,7 @@
         <v>11</v>
       </c>
       <c r="AA14" s="41" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="AB14" s="26" t="s">
         <v>11</v>
@@ -11563,7 +11639,7 @@
         <v>11</v>
       </c>
       <c r="AH14" s="41" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="AI14" s="26" t="s">
         <v>11</v>
@@ -11607,7 +11683,7 @@
         <v>11</v>
       </c>
       <c r="N15" s="43" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="O15" s="24" t="s">
         <v>11</v>
@@ -11644,7 +11720,7 @@
         <v>11</v>
       </c>
       <c r="AA15" s="41" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="AB15" s="26" t="s">
         <v>11</v>
@@ -11665,7 +11741,7 @@
         <v>11</v>
       </c>
       <c r="AH15" s="41" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="AI15" s="26" t="s">
         <v>11</v>
@@ -11676,7 +11752,7 @@
         <v>64</v>
       </c>
       <c r="C16" s="21" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D16" s="21" t="s">
         <v>21</v>
@@ -11709,7 +11785,7 @@
         <v>11</v>
       </c>
       <c r="N16" s="43" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="O16" s="24" t="s">
         <v>11</v>
@@ -11811,7 +11887,7 @@
         <v>11</v>
       </c>
       <c r="N17" s="43" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="O17" s="24" t="s">
         <v>11</v>
@@ -11913,7 +11989,7 @@
         <v>11</v>
       </c>
       <c r="N18" s="43" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="O18" s="23" t="s">
         <v>11</v>
@@ -11982,7 +12058,7 @@
         <v>69</v>
       </c>
       <c r="C19" s="21" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="D19" s="21" t="s">
         <v>24</v>
@@ -12015,7 +12091,7 @@
         <v>11</v>
       </c>
       <c r="N19" s="43" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="O19" s="24" t="s">
         <v>11</v>
@@ -12052,7 +12128,7 @@
         <v>11</v>
       </c>
       <c r="AA19" s="41" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="AB19" s="26" t="s">
         <v>11</v>
@@ -12178,7 +12254,7 @@
         <v>11</v>
       </c>
       <c r="AI20" s="41" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
     </row>
     <row r="21" spans="2:35" ht="20" hidden="1" x14ac:dyDescent="0.35">
@@ -12222,19 +12298,19 @@
         <v>11</v>
       </c>
       <c r="O21" s="43" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="P21" s="43" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="Q21" s="43" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="R21" s="43" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="S21" s="43" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="T21" s="23" t="s">
         <v>11</v>
@@ -12268,13 +12344,13 @@
         <v>11</v>
       </c>
       <c r="AE21" s="41" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="AF21" s="41" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="AG21" s="41" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="AH21" s="26" t="s">
         <v>11</v>
@@ -12327,7 +12403,7 @@
         <v>11</v>
       </c>
       <c r="P22" s="43" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="Q22" s="24" t="s">
         <v>11</v>
@@ -12339,10 +12415,10 @@
         <v>11</v>
       </c>
       <c r="T22" s="43" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="U22" s="43" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="V22" s="23" t="s">
         <v>11</v>
@@ -12393,7 +12469,7 @@
         <v>30</v>
       </c>
       <c r="D23" s="21" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="E23" s="21">
         <v>4</v>
@@ -12408,7 +12484,7 @@
         <v>11</v>
       </c>
       <c r="I23" s="42" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="J23" s="23" t="s">
         <v>11</v>
@@ -12513,16 +12589,16 @@
         <v>11</v>
       </c>
       <c r="J24" s="42" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="K24" s="42" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="L24" s="42" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="M24" s="42" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="N24" s="24" t="s">
         <v>11</v>
@@ -12556,22 +12632,22 @@
       </c>
       <c r="X24" s="25"/>
       <c r="Y24" s="41" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="Z24" s="26" t="s">
         <v>11</v>
       </c>
       <c r="AA24" s="41" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="AB24" s="41" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="AC24" s="26" t="s">
         <v>11</v>
       </c>
       <c r="AD24" s="41" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="AE24" s="26" t="s">
         <v>11</v>
@@ -12623,12 +12699,12 @@
   <sheetData>
     <row r="2" spans="2:11" x14ac:dyDescent="0.35">
       <c r="F2" s="16" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="G2" s="16"/>
       <c r="H2" s="16"/>
       <c r="J2" s="17" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="K2" s="19"/>
     </row>
@@ -12637,7 +12713,7 @@
         <v>2</v>
       </c>
       <c r="C3" s="30" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D3" s="30" t="s">
         <v>27</v>
@@ -12649,17 +12725,17 @@
         <v>15</v>
       </c>
       <c r="G3" s="20" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="H3" s="38" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="I3" s="33"/>
       <c r="J3" s="20" t="s">
         <v>39</v>
       </c>
       <c r="K3" s="38" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
     </row>
     <row r="4" spans="2:11" ht="30" x14ac:dyDescent="0.35">
@@ -12682,14 +12758,14 @@
         <v>11</v>
       </c>
       <c r="H4" s="43" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="I4" s="25"/>
       <c r="J4" s="27" t="s">
         <v>11</v>
       </c>
       <c r="K4" s="41" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
     </row>
     <row r="5" spans="2:11" ht="30" x14ac:dyDescent="0.35">
@@ -12712,14 +12788,14 @@
         <v>11</v>
       </c>
       <c r="H5" s="43" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="I5" s="25"/>
       <c r="J5" s="27" t="s">
         <v>11</v>
       </c>
       <c r="K5" s="41" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
     </row>
     <row r="6" spans="2:11" ht="30" x14ac:dyDescent="0.35">
@@ -12730,23 +12806,23 @@
         <v>31</v>
       </c>
       <c r="D6" s="21" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="E6" s="21">
         <v>1</v>
       </c>
       <c r="F6" s="43" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="G6" s="43" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="H6" s="23" t="s">
         <v>11</v>
       </c>
       <c r="I6" s="25"/>
       <c r="J6" s="41" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="K6" s="26" t="s">
         <v>11</v>
@@ -12772,7 +12848,7 @@
         <v>11</v>
       </c>
       <c r="H7" s="43" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="I7" s="25"/>
       <c r="J7" s="26" t="s">
@@ -12797,7 +12873,7 @@
   <sheetData>
     <row r="1" spans="1:1" ht="23" x14ac:dyDescent="0.35">
       <c r="A1" s="46" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.35">
@@ -12805,52 +12881,52 @@
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A3" s="48" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A4" s="48" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A5" s="48" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A6" s="48" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A7" s="48" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
     </row>
     <row r="8" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A8" s="48" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
     </row>
     <row r="9" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A9" s="48" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
     </row>
     <row r="10" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A10" s="48" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
     </row>
     <row r="11" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A11" s="48" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
     </row>
     <row r="12" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A12" s="48" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
     </row>
     <row r="13" spans="1:1" x14ac:dyDescent="0.35">
@@ -12861,7 +12937,7 @@
     </row>
     <row r="15" spans="1:1" ht="23" x14ac:dyDescent="0.35">
       <c r="A15" s="46" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
     </row>
     <row r="16" spans="1:1" x14ac:dyDescent="0.35">
@@ -12869,57 +12945,57 @@
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A17" s="48" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
     </row>
     <row r="18" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A18" s="48" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
     </row>
     <row r="19" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A19" s="48" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
     </row>
     <row r="20" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A20" s="48" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
     </row>
     <row r="21" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A21" s="48" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
     </row>
     <row r="22" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A22" s="48" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
     </row>
     <row r="23" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A23" s="48" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
     </row>
     <row r="24" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A24" s="48" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
     </row>
     <row r="25" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A25" s="48" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
     </row>
     <row r="26" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A26" s="48" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
     </row>
     <row r="27" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A27" s="48" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
     </row>
     <row r="28" spans="1:1" x14ac:dyDescent="0.35">
@@ -12933,7 +13009,7 @@
     </row>
     <row r="31" spans="1:1" ht="23" x14ac:dyDescent="0.35">
       <c r="A31" s="46" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
     </row>
     <row r="32" spans="1:1" x14ac:dyDescent="0.35">
@@ -12941,42 +13017,42 @@
     </row>
     <row r="33" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A33" s="48" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
     </row>
     <row r="34" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A34" s="48" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
     </row>
     <row r="35" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A35" s="48" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
     </row>
     <row r="36" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A36" s="48" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
     </row>
     <row r="37" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A37" s="48" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
     </row>
     <row r="38" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A38" s="48" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
     </row>
     <row r="39" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A39" s="48" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
     </row>
     <row r="40" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A40" s="48" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
     </row>
     <row r="41" spans="1:1" x14ac:dyDescent="0.35">
@@ -12990,7 +13066,7 @@
     </row>
     <row r="44" spans="1:1" ht="23" x14ac:dyDescent="0.35">
       <c r="A44" s="46" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
     </row>
     <row r="45" spans="1:1" x14ac:dyDescent="0.35">
@@ -12998,47 +13074,47 @@
     </row>
     <row r="46" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A46" s="48" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
     </row>
     <row r="47" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A47" s="48" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
     </row>
     <row r="48" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A48" s="48" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
     </row>
     <row r="49" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A49" s="48" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
     </row>
     <row r="50" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A50" s="48" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
     </row>
     <row r="51" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A51" s="48" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
     </row>
     <row r="52" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A52" s="48" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
     </row>
     <row r="53" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A53" s="48" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
     </row>
     <row r="54" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A54" s="48" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
     </row>
     <row r="55" spans="1:1" x14ac:dyDescent="0.35">
@@ -13052,7 +13128,7 @@
     </row>
     <row r="58" spans="1:1" ht="23" x14ac:dyDescent="0.35">
       <c r="A58" s="46" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
     </row>
     <row r="59" spans="1:1" x14ac:dyDescent="0.35">
@@ -13060,52 +13136,52 @@
     </row>
     <row r="60" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A60" s="48" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
     </row>
     <row r="61" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A61" s="48" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
     </row>
     <row r="62" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A62" s="48" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
     </row>
     <row r="63" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A63" s="48" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
     </row>
     <row r="64" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A64" s="48" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
     </row>
     <row r="65" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A65" s="48" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
     </row>
     <row r="66" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A66" s="48" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
     </row>
     <row r="67" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A67" s="48" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
     </row>
     <row r="68" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A68" s="48" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
     </row>
     <row r="69" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A69" s="48" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
     </row>
     <row r="70" spans="1:1" x14ac:dyDescent="0.35">
@@ -13119,7 +13195,7 @@
     </row>
     <row r="73" spans="1:1" ht="23" x14ac:dyDescent="0.35">
       <c r="A73" s="46" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
     </row>
     <row r="74" spans="1:1" x14ac:dyDescent="0.35">
@@ -13127,47 +13203,47 @@
     </row>
     <row r="75" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A75" s="48" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
     </row>
     <row r="76" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A76" s="48" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
     </row>
     <row r="77" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A77" s="48" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
     </row>
     <row r="78" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A78" s="48" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
     </row>
     <row r="79" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A79" s="48" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
     </row>
     <row r="80" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A80" s="48" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
     </row>
     <row r="81" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A81" s="48" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
     </row>
     <row r="82" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A82" s="48" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
     </row>
     <row r="83" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A83" s="48" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
     </row>
     <row r="84" spans="1:1" x14ac:dyDescent="0.35">
@@ -13181,7 +13257,7 @@
     </row>
     <row r="87" spans="1:1" ht="23" x14ac:dyDescent="0.35">
       <c r="A87" s="46" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
     </row>
     <row r="88" spans="1:1" x14ac:dyDescent="0.35">
@@ -13189,52 +13265,52 @@
     </row>
     <row r="89" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A89" s="48" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
     </row>
     <row r="90" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A90" s="48" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
     </row>
     <row r="91" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A91" s="48" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
     </row>
     <row r="92" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A92" s="48" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
     </row>
     <row r="93" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A93" s="48" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
     </row>
     <row r="94" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A94" s="48" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
     </row>
     <row r="95" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A95" s="48" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
     </row>
     <row r="96" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A96" s="48" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
     </row>
     <row r="97" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A97" s="48" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
     </row>
     <row r="98" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A98" s="48" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
     </row>
   </sheetData>
@@ -13269,13 +13345,13 @@
       <c r="D1" s="26" t="s">
         <v>16</v>
       </c>
-      <c r="F1" s="64" t="s">
-        <v>240</v>
-      </c>
-      <c r="G1" s="64"/>
-      <c r="H1" s="64"/>
-      <c r="I1" s="64"/>
-      <c r="J1" s="64"/>
+      <c r="F1" s="68" t="s">
+        <v>239</v>
+      </c>
+      <c r="G1" s="68"/>
+      <c r="H1" s="68"/>
+      <c r="I1" s="68"/>
+      <c r="J1" s="68"/>
     </row>
     <row r="2" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B2" s="39" t="s">
@@ -13287,11 +13363,11 @@
       <c r="D2" s="26" t="s">
         <v>24</v>
       </c>
-      <c r="F2" s="64"/>
-      <c r="G2" s="64"/>
-      <c r="H2" s="64"/>
-      <c r="I2" s="64"/>
-      <c r="J2" s="64"/>
+      <c r="F2" s="68"/>
+      <c r="G2" s="68"/>
+      <c r="H2" s="68"/>
+      <c r="I2" s="68"/>
+      <c r="J2" s="68"/>
     </row>
     <row r="3" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B3" s="39" t="s">
@@ -13303,11 +13379,11 @@
       <c r="D3" s="26" t="s">
         <v>16</v>
       </c>
-      <c r="F3" s="64"/>
-      <c r="G3" s="64"/>
-      <c r="H3" s="64"/>
-      <c r="I3" s="64"/>
-      <c r="J3" s="64"/>
+      <c r="F3" s="68"/>
+      <c r="G3" s="68"/>
+      <c r="H3" s="68"/>
+      <c r="I3" s="68"/>
+      <c r="J3" s="68"/>
     </row>
     <row r="4" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B4" s="39" t="s">
@@ -13319,11 +13395,11 @@
       <c r="D4" s="26" t="s">
         <v>21</v>
       </c>
-      <c r="F4" s="64"/>
-      <c r="G4" s="64"/>
-      <c r="H4" s="64"/>
-      <c r="I4" s="64"/>
-      <c r="J4" s="64"/>
+      <c r="F4" s="68"/>
+      <c r="G4" s="68"/>
+      <c r="H4" s="68"/>
+      <c r="I4" s="68"/>
+      <c r="J4" s="68"/>
     </row>
     <row r="5" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B5" s="39" t="s">
@@ -13335,11 +13411,11 @@
       <c r="D5" s="26" t="s">
         <v>21</v>
       </c>
-      <c r="F5" s="64"/>
-      <c r="G5" s="64"/>
-      <c r="H5" s="64"/>
-      <c r="I5" s="64"/>
-      <c r="J5" s="64"/>
+      <c r="F5" s="68"/>
+      <c r="G5" s="68"/>
+      <c r="H5" s="68"/>
+      <c r="I5" s="68"/>
+      <c r="J5" s="68"/>
     </row>
     <row r="6" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B6" s="39" t="s">
@@ -13351,11 +13427,11 @@
       <c r="D6" s="26" t="s">
         <v>21</v>
       </c>
-      <c r="F6" s="64"/>
-      <c r="G6" s="64"/>
-      <c r="H6" s="64"/>
-      <c r="I6" s="64"/>
-      <c r="J6" s="64"/>
+      <c r="F6" s="68"/>
+      <c r="G6" s="68"/>
+      <c r="H6" s="68"/>
+      <c r="I6" s="68"/>
+      <c r="J6" s="68"/>
     </row>
     <row r="7" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B7" s="39" t="s">
@@ -13367,181 +13443,181 @@
       <c r="D7" s="26" t="s">
         <v>24</v>
       </c>
-      <c r="F7" s="64"/>
-      <c r="G7" s="64"/>
-      <c r="H7" s="64"/>
-      <c r="I7" s="64"/>
-      <c r="J7" s="64"/>
+      <c r="F7" s="68"/>
+      <c r="G7" s="68"/>
+      <c r="H7" s="68"/>
+      <c r="I7" s="68"/>
+      <c r="J7" s="68"/>
     </row>
     <row r="9" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B9" s="37" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="D9" s="37" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="F9" s="37" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="H9" s="37" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="J9" s="37" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
     </row>
     <row r="10" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B10" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="D10" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="F10" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="H10" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="J10" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
     </row>
     <row r="11" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B11" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="D11" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="F11" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="H11" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="J11" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
     </row>
     <row r="12" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B12" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="D12" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="F12" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="H12" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="J12" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
     </row>
     <row r="13" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B13" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="D13" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="F13" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="H13" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="J13" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
     </row>
     <row r="14" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B14" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="D14" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="F14" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="H14" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="J14" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
     </row>
     <row r="15" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B15" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="D15" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="F15" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
     </row>
     <row r="16" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B16" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="D16" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="F16" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
     </row>
     <row r="17" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B17" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="F17" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
     </row>
     <row r="18" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B18" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="F18" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
     </row>
     <row r="19" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B19" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="F19" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
     </row>
     <row r="20" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B20" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="F20" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
     </row>
     <row r="21" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B21" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
     </row>
     <row r="22" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B22" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
     </row>
     <row r="23" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B23" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
     </row>
     <row r="27" spans="2:10" x14ac:dyDescent="0.35">
@@ -13549,279 +13625,279 @@
         <v>55</v>
       </c>
       <c r="C27" s="26" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D27" s="26" t="s">
         <v>21</v>
       </c>
-      <c r="F27" s="65" t="s">
-        <v>251</v>
-      </c>
-      <c r="G27" s="65"/>
-      <c r="H27" s="65"/>
-      <c r="I27" s="65"/>
-      <c r="J27" s="65"/>
+      <c r="F27" s="69" t="s">
+        <v>250</v>
+      </c>
+      <c r="G27" s="69"/>
+      <c r="H27" s="69"/>
+      <c r="I27" s="69"/>
+      <c r="J27" s="69"/>
     </row>
     <row r="28" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B28" s="39" t="s">
         <v>57</v>
       </c>
       <c r="C28" s="26" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D28" s="26" t="s">
         <v>21</v>
       </c>
-      <c r="F28" s="65" t="s">
-        <v>252</v>
-      </c>
-      <c r="G28" s="65"/>
-      <c r="H28" s="65"/>
-      <c r="I28" s="65"/>
-      <c r="J28" s="65"/>
+      <c r="F28" s="69" t="s">
+        <v>251</v>
+      </c>
+      <c r="G28" s="69"/>
+      <c r="H28" s="69"/>
+      <c r="I28" s="69"/>
+      <c r="J28" s="69"/>
     </row>
     <row r="29" spans="2:10" ht="31" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B29" s="39" t="s">
         <v>60</v>
       </c>
       <c r="C29" s="26" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D29" s="26" t="s">
         <v>21</v>
       </c>
-      <c r="F29" s="63" t="s">
-        <v>253</v>
-      </c>
-      <c r="G29" s="63"/>
-      <c r="H29" s="63"/>
-      <c r="I29" s="63"/>
-      <c r="J29" s="63"/>
+      <c r="F29" s="67" t="s">
+        <v>252</v>
+      </c>
+      <c r="G29" s="67"/>
+      <c r="H29" s="67"/>
+      <c r="I29" s="67"/>
+      <c r="J29" s="67"/>
     </row>
     <row r="30" spans="2:10" ht="29.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B30" s="39" t="s">
         <v>64</v>
       </c>
       <c r="C30" s="26" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D30" s="26" t="s">
         <v>21</v>
       </c>
-      <c r="F30" s="63" t="s">
-        <v>254</v>
-      </c>
-      <c r="G30" s="63"/>
-      <c r="H30" s="63"/>
-      <c r="I30" s="63"/>
-      <c r="J30" s="63"/>
+      <c r="F30" s="67" t="s">
+        <v>253</v>
+      </c>
+      <c r="G30" s="67"/>
+      <c r="H30" s="67"/>
+      <c r="I30" s="67"/>
+      <c r="J30" s="67"/>
     </row>
     <row r="31" spans="2:10" ht="20" x14ac:dyDescent="0.35">
       <c r="B31" s="39" t="s">
         <v>69</v>
       </c>
       <c r="C31" s="26" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="D31" s="26" t="s">
         <v>24</v>
       </c>
-      <c r="F31" s="63" t="s">
-        <v>255</v>
-      </c>
-      <c r="G31" s="63"/>
-      <c r="H31" s="63"/>
-      <c r="I31" s="63"/>
-      <c r="J31" s="63"/>
+      <c r="F31" s="67" t="s">
+        <v>254</v>
+      </c>
+      <c r="G31" s="67"/>
+      <c r="H31" s="67"/>
+      <c r="I31" s="67"/>
+      <c r="J31" s="67"/>
     </row>
     <row r="32" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B32" s="45"/>
     </row>
     <row r="34" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B34" s="37" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="D34" s="37" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="F34" s="37" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="H34" s="37" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
     </row>
     <row r="35" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B35" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="D35" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="F35" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="H35" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
     </row>
     <row r="36" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B36" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="D36" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="F36" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="H36" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
     </row>
     <row r="37" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B37" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="D37" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="F37" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="H37" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
     </row>
     <row r="38" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B38" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="D38" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="F38" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="H38" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
     </row>
     <row r="39" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B39" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
     </row>
     <row r="41" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B41" s="37" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="D41" s="37" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="F41" s="37" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="H41" s="37" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
     </row>
     <row r="42" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B42" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="D42" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="F42" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="H42" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
     </row>
     <row r="43" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B43" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="D43" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="F43" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
     </row>
     <row r="44" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B44" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="D44" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="F44" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
     </row>
     <row r="45" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B45" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="D45" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
     </row>
     <row r="46" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B46" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="D46" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
     </row>
     <row r="47" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B47" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="D47" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
     </row>
     <row r="49" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B49" s="37" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="D49" s="37" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="F49" s="37" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
     </row>
     <row r="50" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B50" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="D50" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="F50" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
     </row>
     <row r="51" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B51" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="D51" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
     </row>
     <row r="52" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B52" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="D52" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
     </row>
   </sheetData>
@@ -13844,454 +13920,454 @@
   <sheetData>
     <row r="4" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B4" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
     </row>
     <row r="5" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B5" t="s">
+        <v>256</v>
+      </c>
+      <c r="C5" t="s">
         <v>257</v>
       </c>
-      <c r="C5" t="s">
+      <c r="D5" t="s">
         <v>258</v>
       </c>
-      <c r="D5" t="s">
+      <c r="E5" t="s">
         <v>259</v>
       </c>
-      <c r="E5" t="s">
+      <c r="F5" t="s">
         <v>260</v>
       </c>
-      <c r="F5" t="s">
+      <c r="G5" t="s">
         <v>261</v>
       </c>
-      <c r="G5" t="s">
+      <c r="H5" t="s">
         <v>262</v>
       </c>
-      <c r="H5" t="s">
+      <c r="I5" t="s">
         <v>263</v>
-      </c>
-      <c r="I5" t="s">
-        <v>264</v>
       </c>
     </row>
     <row r="6" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B6" t="s">
+        <v>264</v>
+      </c>
+      <c r="C6" t="s">
         <v>265</v>
       </c>
-      <c r="C6" t="s">
+      <c r="D6" t="s">
+        <v>265</v>
+      </c>
+      <c r="E6" t="s">
+        <v>183</v>
+      </c>
+      <c r="F6" t="s">
         <v>266</v>
       </c>
-      <c r="D6" t="s">
+      <c r="G6" t="s">
         <v>266</v>
       </c>
-      <c r="E6" t="s">
-        <v>184</v>
-      </c>
-      <c r="F6" t="s">
+      <c r="H6" t="s">
         <v>267</v>
       </c>
-      <c r="G6" t="s">
-        <v>267</v>
-      </c>
-      <c r="H6" t="s">
+      <c r="I6" t="s">
         <v>268</v>
-      </c>
-      <c r="I6" t="s">
-        <v>269</v>
       </c>
     </row>
     <row r="7" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B7" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="C7" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="D7" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="E7" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="F7" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="G7" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="H7" t="s">
+        <v>269</v>
+      </c>
+      <c r="I7" t="s">
         <v>270</v>
-      </c>
-      <c r="I7" t="s">
-        <v>271</v>
       </c>
     </row>
     <row r="8" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B8" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="C8" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="D8" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="E8" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="F8" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="G8" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="H8" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="I8" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
     </row>
     <row r="9" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B9" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="C9" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="D9" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="E9" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="F9" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="G9" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="H9" t="s">
+        <v>271</v>
+      </c>
+      <c r="I9" t="s">
         <v>272</v>
-      </c>
-      <c r="I9" t="s">
-        <v>273</v>
       </c>
     </row>
     <row r="10" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B10" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="C10" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="D10" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="E10" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="F10" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="G10" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="H10" t="s">
+        <v>273</v>
+      </c>
+      <c r="I10" t="s">
         <v>274</v>
-      </c>
-      <c r="I10" t="s">
-        <v>275</v>
       </c>
     </row>
     <row r="11" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B11" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="C11" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="D11" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="E11" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="F11" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="G11" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="H11" t="s">
+        <v>273</v>
+      </c>
+      <c r="I11" t="s">
         <v>274</v>
-      </c>
-      <c r="I11" t="s">
-        <v>275</v>
       </c>
     </row>
     <row r="12" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B12" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="C12" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="D12" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="E12" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="F12" t="s">
+        <v>266</v>
+      </c>
+      <c r="G12" t="s">
+        <v>266</v>
+      </c>
+      <c r="H12" t="s">
         <v>267</v>
       </c>
-      <c r="G12" t="s">
-        <v>267</v>
-      </c>
-      <c r="H12" t="s">
-        <v>268</v>
-      </c>
       <c r="I12" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
     </row>
     <row r="15" spans="2:9" ht="15" x14ac:dyDescent="0.4">
       <c r="B15" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
     </row>
     <row r="16" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B16" t="s">
+        <v>256</v>
+      </c>
+      <c r="C16" t="s">
         <v>257</v>
       </c>
-      <c r="C16" t="s">
+      <c r="D16" t="s">
         <v>258</v>
       </c>
-      <c r="D16" t="s">
+      <c r="E16" t="s">
         <v>259</v>
       </c>
-      <c r="E16" t="s">
+      <c r="F16" t="s">
         <v>260</v>
       </c>
-      <c r="F16" t="s">
+      <c r="G16" t="s">
         <v>261</v>
       </c>
-      <c r="G16" t="s">
+      <c r="H16" t="s">
         <v>262</v>
       </c>
-      <c r="H16" t="s">
+      <c r="I16" t="s">
         <v>263</v>
-      </c>
-      <c r="I16" t="s">
-        <v>264</v>
       </c>
     </row>
     <row r="17" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B17" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="C17" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="D17" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="E17" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="F17" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="G17" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="H17" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="I17" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
     </row>
     <row r="18" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B18" t="s">
+        <v>277</v>
+      </c>
+      <c r="C18" t="s">
         <v>278</v>
       </c>
-      <c r="C18" t="s">
+      <c r="D18" t="s">
         <v>279</v>
       </c>
-      <c r="D18" t="s">
+      <c r="E18" t="s">
         <v>280</v>
       </c>
-      <c r="E18" t="s">
+      <c r="F18" t="s">
+        <v>266</v>
+      </c>
+      <c r="G18" t="s">
         <v>281</v>
       </c>
-      <c r="F18" t="s">
+      <c r="H18" t="s">
         <v>267</v>
       </c>
-      <c r="G18" t="s">
+      <c r="I18" t="s">
         <v>282</v>
-      </c>
-      <c r="H18" t="s">
-        <v>268</v>
-      </c>
-      <c r="I18" t="s">
-        <v>283</v>
       </c>
     </row>
     <row r="19" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B19" t="s">
+        <v>283</v>
+      </c>
+      <c r="C19" t="s">
         <v>284</v>
       </c>
-      <c r="C19" t="s">
-        <v>285</v>
-      </c>
       <c r="D19" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="E19" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="F19" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="G19" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="H19" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="I19" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
     </row>
     <row r="20" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B20" t="s">
+        <v>285</v>
+      </c>
+      <c r="C20" t="s">
         <v>286</v>
       </c>
-      <c r="C20" t="s">
-        <v>287</v>
-      </c>
       <c r="D20" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="E20" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="F20" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="G20" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="H20" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="I20" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
     </row>
     <row r="21" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B21" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="C21" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="D21" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="E21" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="F21" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="G21" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="H21" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="I21" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
     </row>
     <row r="22" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B22" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="C22" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="D22" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="E22" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="F22" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="G22" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="H22" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="I22" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
     </row>
     <row r="23" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B23" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="C23" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="D23" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="E23" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="F23" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="G23" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="H23" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="I23" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
     </row>
     <row r="24" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B24" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="C24" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="D24" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="E24" t="s">
+        <v>288</v>
+      </c>
+      <c r="F24" t="s">
+        <v>266</v>
+      </c>
+      <c r="G24" t="s">
+        <v>288</v>
+      </c>
+      <c r="H24" t="s">
+        <v>271</v>
+      </c>
+      <c r="I24" t="s">
         <v>289</v>
-      </c>
-      <c r="F24" t="s">
-        <v>267</v>
-      </c>
-      <c r="G24" t="s">
-        <v>289</v>
-      </c>
-      <c r="H24" t="s">
-        <v>272</v>
-      </c>
-      <c r="I24" t="s">
-        <v>290</v>
       </c>
     </row>
   </sheetData>
@@ -14300,15 +14376,12 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="882a8f42-f1f9-4ba8-a024-a9506b2a3f1b" xsi:nil="true"/>
-    <Comentario xmlns="f3dc767a-0b06-462e-8350-fa01f76d53d6" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="f3dc767a-0b06-462e-8350-fa01f76d53d6">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -14549,27 +14622,21 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="882a8f42-f1f9-4ba8-a024-a9506b2a3f1b" xsi:nil="true"/>
+    <Comentario xmlns="f3dc767a-0b06-462e-8350-fa01f76d53d6" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="f3dc767a-0b06-462e-8350-fa01f76d53d6">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{784A4964-F218-48FA-B8A8-6EC1F8CC6785}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F2F9F198-AAB3-4743-83B7-70E545DDE86B}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="882a8f42-f1f9-4ba8-a024-a9506b2a3f1b"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="f3dc767a-0b06-462e-8350-fa01f76d53d6"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -14594,9 +14661,18 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F2F9F198-AAB3-4743-83B7-70E545DDE86B}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{784A4964-F218-48FA-B8A8-6EC1F8CC6785}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="882a8f42-f1f9-4ba8-a024-a9506b2a3f1b"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="f3dc767a-0b06-462e-8350-fa01f76d53d6"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>